--- a/AAPL.xlsx
+++ b/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE27E36A-FAB8-45DB-A65D-4EEF6B086BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295740D7-C36C-442C-85B0-0084DAE2192C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42260" yWindow="2970" windowWidth="24340" windowHeight="15680" activeTab="1" xr2:uid="{B6F3B1E3-62A6-41E2-953C-3DEF4B9ACA9E}"/>
+    <workbookView xWindow="160" yWindow="1310" windowWidth="20990" windowHeight="18600" activeTab="1" xr2:uid="{B6F3B1E3-62A6-41E2-953C-3DEF4B9ACA9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -727,14 +727,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>29236</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>7339</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>29236</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>7339</xdr:colOff>
       <xdr:row>107</xdr:row>
       <xdr:rowOff>59120</xdr:rowOff>
     </xdr:to>
@@ -751,7 +751,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21308305" y="0"/>
+          <a:off x="23138856" y="0"/>
           <a:ext cx="0" cy="16998292"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="6">
-        <v>269</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="O4" s="2">
         <f>+O2*O3</f>
-        <v>4021012</v>
+        <v>4992632</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="O7" s="2">
         <f>+O4-O5+O6</f>
-        <v>3989724</v>
+        <v>4961344</v>
       </c>
     </row>
     <row r="10" spans="14:16" x14ac:dyDescent="0.25">
@@ -1367,6 +1367,15 @@
         <f t="shared" si="0"/>
         <v>45929</v>
       </c>
+      <c r="AI2" s="11">
+        <v>46018</v>
+      </c>
+      <c r="AJ2" s="11">
+        <v>46109</v>
+      </c>
+      <c r="AK2" s="11">
+        <v>46200</v>
+      </c>
       <c r="BH2" s="11">
         <v>43008</v>
       </c>
@@ -2093,6 +2102,15 @@
       </c>
       <c r="AH10" s="7">
         <v>49025</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>85269</v>
+      </c>
+      <c r="AJ10" s="7">
+        <v>56994</v>
+      </c>
+      <c r="AK10" s="7">
+        <v>54252</v>
       </c>
       <c r="AR10" s="7">
         <v>0</v>
@@ -2705,6 +2723,15 @@
       <c r="AH14" s="7">
         <v>8726</v>
       </c>
+      <c r="AI14" s="7">
+        <v>8386</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>8399</v>
+      </c>
+      <c r="AK14" s="7">
+        <v>10352</v>
+      </c>
       <c r="AQ14" s="7">
         <f>2747+948+2381</f>
         <v>6076</v>
@@ -2940,6 +2967,15 @@
       <c r="AH15" s="7">
         <v>6952</v>
       </c>
+      <c r="AI15" s="7">
+        <v>8595</v>
+      </c>
+      <c r="AJ15" s="7">
+        <v>6914</v>
+      </c>
+      <c r="AK15" s="7">
+        <v>6191</v>
+      </c>
       <c r="AQ15" s="7">
         <v>0</v>
       </c>
@@ -3173,6 +3209,15 @@
       </c>
       <c r="AH16" s="7">
         <v>9013</v>
+      </c>
+      <c r="AI16" s="7">
+        <v>11493</v>
+      </c>
+      <c r="AJ16" s="7">
+        <v>7901</v>
+      </c>
+      <c r="AK16" s="7">
+        <v>7883</v>
       </c>
       <c r="AQ16" s="7">
         <v>809</v>
@@ -3438,107 +3483,107 @@
         <v>73716</v>
       </c>
       <c r="AI18" s="2">
-        <f t="shared" ref="AI18" si="18">+AE18*1.01</f>
-        <v>98939.6</v>
+        <f>SUM(AI10:AI16)</f>
+        <v>113743</v>
       </c>
       <c r="AJ18" s="2">
-        <f t="shared" ref="AJ18" si="19">+AF18*1.01</f>
-        <v>69401.14</v>
+        <f>SUM(AJ10:AJ16)</f>
+        <v>80208</v>
       </c>
       <c r="AK18" s="2">
-        <f t="shared" ref="AK18" si="20">+AG18*1.01</f>
-        <v>67279.13</v>
+        <f t="shared" ref="AK18" si="18">SUM(AK10:AK16)</f>
+        <v>78678</v>
       </c>
       <c r="AL18" s="2">
-        <f t="shared" ref="AL18" si="21">+AH18*1.01</f>
+        <f t="shared" ref="AL18" si="19">+AH18*1.01</f>
         <v>74453.16</v>
       </c>
       <c r="AQ18" s="2">
-        <f t="shared" ref="AQ18:AZ18" si="22">SUM(AQ14:AQ16)+AQ10</f>
+        <f t="shared" ref="AQ18:AZ18" si="20">SUM(AQ14:AQ16)+AQ10</f>
         <v>6885</v>
       </c>
       <c r="AR18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>4790</v>
       </c>
       <c r="AS18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>5208</v>
       </c>
       <c r="AT18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>5527</v>
       </c>
       <c r="AU18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7180</v>
       </c>
       <c r="AV18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>11941</v>
       </c>
       <c r="AW18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>16151</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>20002</v>
       </c>
       <c r="AY18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>31943</v>
       </c>
       <c r="AZ18" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>36458</v>
       </c>
       <c r="BA18" s="2">
-        <f t="shared" ref="BA18:BL18" si="23">SUM(BA14:BA16)+BA10</f>
+        <f t="shared" ref="BA18:BL18" si="21">SUM(BA14:BA16)+BA10</f>
         <v>57704</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>98876</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>143618</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>154859</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>164732</v>
       </c>
       <c r="BF18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>213806</v>
       </c>
       <c r="BG18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>191291</v>
       </c>
       <c r="BH18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>199254</v>
       </c>
       <c r="BI18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>225847</v>
       </c>
       <c r="BJ18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>213883</v>
       </c>
       <c r="BK18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>220747</v>
       </c>
       <c r="BL18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>297392</v>
       </c>
       <c r="BM18" s="2">
@@ -3554,67 +3599,67 @@
         <v>294866</v>
       </c>
       <c r="BP18" s="2">
-        <f t="shared" ref="BP18:CE18" si="24">SUM(BP14:BP16)+BP10</f>
+        <f t="shared" ref="BP18:CE18" si="22">SUM(BP14:BP16)+BP10</f>
         <v>326446.54026193754</v>
       </c>
       <c r="BQ18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>344262.75016477366</v>
       </c>
       <c r="BR18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>363073.98012930644</v>
       </c>
       <c r="BS18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>382936.92460642371</v>
       </c>
       <c r="BT18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>403911.56568950473</v>
       </c>
       <c r="BU18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>422751.74961020425</v>
       </c>
       <c r="BV18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>442481.65168507554</v>
       </c>
       <c r="BW18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>463143.86935604434</v>
       </c>
       <c r="BX18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>484783.07066497603</v>
       </c>
       <c r="BY18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>503981.26037662197</v>
       </c>
       <c r="BZ18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>523402.72874613688</v>
       </c>
       <c r="CA18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>543581.95842149435</v>
       </c>
       <c r="CB18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>564548.951177057</v>
       </c>
       <c r="CC18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>586334.916894019</v>
       </c>
       <c r="CD18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>608972.32313889323</v>
       </c>
       <c r="CE18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>632494.94681880996</v>
       </c>
     </row>
@@ -3708,19 +3753,16 @@
         <v>28750</v>
       </c>
       <c r="AI19" s="2">
-        <f t="shared" ref="AI19" si="25">+AE19*1.05</f>
-        <v>27657</v>
+        <v>30013</v>
       </c>
       <c r="AJ19" s="2">
-        <f t="shared" ref="AJ19" si="26">+AF19*1.05</f>
-        <v>27977.25</v>
+        <v>30976</v>
       </c>
       <c r="AK19" s="2">
-        <f t="shared" ref="AK19" si="27">+AG19*1.05</f>
-        <v>28794.15</v>
+        <v>30739</v>
       </c>
       <c r="AL19" s="2">
-        <f t="shared" ref="AL19" si="28">+AH19*1.05</f>
+        <f t="shared" ref="AL19" si="23">+AH19*1.05</f>
         <v>30187.5</v>
       </c>
       <c r="AQ19" s="2">
@@ -3798,7 +3840,7 @@
         <v>53768</v>
       </c>
       <c r="BL19" s="7">
-        <f t="shared" ref="BL19" si="29">SUM(O19:R19)</f>
+        <f t="shared" ref="BL19" si="24">SUM(O19:R19)</f>
         <v>68425</v>
       </c>
       <c r="BM19" s="7">
@@ -3834,47 +3876,47 @@
         <v>154561.13384250004</v>
       </c>
       <c r="BU19" s="7">
-        <f t="shared" ref="BU19:CE19" si="30">+BT19*1.05</f>
+        <f t="shared" ref="BU19:CE19" si="25">+BT19*1.05</f>
         <v>162289.19053462506</v>
       </c>
       <c r="BV19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>170403.65006135631</v>
       </c>
       <c r="BW19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>178923.83256442414</v>
       </c>
       <c r="BX19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>187870.02419264536</v>
       </c>
       <c r="BY19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>197263.52540227765</v>
       </c>
       <c r="BZ19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>207126.70167239153</v>
       </c>
       <c r="CA19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>217483.0367560111</v>
       </c>
       <c r="CB19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>228357.18859381168</v>
       </c>
       <c r="CC19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>239775.04802350226</v>
       </c>
       <c r="CD19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>251763.80042467738</v>
       </c>
       <c r="CE19" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>264351.99044591124</v>
       </c>
     </row>
@@ -3883,35 +3925,35 @@
         <v>7</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:F20" si="31">+C18+C19</f>
+        <f t="shared" ref="C20:F20" si="26">+C18+C19</f>
         <v>88293</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>61137</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>53265</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="26"/>
         <v>62900</v>
       </c>
       <c r="K20" s="8">
-        <f t="shared" ref="K20:N20" si="32">+K18+K19</f>
+        <f t="shared" ref="K20:N20" si="27">+K18+K19</f>
         <v>91819</v>
       </c>
       <c r="L20" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>58313</v>
       </c>
       <c r="M20" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>59685</v>
       </c>
       <c r="N20" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>64698</v>
       </c>
       <c r="O20" s="8">
@@ -3927,11 +3969,11 @@
         <v>81434</v>
       </c>
       <c r="R20" s="8">
-        <f t="shared" ref="R20" si="33">+R18+R19</f>
+        <f t="shared" ref="R20" si="28">+R18+R19</f>
         <v>83360</v>
       </c>
       <c r="S20" s="8">
-        <f t="shared" ref="S20" si="34">+S18+S19</f>
+        <f t="shared" ref="S20" si="29">+S18+S19</f>
         <v>123945</v>
       </c>
       <c r="T20" s="8">
@@ -3939,7 +3981,7 @@
         <v>97278</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" ref="U20" si="35">+U18+U19</f>
+        <f t="shared" ref="U20" si="30">+U18+U19</f>
         <v>82959</v>
       </c>
       <c r="V20" s="8">
@@ -3951,63 +3993,63 @@
         <v>117154</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" ref="X20:Z20" si="36">+X19+X18</f>
+        <f t="shared" ref="X20:Z20" si="31">+X19+X18</f>
         <v>94836</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>81797</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>89498</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" ref="AA20:AB20" si="37">+AA19+AA18</f>
+        <f t="shared" ref="AA20:AB20" si="32">+AA19+AA18</f>
         <v>119575</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="32"/>
         <v>90753</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" ref="AC20:AF20" si="38">+AC19+AC18</f>
+        <f t="shared" ref="AC20:AF20" si="33">+AC19+AC18</f>
         <v>85777</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="33"/>
         <v>94930</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="33"/>
         <v>124300</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="33"/>
         <v>95359</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" ref="AG20:AL20" si="39">+AG19+AG18</f>
+        <f t="shared" ref="AG20:AL20" si="34">+AG19+AG18</f>
         <v>94036</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>102466</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="39"/>
-        <v>126596.6</v>
+        <f t="shared" si="34"/>
+        <v>143756</v>
       </c>
       <c r="AJ20" s="8">
-        <f t="shared" si="39"/>
-        <v>97378.39</v>
+        <f>+AJ19+AJ18</f>
+        <v>111184</v>
       </c>
       <c r="AK20" s="8">
-        <f t="shared" si="39"/>
-        <v>96073.279999999999</v>
+        <f t="shared" si="34"/>
+        <v>109417</v>
       </c>
       <c r="AL20" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>104640.66</v>
       </c>
       <c r="AO20" s="8">
@@ -4017,83 +4059,83 @@
         <v>6134</v>
       </c>
       <c r="AQ20" s="8">
-        <f t="shared" ref="AQ20:BI20" si="40">+AQ18+AQ19</f>
+        <f t="shared" ref="AQ20:BI20" si="35">+AQ18+AQ19</f>
         <v>7983</v>
       </c>
       <c r="AR20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>5363</v>
       </c>
       <c r="AS20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>5742</v>
       </c>
       <c r="AT20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>6207</v>
       </c>
       <c r="AU20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>8279</v>
       </c>
       <c r="AV20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>13931</v>
       </c>
       <c r="AW20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>19315</v>
       </c>
       <c r="AX20" s="16">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>24006</v>
       </c>
       <c r="AY20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>37491</v>
       </c>
       <c r="AZ20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>42905</v>
       </c>
       <c r="BA20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>65225</v>
       </c>
       <c r="BB20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>108249</v>
       </c>
       <c r="BC20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>156508</v>
       </c>
       <c r="BD20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>170910</v>
       </c>
       <c r="BE20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>182795</v>
       </c>
       <c r="BF20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>233715</v>
       </c>
       <c r="BG20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>215639</v>
       </c>
       <c r="BH20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>229234</v>
       </c>
       <c r="BI20" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="35"/>
         <v>265595</v>
       </c>
       <c r="BJ20" s="8">
-        <f t="shared" ref="BJ20" si="41">+BJ18+BJ19</f>
+        <f t="shared" ref="BJ20" si="36">+BJ18+BJ19</f>
         <v>260174</v>
       </c>
       <c r="BK20" s="8">
@@ -4113,71 +4155,71 @@
         <v>383285</v>
       </c>
       <c r="BO20" s="8">
-        <f t="shared" ref="BO20:CE20" si="42">+BO18+BO19</f>
+        <f t="shared" ref="BO20:CE20" si="37">+BO18+BO19</f>
         <v>391035</v>
       </c>
       <c r="BP20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>437040.89026193751</v>
       </c>
       <c r="BQ20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>465916.5351647737</v>
       </c>
       <c r="BR20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>496893.14362930646</v>
       </c>
       <c r="BS20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>530138.00445642369</v>
       </c>
       <c r="BT20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>558472.69953200477</v>
       </c>
       <c r="BU20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>585040.94014482934</v>
       </c>
       <c r="BV20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>612885.30174643185</v>
       </c>
       <c r="BW20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>642067.70192046848</v>
       </c>
       <c r="BX20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>672653.09485762136</v>
       </c>
       <c r="BY20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>701244.78577889968</v>
       </c>
       <c r="BZ20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>730529.43041852838</v>
       </c>
       <c r="CA20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>761064.99517750542</v>
       </c>
       <c r="CB20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>792906.1397708687</v>
       </c>
       <c r="CC20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>826109.96491752123</v>
       </c>
       <c r="CD20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>860736.12356357067</v>
       </c>
       <c r="CE20" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>896846.93726472114</v>
       </c>
     </row>
@@ -4268,11 +4310,11 @@
         <v>151286</v>
       </c>
       <c r="BL21" s="7">
-        <f t="shared" ref="BL21:BL22" si="43">SUM(O21:R21)</f>
+        <f t="shared" ref="BL21:BL22" si="38">SUM(O21:R21)</f>
         <v>192266</v>
       </c>
       <c r="BM21" s="7">
-        <f t="shared" ref="BM21:BM22" si="44">SUM(S21:V21)</f>
+        <f t="shared" ref="BM21:BM22" si="39">SUM(S21:V21)</f>
         <v>201471</v>
       </c>
       <c r="BN21" s="2">
@@ -4280,71 +4322,71 @@
         <v>189282</v>
       </c>
       <c r="BO21" s="2">
-        <f t="shared" ref="BO21:BO22" si="45">SUM(AA21:AD21)</f>
+        <f t="shared" ref="BO21:BO22" si="40">SUM(AA21:AD21)</f>
         <v>185233</v>
       </c>
       <c r="BP21" s="2">
-        <f t="shared" ref="BP21:CE21" si="46">+BP18*0.64</f>
+        <f t="shared" ref="BP21:CE21" si="41">+BP18*0.64</f>
         <v>208925.78576764002</v>
       </c>
       <c r="BQ21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>220328.16010545514</v>
       </c>
       <c r="BR21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>232367.34728275612</v>
       </c>
       <c r="BS21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>245079.63174811119</v>
       </c>
       <c r="BT21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>258503.40204128303</v>
       </c>
       <c r="BU21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>270561.11975053075</v>
       </c>
       <c r="BV21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>283188.25707844837</v>
       </c>
       <c r="BW21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>296412.07638786838</v>
       </c>
       <c r="BX21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>310261.16522558464</v>
       </c>
       <c r="BY21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>322548.00664103805</v>
       </c>
       <c r="BZ21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>334977.74639752763</v>
       </c>
       <c r="CA21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>347892.45338975638</v>
       </c>
       <c r="CB21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>361311.32875331648</v>
       </c>
       <c r="CC21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>375254.34681217215</v>
       </c>
       <c r="CD21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>389742.28680889169</v>
       </c>
       <c r="CE21" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="41"/>
         <v>404796.76596403838</v>
       </c>
     </row>
@@ -4435,11 +4477,11 @@
         <v>18273</v>
       </c>
       <c r="BL22" s="7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="38"/>
         <v>20715</v>
       </c>
       <c r="BM22" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="39"/>
         <v>22075</v>
       </c>
       <c r="BN22" s="2">
@@ -4447,71 +4489,71 @@
         <v>24855</v>
       </c>
       <c r="BO22" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>25119</v>
       </c>
       <c r="BP22" s="2">
-        <f t="shared" ref="BP22:CE22" si="47">+BP19*0.27</f>
+        <f t="shared" ref="BP22:CE22" si="42">+BP19*0.27</f>
         <v>29860.4745</v>
       </c>
       <c r="BQ22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>32846.521950000002</v>
       </c>
       <c r="BR22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>36131.174145000012</v>
       </c>
       <c r="BS22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>39744.291559500016</v>
       </c>
       <c r="BT22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>41731.506137475015</v>
       </c>
       <c r="BU22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>43818.081444348769</v>
       </c>
       <c r="BV22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>46008.985516566208</v>
       </c>
       <c r="BW22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>48309.434792394524</v>
       </c>
       <c r="BX22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>50724.906532014247</v>
       </c>
       <c r="BY22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>53261.151858614969</v>
       </c>
       <c r="BZ22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>55924.209451545714</v>
       </c>
       <c r="CA22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>58720.419924123002</v>
       </c>
       <c r="CB22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>61656.440920329158</v>
       </c>
       <c r="CC22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>64739.26296634561</v>
       </c>
       <c r="CD22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>67976.226114662903</v>
       </c>
       <c r="CE22" s="2">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>71375.037420396038</v>
       </c>
     </row>
@@ -4533,19 +4575,19 @@
         <v>38816</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" ref="K23:N23" si="48">+K21+K22</f>
+        <f t="shared" ref="K23:N23" si="43">+K21+K22</f>
         <v>56602</v>
       </c>
       <c r="L23" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>35943</v>
       </c>
       <c r="M23" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>37005</v>
       </c>
       <c r="N23" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>40009</v>
       </c>
       <c r="O23" s="2">
@@ -4561,11 +4603,11 @@
         <v>46179</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" ref="R23" si="49">+R21+R22</f>
+        <f t="shared" ref="R23" si="44">+R21+R22</f>
         <v>48186</v>
       </c>
       <c r="S23" s="2">
-        <f t="shared" ref="S23" si="50">+S21+S22</f>
+        <f t="shared" ref="S23" si="45">+S21+S22</f>
         <v>69702</v>
       </c>
       <c r="T23" s="2">
@@ -4573,59 +4615,59 @@
         <v>54719</v>
       </c>
       <c r="U23" s="2">
-        <f t="shared" ref="U23" si="51">+U21+U22</f>
+        <f t="shared" ref="U23" si="46">+U21+U22</f>
         <v>47074</v>
       </c>
       <c r="V23" s="2">
-        <f t="shared" ref="V23" si="52">+V21+V22</f>
+        <f t="shared" ref="V23" si="47">+V21+V22</f>
         <v>52051</v>
       </c>
       <c r="W23" s="2">
-        <f t="shared" ref="W23:AF23" si="53">+W21+W22</f>
+        <f t="shared" ref="W23:AF23" si="48">+W21+W22</f>
         <v>66822</v>
       </c>
       <c r="X23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>52860</v>
       </c>
       <c r="Y23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>45384</v>
       </c>
       <c r="Z23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>49071</v>
       </c>
       <c r="AA23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>64720</v>
       </c>
       <c r="AB23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>48482</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>46099</v>
       </c>
       <c r="AD23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>51051</v>
       </c>
       <c r="AE23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>66025</v>
       </c>
       <c r="AF23" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="48"/>
         <v>50492</v>
       </c>
       <c r="AG23" s="2">
-        <f t="shared" ref="AG23:AH23" si="54">+AG21+AG22</f>
+        <f t="shared" ref="AG23:AH23" si="49">+AG21+AG22</f>
         <v>50318</v>
       </c>
       <c r="AH23" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>54125</v>
       </c>
       <c r="AQ23" s="2">
@@ -4683,11 +4725,11 @@
         <v>141048</v>
       </c>
       <c r="BI23" s="2">
-        <f t="shared" ref="BI23:BJ23" si="55">+BI21+BI22</f>
+        <f t="shared" ref="BI23:BJ23" si="50">+BI21+BI22</f>
         <v>163756</v>
       </c>
       <c r="BJ23" s="2">
-        <f t="shared" si="55"/>
+        <f t="shared" si="50"/>
         <v>161782</v>
       </c>
       <c r="BK23" s="2">
@@ -4703,75 +4745,75 @@
         <v>223546</v>
       </c>
       <c r="BN23" s="2">
-        <f t="shared" ref="BN23:CE23" si="56">+BN21+BN22</f>
+        <f t="shared" ref="BN23:CE23" si="51">+BN21+BN22</f>
         <v>214137</v>
       </c>
       <c r="BO23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>210352</v>
       </c>
       <c r="BP23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>238786.26026764003</v>
       </c>
       <c r="BQ23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>253174.68205545514</v>
       </c>
       <c r="BR23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>268498.52142775612</v>
       </c>
       <c r="BS23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>284823.9233076112</v>
       </c>
       <c r="BT23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>300234.90817875805</v>
       </c>
       <c r="BU23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>314379.20119487954</v>
       </c>
       <c r="BV23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>329197.24259501457</v>
       </c>
       <c r="BW23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>344721.5111802629</v>
       </c>
       <c r="BX23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>360986.0717575989</v>
       </c>
       <c r="BY23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>375809.15849965304</v>
       </c>
       <c r="BZ23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>390901.95584907336</v>
       </c>
       <c r="CA23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>406612.87331387936</v>
       </c>
       <c r="CB23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>422967.76967364561</v>
       </c>
       <c r="CC23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>439993.60977851774</v>
       </c>
       <c r="CD23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>457718.51292355458</v>
       </c>
       <c r="CE23" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>476171.80338443443</v>
       </c>
     </row>
@@ -4780,35 +4822,35 @@
         <v>22</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" ref="C24" si="57">+C20-C23</f>
+        <f t="shared" ref="C24" si="52">+C20-C23</f>
         <v>33912</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" ref="D24:F24" si="58">+D20-D23</f>
+        <f t="shared" ref="D24:F24" si="53">+D20-D23</f>
         <v>23422</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>20421</v>
       </c>
       <c r="F24" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="53"/>
         <v>24084</v>
       </c>
       <c r="K24" s="2">
-        <f t="shared" ref="K24:N24" si="59">+K20-K23</f>
+        <f t="shared" ref="K24:N24" si="54">+K20-K23</f>
         <v>35217</v>
       </c>
       <c r="L24" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>22370</v>
       </c>
       <c r="M24" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>22680</v>
       </c>
       <c r="N24" s="2">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>24689</v>
       </c>
       <c r="O24" s="2">
@@ -4824,11 +4866,11 @@
         <v>35255</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" ref="R24" si="60">+R20-R23</f>
+        <f t="shared" ref="R24" si="55">+R20-R23</f>
         <v>35174</v>
       </c>
       <c r="S24" s="2">
-        <f t="shared" ref="S24" si="61">+S20-S23</f>
+        <f t="shared" ref="S24" si="56">+S20-S23</f>
         <v>54243</v>
       </c>
       <c r="T24" s="2">
@@ -4836,83 +4878,83 @@
         <v>42559</v>
       </c>
       <c r="U24" s="2">
-        <f t="shared" ref="U24" si="62">+U20-U23</f>
+        <f t="shared" ref="U24" si="57">+U20-U23</f>
         <v>35885</v>
       </c>
       <c r="V24" s="2">
-        <f t="shared" ref="V24" si="63">+V20-V23</f>
+        <f t="shared" ref="V24" si="58">+V20-V23</f>
         <v>38095</v>
       </c>
       <c r="W24" s="2">
-        <f t="shared" ref="W24:AF24" si="64">+W20-W23</f>
+        <f t="shared" ref="W24:AF24" si="59">+W20-W23</f>
         <v>50332</v>
       </c>
       <c r="X24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>41976</v>
       </c>
       <c r="Y24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>36413</v>
       </c>
       <c r="Z24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>40427</v>
       </c>
       <c r="AA24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>54855</v>
       </c>
       <c r="AB24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>42271</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>39678</v>
       </c>
       <c r="AD24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>43879</v>
       </c>
       <c r="AE24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>58275</v>
       </c>
       <c r="AF24" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="59"/>
         <v>44867</v>
       </c>
       <c r="AG24" s="2">
-        <f t="shared" ref="AG24:AH24" si="65">+AG20-AG23</f>
+        <f t="shared" ref="AG24:AH24" si="60">+AG20-AG23</f>
         <v>43718</v>
       </c>
       <c r="AH24" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="60"/>
         <v>48341</v>
       </c>
       <c r="AI24" s="2">
         <f>+AI20*0.47</f>
-        <v>59500.402000000002</v>
+        <v>67565.319999999992</v>
       </c>
       <c r="AJ24" s="2">
         <f>+AJ20*0.47</f>
-        <v>45767.8433</v>
+        <v>52256.479999999996</v>
       </c>
       <c r="AK24" s="2">
         <f>+AK20*0.47</f>
-        <v>45154.441599999998</v>
+        <v>51425.99</v>
       </c>
       <c r="AL24" s="2">
         <f>+AL20*0.47</f>
         <v>49181.110199999996</v>
       </c>
       <c r="AQ24" s="2">
-        <f t="shared" ref="AQ24:AR24" si="66">+AQ20-AQ23</f>
+        <f t="shared" ref="AQ24:AR24" si="61">+AQ20-AQ23</f>
         <v>2166</v>
       </c>
       <c r="AR24" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="61"/>
         <v>1235</v>
       </c>
       <c r="AS24" s="2">
@@ -4920,71 +4962,71 @@
         <v>1603</v>
       </c>
       <c r="AT24" s="2">
-        <f t="shared" ref="AT24:AU24" si="67">+AT20-AT23</f>
+        <f t="shared" ref="AT24:AU24" si="62">+AT20-AT23</f>
         <v>1708</v>
       </c>
       <c r="AU24" s="2">
+        <f t="shared" si="62"/>
+        <v>2259</v>
+      </c>
+      <c r="AV24" s="2">
+        <f t="shared" ref="AV24:AW24" si="63">+AV20-AV23</f>
+        <v>4043</v>
+      </c>
+      <c r="AW24" s="2">
+        <f t="shared" si="63"/>
+        <v>5598</v>
+      </c>
+      <c r="AX24" s="2">
+        <f t="shared" ref="AX24:AY24" si="64">+AX20-AX23</f>
+        <v>8154</v>
+      </c>
+      <c r="AY24" s="2">
+        <f t="shared" si="64"/>
+        <v>13197</v>
+      </c>
+      <c r="AZ24" s="2">
+        <f t="shared" ref="AZ24:BB24" si="65">+AZ20-AZ23</f>
+        <v>17222</v>
+      </c>
+      <c r="BA24" s="2">
+        <f t="shared" si="65"/>
+        <v>25684</v>
+      </c>
+      <c r="BB24" s="2">
+        <f t="shared" si="65"/>
+        <v>43818</v>
+      </c>
+      <c r="BC24" s="2">
+        <f t="shared" ref="BC24:BH24" si="66">+BC20-BC23</f>
+        <v>68662</v>
+      </c>
+      <c r="BD24" s="2">
+        <f t="shared" si="66"/>
+        <v>64304</v>
+      </c>
+      <c r="BE24" s="2">
+        <f t="shared" si="66"/>
+        <v>70537</v>
+      </c>
+      <c r="BF24" s="2">
+        <f t="shared" si="66"/>
+        <v>93626</v>
+      </c>
+      <c r="BG24" s="2">
+        <f t="shared" si="66"/>
+        <v>84263</v>
+      </c>
+      <c r="BH24" s="2">
+        <f t="shared" si="66"/>
+        <v>88186</v>
+      </c>
+      <c r="BI24" s="2">
+        <f t="shared" ref="BI24:BJ24" si="67">+BI20-BI23</f>
+        <v>101839</v>
+      </c>
+      <c r="BJ24" s="2">
         <f t="shared" si="67"/>
-        <v>2259</v>
-      </c>
-      <c r="AV24" s="2">
-        <f t="shared" ref="AV24:AW24" si="68">+AV20-AV23</f>
-        <v>4043</v>
-      </c>
-      <c r="AW24" s="2">
-        <f t="shared" si="68"/>
-        <v>5598</v>
-      </c>
-      <c r="AX24" s="2">
-        <f t="shared" ref="AX24:AY24" si="69">+AX20-AX23</f>
-        <v>8154</v>
-      </c>
-      <c r="AY24" s="2">
-        <f t="shared" si="69"/>
-        <v>13197</v>
-      </c>
-      <c r="AZ24" s="2">
-        <f t="shared" ref="AZ24:BB24" si="70">+AZ20-AZ23</f>
-        <v>17222</v>
-      </c>
-      <c r="BA24" s="2">
-        <f t="shared" si="70"/>
-        <v>25684</v>
-      </c>
-      <c r="BB24" s="2">
-        <f t="shared" si="70"/>
-        <v>43818</v>
-      </c>
-      <c r="BC24" s="2">
-        <f t="shared" ref="BC24:BH24" si="71">+BC20-BC23</f>
-        <v>68662</v>
-      </c>
-      <c r="BD24" s="2">
-        <f t="shared" si="71"/>
-        <v>64304</v>
-      </c>
-      <c r="BE24" s="2">
-        <f t="shared" si="71"/>
-        <v>70537</v>
-      </c>
-      <c r="BF24" s="2">
-        <f t="shared" si="71"/>
-        <v>93626</v>
-      </c>
-      <c r="BG24" s="2">
-        <f t="shared" si="71"/>
-        <v>84263</v>
-      </c>
-      <c r="BH24" s="2">
-        <f t="shared" si="71"/>
-        <v>88186</v>
-      </c>
-      <c r="BI24" s="2">
-        <f t="shared" ref="BI24:BJ24" si="72">+BI20-BI23</f>
-        <v>101839</v>
-      </c>
-      <c r="BJ24" s="2">
-        <f t="shared" si="72"/>
         <v>98392</v>
       </c>
       <c r="BK24" s="2">
@@ -5000,75 +5042,75 @@
         <v>170782</v>
       </c>
       <c r="BN24" s="2">
-        <f t="shared" ref="BN24:CE24" si="73">+BN20-BN23</f>
+        <f t="shared" ref="BN24:CE24" si="68">+BN20-BN23</f>
         <v>169148</v>
       </c>
       <c r="BO24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>180683</v>
       </c>
       <c r="BP24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>198254.62999429749</v>
       </c>
       <c r="BQ24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>212741.85310931856</v>
       </c>
       <c r="BR24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>228394.62220155034</v>
       </c>
       <c r="BS24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>245314.08114881249</v>
       </c>
       <c r="BT24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>258237.79135324672</v>
       </c>
       <c r="BU24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>270661.73894994979</v>
       </c>
       <c r="BV24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>283688.05915141728</v>
       </c>
       <c r="BW24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>297346.19074020558</v>
       </c>
       <c r="BX24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>311667.02310002246</v>
       </c>
       <c r="BY24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>325435.62727924663</v>
       </c>
       <c r="BZ24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>339627.47456945502</v>
       </c>
       <c r="CA24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>354452.12186362606</v>
       </c>
       <c r="CB24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>369938.37009722309</v>
       </c>
       <c r="CC24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>386116.35513900348</v>
       </c>
       <c r="CD24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>403017.61064001609</v>
       </c>
       <c r="CE24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="68"/>
         <v>420675.13388028671</v>
       </c>
     </row>
@@ -5166,15 +5208,15 @@
         <v>8516.0400000000009</v>
       </c>
       <c r="AJ25" s="2">
-        <f t="shared" ref="AJ25:AJ26" si="74">+AF25*1.03</f>
+        <f t="shared" ref="AJ25:AJ26" si="69">+AF25*1.03</f>
         <v>8806.5</v>
       </c>
       <c r="AK25" s="2">
-        <f t="shared" ref="AK25:AK26" si="75">+AG25*1.03</f>
+        <f t="shared" ref="AK25:AK26" si="70">+AG25*1.03</f>
         <v>9131.98</v>
       </c>
       <c r="AL25" s="2">
-        <f t="shared" ref="AL25:AL26" si="76">+AH25*1.03</f>
+        <f t="shared" ref="AL25:AL26" si="71">+AH25*1.03</f>
         <v>9131.98</v>
       </c>
       <c r="AQ25" s="2">
@@ -5242,11 +5284,11 @@
         <v>18752</v>
       </c>
       <c r="BL25" s="7">
-        <f t="shared" ref="BL25:BL26" si="77">SUM(O25:R25)</f>
+        <f t="shared" ref="BL25:BL26" si="72">SUM(O25:R25)</f>
         <v>21914</v>
       </c>
       <c r="BM25" s="7">
-        <f t="shared" ref="BM25:BM26" si="78">SUM(S25:V25)</f>
+        <f t="shared" ref="BM25:BM26" si="73">SUM(S25:V25)</f>
         <v>26251</v>
       </c>
       <c r="BN25" s="2">
@@ -5254,71 +5296,71 @@
         <v>29915</v>
       </c>
       <c r="BO25" s="2">
-        <f t="shared" ref="BO25:BO26" si="79">SUM(AA25:AD25)</f>
+        <f t="shared" ref="BO25:BO26" si="74">SUM(AA25:AD25)</f>
         <v>31370</v>
       </c>
       <c r="BP25" s="2">
-        <f t="shared" ref="BP25:CE25" si="80">+BO25*1.03</f>
+        <f t="shared" ref="BP25:CE25" si="75">+BO25*1.03</f>
         <v>32311.100000000002</v>
       </c>
       <c r="BQ25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>33280.433000000005</v>
       </c>
       <c r="BR25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>34278.845990000009</v>
       </c>
       <c r="BS25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>35307.21136970001</v>
       </c>
       <c r="BT25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>36366.427710791009</v>
       </c>
       <c r="BU25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>37457.420542114742</v>
       </c>
       <c r="BV25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>38581.143158378181</v>
       </c>
       <c r="BW25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>39738.577453129525</v>
       </c>
       <c r="BX25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>40930.73477672341</v>
       </c>
       <c r="BY25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>42158.656820025113</v>
       </c>
       <c r="BZ25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>43423.416524625871</v>
       </c>
       <c r="CA25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>44726.119020364647</v>
       </c>
       <c r="CB25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>46067.902590975587</v>
       </c>
       <c r="CC25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>47449.939668704857</v>
       </c>
       <c r="CD25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>48873.437858766003</v>
       </c>
       <c r="CE25" s="2">
-        <f t="shared" si="80"/>
+        <f t="shared" si="75"/>
         <v>50339.640994528985</v>
       </c>
     </row>
@@ -5412,19 +5454,19 @@
         <v>7048</v>
       </c>
       <c r="AI26" s="2">
-        <f t="shared" ref="AI26" si="81">+AE26*1.03</f>
+        <f t="shared" ref="AI26" si="76">+AE26*1.03</f>
         <v>7390.25</v>
       </c>
       <c r="AJ26" s="2">
-        <f t="shared" si="74"/>
+        <f t="shared" si="69"/>
         <v>6929.84</v>
       </c>
       <c r="AK26" s="2">
-        <f t="shared" si="75"/>
+        <f t="shared" si="70"/>
         <v>6849.5</v>
       </c>
       <c r="AL26" s="2">
-        <f t="shared" si="76"/>
+        <f t="shared" si="71"/>
         <v>7259.4400000000005</v>
       </c>
       <c r="AQ26" s="2">
@@ -5492,11 +5534,11 @@
         <v>19916</v>
       </c>
       <c r="BL26" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="72"/>
         <v>21973</v>
       </c>
       <c r="BM26" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="73"/>
         <v>25094</v>
       </c>
       <c r="BN26" s="2">
@@ -5504,71 +5546,71 @@
         <v>24932</v>
       </c>
       <c r="BO26" s="2">
-        <f t="shared" si="79"/>
+        <f t="shared" si="74"/>
         <v>26097</v>
       </c>
       <c r="BP26" s="2">
-        <f t="shared" ref="BP26:CE26" si="82">+BO26*1.03</f>
+        <f t="shared" ref="BP26:CE26" si="77">+BO26*1.03</f>
         <v>26879.91</v>
       </c>
       <c r="BQ26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>27686.3073</v>
       </c>
       <c r="BR26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>28516.896519000002</v>
       </c>
       <c r="BS26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>29372.403414570002</v>
       </c>
       <c r="BT26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>30253.575517007102</v>
       </c>
       <c r="BU26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>31161.182782517317</v>
       </c>
       <c r="BV26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>32096.018265992836</v>
       </c>
       <c r="BW26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>33058.898813972621</v>
       </c>
       <c r="BX26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>34050.665778391798</v>
       </c>
       <c r="BY26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>35072.185751743556</v>
       </c>
       <c r="BZ26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>36124.351324295865</v>
       </c>
       <c r="CA26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>37208.081864024745</v>
       </c>
       <c r="CB26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>38324.324319945488</v>
       </c>
       <c r="CC26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>39474.054049543854</v>
       </c>
       <c r="CD26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>40658.275671030169</v>
       </c>
       <c r="CE26" s="2">
-        <f t="shared" si="82"/>
+        <f t="shared" si="77"/>
         <v>41878.023941161075</v>
       </c>
     </row>
@@ -5577,35 +5619,35 @@
         <v>28</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" ref="C27" si="83">+C25+C26</f>
+        <f t="shared" ref="C27" si="78">+C25+C26</f>
         <v>7638</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" ref="D27:F27" si="84">+D25+D26</f>
+        <f t="shared" ref="D27:F27" si="79">+D25+D26</f>
         <v>7528</v>
       </c>
       <c r="E27" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>7809</v>
       </c>
       <c r="F27" s="2">
-        <f t="shared" si="84"/>
+        <f t="shared" si="79"/>
         <v>7966</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" ref="K27:N27" si="85">+K25+K26</f>
+        <f t="shared" ref="K27:N27" si="80">+K25+K26</f>
         <v>9648</v>
       </c>
       <c r="L27" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>9517</v>
       </c>
       <c r="M27" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>9589</v>
       </c>
       <c r="N27" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="80"/>
         <v>9914</v>
       </c>
       <c r="O27" s="2">
@@ -5621,11 +5663,11 @@
         <v>11129</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" ref="R27" si="86">+R25+R26</f>
+        <f t="shared" ref="R27" si="81">+R25+R26</f>
         <v>11388</v>
       </c>
       <c r="S27" s="2">
-        <f t="shared" ref="S27" si="87">+S25+S26</f>
+        <f t="shared" ref="S27" si="82">+S25+S26</f>
         <v>12755</v>
       </c>
       <c r="T27" s="2">
@@ -5633,155 +5675,155 @@
         <v>12580</v>
       </c>
       <c r="U27" s="2">
-        <f t="shared" ref="U27" si="88">+U25+U26</f>
+        <f t="shared" ref="U27" si="83">+U25+U26</f>
         <v>12809</v>
       </c>
       <c r="V27" s="2">
-        <f t="shared" ref="V27:Z27" si="89">+V25+V26</f>
+        <f t="shared" ref="V27:Z27" si="84">+V25+V26</f>
         <v>13201</v>
       </c>
       <c r="W27" s="2">
+        <f t="shared" si="84"/>
+        <v>14316</v>
+      </c>
+      <c r="X27" s="2">
+        <f t="shared" si="84"/>
+        <v>13658</v>
+      </c>
+      <c r="Y27" s="2">
+        <f t="shared" si="84"/>
+        <v>13415</v>
+      </c>
+      <c r="Z27" s="2">
+        <f t="shared" si="84"/>
+        <v>13458</v>
+      </c>
+      <c r="AA27" s="2">
+        <f t="shared" ref="AA27:AB27" si="85">+AA25+AA26</f>
+        <v>14482</v>
+      </c>
+      <c r="AB27" s="2">
+        <f t="shared" si="85"/>
+        <v>14371</v>
+      </c>
+      <c r="AC27" s="2">
+        <f t="shared" ref="AC27:AD27" si="86">+AC25+AC26</f>
+        <v>14326</v>
+      </c>
+      <c r="AD27" s="2">
+        <f t="shared" si="86"/>
+        <v>14288</v>
+      </c>
+      <c r="AE27" s="2">
+        <f t="shared" ref="AE27:AH27" si="87">+AE25+AE26</f>
+        <v>15443</v>
+      </c>
+      <c r="AF27" s="2">
+        <f t="shared" si="87"/>
+        <v>15278</v>
+      </c>
+      <c r="AG27" s="2">
+        <f t="shared" si="87"/>
+        <v>15516</v>
+      </c>
+      <c r="AH27" s="2">
+        <f t="shared" si="87"/>
+        <v>15914</v>
+      </c>
+      <c r="AI27" s="2">
+        <f t="shared" ref="AI27:AL27" si="88">+AI25+AI26</f>
+        <v>15906.29</v>
+      </c>
+      <c r="AJ27" s="2">
+        <f t="shared" si="88"/>
+        <v>15736.34</v>
+      </c>
+      <c r="AK27" s="2">
+        <f t="shared" si="88"/>
+        <v>15981.48</v>
+      </c>
+      <c r="AL27" s="2">
+        <f t="shared" si="88"/>
+        <v>16391.419999999998</v>
+      </c>
+      <c r="AQ27" s="2">
+        <f t="shared" ref="AQ27:AR27" si="89">+AQ25+AQ26</f>
+        <v>1546</v>
+      </c>
+      <c r="AR27" s="2">
         <f t="shared" si="89"/>
-        <v>14316</v>
-      </c>
-      <c r="X27" s="2">
-        <f t="shared" si="89"/>
-        <v>13658</v>
-      </c>
-      <c r="Y27" s="2">
-        <f t="shared" si="89"/>
-        <v>13415</v>
-      </c>
-      <c r="Z27" s="2">
-        <f t="shared" si="89"/>
-        <v>13458</v>
-      </c>
-      <c r="AA27" s="2">
-        <f t="shared" ref="AA27:AB27" si="90">+AA25+AA26</f>
-        <v>14482</v>
-      </c>
-      <c r="AB27" s="2">
+        <v>1568</v>
+      </c>
+      <c r="AS27" s="2">
+        <f t="shared" ref="AS27:AU27" si="90">+AS25+AS26</f>
+        <v>1555</v>
+      </c>
+      <c r="AT27" s="2">
         <f t="shared" si="90"/>
-        <v>14371</v>
-      </c>
-      <c r="AC27" s="2">
-        <f t="shared" ref="AC27:AD27" si="91">+AC25+AC26</f>
-        <v>14326</v>
-      </c>
-      <c r="AD27" s="2">
+        <v>1683</v>
+      </c>
+      <c r="AU27" s="2">
+        <f t="shared" si="90"/>
+        <v>1910</v>
+      </c>
+      <c r="AV27" s="2">
+        <f t="shared" ref="AV27:AW27" si="91">+AV25+AV26</f>
+        <v>2393</v>
+      </c>
+      <c r="AW27" s="2">
         <f t="shared" si="91"/>
-        <v>14288</v>
-      </c>
-      <c r="AE27" s="2">
-        <f t="shared" ref="AE27:AH27" si="92">+AE25+AE26</f>
-        <v>15443</v>
-      </c>
-      <c r="AF27" s="2">
+        <v>3145</v>
+      </c>
+      <c r="AX27" s="2">
+        <f t="shared" ref="AX27:AY27" si="92">+AX25+AX26</f>
+        <v>3745</v>
+      </c>
+      <c r="AY27" s="2">
         <f t="shared" si="92"/>
-        <v>15278</v>
-      </c>
-      <c r="AG27" s="2">
-        <f t="shared" si="92"/>
-        <v>15516</v>
-      </c>
-      <c r="AH27" s="2">
-        <f t="shared" si="92"/>
-        <v>15914</v>
-      </c>
-      <c r="AI27" s="2">
-        <f t="shared" ref="AI27:AL27" si="93">+AI25+AI26</f>
-        <v>15906.29</v>
-      </c>
-      <c r="AJ27" s="2">
+        <v>4870</v>
+      </c>
+      <c r="AZ27" s="2">
+        <f t="shared" ref="AZ27:BB27" si="93">+AZ25+AZ26</f>
+        <v>5482</v>
+      </c>
+      <c r="BA27" s="2">
         <f t="shared" si="93"/>
-        <v>15736.34</v>
-      </c>
-      <c r="AK27" s="2">
+        <v>7299</v>
+      </c>
+      <c r="BB27" s="2">
         <f t="shared" si="93"/>
-        <v>15981.48</v>
-      </c>
-      <c r="AL27" s="2">
-        <f t="shared" si="93"/>
-        <v>16391.419999999998</v>
-      </c>
-      <c r="AQ27" s="2">
-        <f t="shared" ref="AQ27:AR27" si="94">+AQ25+AQ26</f>
-        <v>1546</v>
-      </c>
-      <c r="AR27" s="2">
+        <v>10028</v>
+      </c>
+      <c r="BC27" s="2">
+        <f t="shared" ref="BC27:BH27" si="94">+BC25+BC26</f>
+        <v>13421</v>
+      </c>
+      <c r="BD27" s="2">
         <f t="shared" si="94"/>
-        <v>1568</v>
-      </c>
-      <c r="AS27" s="2">
-        <f t="shared" ref="AS27:AU27" si="95">+AS25+AS26</f>
-        <v>1555</v>
-      </c>
-      <c r="AT27" s="2">
+        <v>15305</v>
+      </c>
+      <c r="BE27" s="2">
+        <f t="shared" si="94"/>
+        <v>18034</v>
+      </c>
+      <c r="BF27" s="2">
+        <f t="shared" si="94"/>
+        <v>22396</v>
+      </c>
+      <c r="BG27" s="2">
+        <f t="shared" si="94"/>
+        <v>24239</v>
+      </c>
+      <c r="BH27" s="2">
+        <f t="shared" si="94"/>
+        <v>26842</v>
+      </c>
+      <c r="BI27" s="2">
+        <f t="shared" ref="BI27:BJ27" si="95">+BI25+BI26</f>
+        <v>30941</v>
+      </c>
+      <c r="BJ27" s="2">
         <f t="shared" si="95"/>
-        <v>1683</v>
-      </c>
-      <c r="AU27" s="2">
-        <f t="shared" si="95"/>
-        <v>1910</v>
-      </c>
-      <c r="AV27" s="2">
-        <f t="shared" ref="AV27:AW27" si="96">+AV25+AV26</f>
-        <v>2393</v>
-      </c>
-      <c r="AW27" s="2">
-        <f t="shared" si="96"/>
-        <v>3145</v>
-      </c>
-      <c r="AX27" s="2">
-        <f t="shared" ref="AX27:AY27" si="97">+AX25+AX26</f>
-        <v>3745</v>
-      </c>
-      <c r="AY27" s="2">
-        <f t="shared" si="97"/>
-        <v>4870</v>
-      </c>
-      <c r="AZ27" s="2">
-        <f t="shared" ref="AZ27:BB27" si="98">+AZ25+AZ26</f>
-        <v>5482</v>
-      </c>
-      <c r="BA27" s="2">
-        <f t="shared" si="98"/>
-        <v>7299</v>
-      </c>
-      <c r="BB27" s="2">
-        <f t="shared" si="98"/>
-        <v>10028</v>
-      </c>
-      <c r="BC27" s="2">
-        <f t="shared" ref="BC27:BH27" si="99">+BC25+BC26</f>
-        <v>13421</v>
-      </c>
-      <c r="BD27" s="2">
-        <f t="shared" si="99"/>
-        <v>15305</v>
-      </c>
-      <c r="BE27" s="2">
-        <f t="shared" si="99"/>
-        <v>18034</v>
-      </c>
-      <c r="BF27" s="2">
-        <f t="shared" si="99"/>
-        <v>22396</v>
-      </c>
-      <c r="BG27" s="2">
-        <f t="shared" si="99"/>
-        <v>24239</v>
-      </c>
-      <c r="BH27" s="2">
-        <f t="shared" si="99"/>
-        <v>26842</v>
-      </c>
-      <c r="BI27" s="2">
-        <f t="shared" ref="BI27:BJ27" si="100">+BI25+BI26</f>
-        <v>30941</v>
-      </c>
-      <c r="BJ27" s="2">
-        <f t="shared" si="100"/>
         <v>34462</v>
       </c>
       <c r="BK27" s="2">
@@ -5797,75 +5839,75 @@
         <v>51345</v>
       </c>
       <c r="BN27" s="2">
-        <f t="shared" ref="BN27:CE27" si="101">+BN25+BN26</f>
+        <f t="shared" ref="BN27:CE27" si="96">+BN25+BN26</f>
         <v>54847</v>
       </c>
       <c r="BO27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>57467</v>
       </c>
       <c r="BP27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>59191.01</v>
       </c>
       <c r="BQ27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>60966.740300000005</v>
       </c>
       <c r="BR27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>62795.742509000011</v>
       </c>
       <c r="BS27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>64679.614784270016</v>
       </c>
       <c r="BT27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>66620.003227798108</v>
       </c>
       <c r="BU27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>68618.603324632059</v>
       </c>
       <c r="BV27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>70677.161424371021</v>
       </c>
       <c r="BW27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>72797.476267102145</v>
       </c>
       <c r="BX27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>74981.400555115208</v>
       </c>
       <c r="BY27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>77230.842571768677</v>
       </c>
       <c r="BZ27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>79547.767848921736</v>
       </c>
       <c r="CA27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>81934.2008843894</v>
       </c>
       <c r="CB27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>84392.226910921076</v>
       </c>
       <c r="CC27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>86923.993718248705</v>
       </c>
       <c r="CD27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>89531.713529796165</v>
       </c>
       <c r="CE27" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="96"/>
         <v>92217.66493569006</v>
       </c>
     </row>
@@ -5874,35 +5916,35 @@
         <v>29</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" ref="C28" si="102">+C24-C27</f>
+        <f t="shared" ref="C28" si="97">+C24-C27</f>
         <v>26274</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" ref="D28:F28" si="103">+D24-D27</f>
+        <f t="shared" ref="D28:F28" si="98">+D24-D27</f>
         <v>15894</v>
       </c>
       <c r="E28" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="98"/>
         <v>12612</v>
       </c>
       <c r="F28" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="98"/>
         <v>16118</v>
       </c>
       <c r="K28" s="2">
-        <f t="shared" ref="K28:N28" si="104">+K24-K27</f>
+        <f t="shared" ref="K28:N28" si="99">+K24-K27</f>
         <v>25569</v>
       </c>
       <c r="L28" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="99"/>
         <v>12853</v>
       </c>
       <c r="M28" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="99"/>
         <v>13091</v>
       </c>
       <c r="N28" s="2">
-        <f t="shared" si="104"/>
+        <f t="shared" si="99"/>
         <v>14775</v>
       </c>
       <c r="O28" s="2">
@@ -5918,11 +5960,11 @@
         <v>24126</v>
       </c>
       <c r="R28" s="2">
-        <f t="shared" ref="R28" si="105">+R24-R27</f>
+        <f t="shared" ref="R28" si="100">+R24-R27</f>
         <v>23786</v>
       </c>
       <c r="S28" s="2">
-        <f t="shared" ref="S28" si="106">+S24-S27</f>
+        <f t="shared" ref="S28" si="101">+S24-S27</f>
         <v>41488</v>
       </c>
       <c r="T28" s="2">
@@ -5930,155 +5972,155 @@
         <v>29979</v>
       </c>
       <c r="U28" s="2">
-        <f t="shared" ref="U28" si="107">+U24-U27</f>
+        <f t="shared" ref="U28" si="102">+U24-U27</f>
         <v>23076</v>
       </c>
       <c r="V28" s="2">
-        <f t="shared" ref="V28:Z28" si="108">+V24-V27</f>
+        <f t="shared" ref="V28:Z28" si="103">+V24-V27</f>
         <v>24894</v>
       </c>
       <c r="W28" s="2">
+        <f t="shared" si="103"/>
+        <v>36016</v>
+      </c>
+      <c r="X28" s="2">
+        <f t="shared" si="103"/>
+        <v>28318</v>
+      </c>
+      <c r="Y28" s="2">
+        <f t="shared" si="103"/>
+        <v>22998</v>
+      </c>
+      <c r="Z28" s="2">
+        <f t="shared" si="103"/>
+        <v>26969</v>
+      </c>
+      <c r="AA28" s="2">
+        <f t="shared" ref="AA28:AB28" si="104">+AA24-AA27</f>
+        <v>40373</v>
+      </c>
+      <c r="AB28" s="2">
+        <f t="shared" si="104"/>
+        <v>27900</v>
+      </c>
+      <c r="AC28" s="2">
+        <f t="shared" ref="AC28:AD28" si="105">+AC24-AC27</f>
+        <v>25352</v>
+      </c>
+      <c r="AD28" s="2">
+        <f t="shared" si="105"/>
+        <v>29591</v>
+      </c>
+      <c r="AE28" s="2">
+        <f t="shared" ref="AE28:AH28" si="106">+AE24-AE27</f>
+        <v>42832</v>
+      </c>
+      <c r="AF28" s="2">
+        <f t="shared" si="106"/>
+        <v>29589</v>
+      </c>
+      <c r="AG28" s="2">
+        <f t="shared" si="106"/>
+        <v>28202</v>
+      </c>
+      <c r="AH28" s="2">
+        <f t="shared" si="106"/>
+        <v>32427</v>
+      </c>
+      <c r="AI28" s="2">
+        <f t="shared" ref="AI28:AL28" si="107">+AI24-AI27</f>
+        <v>51659.029999999992</v>
+      </c>
+      <c r="AJ28" s="2">
+        <f t="shared" si="107"/>
+        <v>36520.14</v>
+      </c>
+      <c r="AK28" s="2">
+        <f t="shared" si="107"/>
+        <v>35444.509999999995</v>
+      </c>
+      <c r="AL28" s="2">
+        <f t="shared" si="107"/>
+        <v>32789.690199999997</v>
+      </c>
+      <c r="AQ28" s="2">
+        <f t="shared" ref="AQ28:AR28" si="108">+AQ24-AQ27</f>
+        <v>620</v>
+      </c>
+      <c r="AR28" s="2">
         <f t="shared" si="108"/>
-        <v>36016</v>
-      </c>
-      <c r="X28" s="2">
-        <f t="shared" si="108"/>
-        <v>28318</v>
-      </c>
-      <c r="Y28" s="2">
-        <f t="shared" si="108"/>
-        <v>22998</v>
-      </c>
-      <c r="Z28" s="2">
-        <f t="shared" si="108"/>
-        <v>26969</v>
-      </c>
-      <c r="AA28" s="2">
-        <f t="shared" ref="AA28:AB28" si="109">+AA24-AA27</f>
-        <v>40373</v>
-      </c>
-      <c r="AB28" s="2">
+        <v>-333</v>
+      </c>
+      <c r="AS28" s="2">
+        <f t="shared" ref="AS28:AU28" si="109">+AS24-AS27</f>
+        <v>48</v>
+      </c>
+      <c r="AT28" s="2">
         <f t="shared" si="109"/>
-        <v>27900</v>
-      </c>
-      <c r="AC28" s="2">
-        <f t="shared" ref="AC28:AD28" si="110">+AC24-AC27</f>
-        <v>25352</v>
-      </c>
-      <c r="AD28" s="2">
+        <v>25</v>
+      </c>
+      <c r="AU28" s="2">
+        <f t="shared" si="109"/>
+        <v>349</v>
+      </c>
+      <c r="AV28" s="2">
+        <f t="shared" ref="AV28:AW28" si="110">+AV24-AV27</f>
+        <v>1650</v>
+      </c>
+      <c r="AW28" s="2">
         <f t="shared" si="110"/>
-        <v>29591</v>
-      </c>
-      <c r="AE28" s="2">
-        <f t="shared" ref="AE28:AH28" si="111">+AE24-AE27</f>
-        <v>42832</v>
-      </c>
-      <c r="AF28" s="2">
+        <v>2453</v>
+      </c>
+      <c r="AX28" s="2">
+        <f t="shared" ref="AX28:AY28" si="111">+AX24-AX27</f>
+        <v>4409</v>
+      </c>
+      <c r="AY28" s="2">
         <f t="shared" si="111"/>
-        <v>29589</v>
-      </c>
-      <c r="AG28" s="2">
-        <f t="shared" si="111"/>
-        <v>28202</v>
-      </c>
-      <c r="AH28" s="2">
-        <f t="shared" si="111"/>
-        <v>32427</v>
-      </c>
-      <c r="AI28" s="2">
-        <f t="shared" ref="AI28:AL28" si="112">+AI24-AI27</f>
-        <v>43594.112000000001</v>
-      </c>
-      <c r="AJ28" s="2">
+        <v>8327</v>
+      </c>
+      <c r="AZ28" s="2">
+        <f t="shared" ref="AZ28:BB28" si="112">+AZ24-AZ27</f>
+        <v>11740</v>
+      </c>
+      <c r="BA28" s="2">
         <f t="shared" si="112"/>
-        <v>30031.5033</v>
-      </c>
-      <c r="AK28" s="2">
+        <v>18385</v>
+      </c>
+      <c r="BB28" s="2">
         <f t="shared" si="112"/>
-        <v>29172.961599999999</v>
-      </c>
-      <c r="AL28" s="2">
-        <f t="shared" si="112"/>
-        <v>32789.690199999997</v>
-      </c>
-      <c r="AQ28" s="2">
-        <f t="shared" ref="AQ28:AR28" si="113">+AQ24-AQ27</f>
-        <v>620</v>
-      </c>
-      <c r="AR28" s="2">
+        <v>33790</v>
+      </c>
+      <c r="BC28" s="2">
+        <f t="shared" ref="BC28:BH28" si="113">+BC24-BC27</f>
+        <v>55241</v>
+      </c>
+      <c r="BD28" s="2">
         <f t="shared" si="113"/>
-        <v>-333</v>
-      </c>
-      <c r="AS28" s="2">
-        <f t="shared" ref="AS28:AU28" si="114">+AS24-AS27</f>
-        <v>48</v>
-      </c>
-      <c r="AT28" s="2">
+        <v>48999</v>
+      </c>
+      <c r="BE28" s="2">
+        <f t="shared" si="113"/>
+        <v>52503</v>
+      </c>
+      <c r="BF28" s="2">
+        <f t="shared" si="113"/>
+        <v>71230</v>
+      </c>
+      <c r="BG28" s="2">
+        <f t="shared" si="113"/>
+        <v>60024</v>
+      </c>
+      <c r="BH28" s="2">
+        <f t="shared" si="113"/>
+        <v>61344</v>
+      </c>
+      <c r="BI28" s="2">
+        <f t="shared" ref="BI28:BJ28" si="114">+BI24-BI27</f>
+        <v>70898</v>
+      </c>
+      <c r="BJ28" s="2">
         <f t="shared" si="114"/>
-        <v>25</v>
-      </c>
-      <c r="AU28" s="2">
-        <f t="shared" si="114"/>
-        <v>349</v>
-      </c>
-      <c r="AV28" s="2">
-        <f t="shared" ref="AV28:AW28" si="115">+AV24-AV27</f>
-        <v>1650</v>
-      </c>
-      <c r="AW28" s="2">
-        <f t="shared" si="115"/>
-        <v>2453</v>
-      </c>
-      <c r="AX28" s="2">
-        <f t="shared" ref="AX28:AY28" si="116">+AX24-AX27</f>
-        <v>4409</v>
-      </c>
-      <c r="AY28" s="2">
-        <f t="shared" si="116"/>
-        <v>8327</v>
-      </c>
-      <c r="AZ28" s="2">
-        <f t="shared" ref="AZ28:BB28" si="117">+AZ24-AZ27</f>
-        <v>11740</v>
-      </c>
-      <c r="BA28" s="2">
-        <f t="shared" si="117"/>
-        <v>18385</v>
-      </c>
-      <c r="BB28" s="2">
-        <f t="shared" si="117"/>
-        <v>33790</v>
-      </c>
-      <c r="BC28" s="2">
-        <f t="shared" ref="BC28:BH28" si="118">+BC24-BC27</f>
-        <v>55241</v>
-      </c>
-      <c r="BD28" s="2">
-        <f t="shared" si="118"/>
-        <v>48999</v>
-      </c>
-      <c r="BE28" s="2">
-        <f t="shared" si="118"/>
-        <v>52503</v>
-      </c>
-      <c r="BF28" s="2">
-        <f t="shared" si="118"/>
-        <v>71230</v>
-      </c>
-      <c r="BG28" s="2">
-        <f t="shared" si="118"/>
-        <v>60024</v>
-      </c>
-      <c r="BH28" s="2">
-        <f t="shared" si="118"/>
-        <v>61344</v>
-      </c>
-      <c r="BI28" s="2">
-        <f t="shared" ref="BI28:BJ28" si="119">+BI24-BI27</f>
-        <v>70898</v>
-      </c>
-      <c r="BJ28" s="2">
-        <f t="shared" si="119"/>
         <v>63930</v>
       </c>
       <c r="BK28" s="2">
@@ -6094,75 +6136,75 @@
         <v>119437</v>
       </c>
       <c r="BN28" s="2">
-        <f t="shared" ref="BN28:CE28" si="120">+BN24-BN27</f>
+        <f t="shared" ref="BN28:CE28" si="115">+BN24-BN27</f>
         <v>114301</v>
       </c>
       <c r="BO28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>123216</v>
       </c>
       <c r="BP28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>139063.61999429748</v>
       </c>
       <c r="BQ28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>151775.11280931855</v>
       </c>
       <c r="BR28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>165598.87969255034</v>
       </c>
       <c r="BS28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>180634.46636454249</v>
       </c>
       <c r="BT28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>191617.78812544863</v>
       </c>
       <c r="BU28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>202043.13562531775</v>
       </c>
       <c r="BV28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>213010.89772704628</v>
       </c>
       <c r="BW28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>224548.71447310344</v>
       </c>
       <c r="BX28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>236685.62254490727</v>
       </c>
       <c r="BY28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>248204.78470747796</v>
       </c>
       <c r="BZ28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>260079.70672053329</v>
       </c>
       <c r="CA28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>272517.92097923666</v>
       </c>
       <c r="CB28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>285546.14318630204</v>
       </c>
       <c r="CC28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>299192.36142075481</v>
       </c>
       <c r="CD28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>313485.89711021993</v>
       </c>
       <c r="CE28" s="2">
-        <f t="shared" si="120"/>
+        <f t="shared" si="115"/>
         <v>328457.46894459665</v>
       </c>
     </row>
@@ -6320,11 +6362,11 @@
         <v>803</v>
       </c>
       <c r="BL29" s="7">
-        <f t="shared" ref="BL29" si="121">SUM(O29:R29)</f>
+        <f t="shared" ref="BL29" si="116">SUM(O29:R29)</f>
         <v>258</v>
       </c>
       <c r="BM29" s="7">
-        <f t="shared" ref="BM29" si="122">SUM(S29:V29)</f>
+        <f t="shared" ref="BM29" si="117">SUM(S29:V29)</f>
         <v>-334</v>
       </c>
       <c r="BN29" s="2">
@@ -6332,7 +6374,7 @@
         <v>-565</v>
       </c>
       <c r="BO29" s="2">
-        <f t="shared" ref="BO29:BO31" si="123">SUM(AA29:AD29)</f>
+        <f t="shared" ref="BO29:BO31" si="118">SUM(AA29:AD29)</f>
         <v>269</v>
       </c>
     </row>
@@ -6341,35 +6383,35 @@
         <v>34</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" ref="C30" si="124">+C28+C29</f>
+        <f t="shared" ref="C30" si="119">+C28+C29</f>
         <v>27030</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" ref="D30:F30" si="125">+D28+D29</f>
+        <f t="shared" ref="D30:F30" si="120">+D28+D29</f>
         <v>16168</v>
       </c>
       <c r="E30" s="2">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>13284</v>
       </c>
       <c r="F30" s="2">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>16421</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" ref="K30:N30" si="126">+K28+K29</f>
+        <f t="shared" ref="K30:N30" si="121">+K28+K29</f>
         <v>25918</v>
       </c>
       <c r="L30" s="2">
-        <f t="shared" si="126"/>
+        <f t="shared" si="121"/>
         <v>13135</v>
       </c>
       <c r="M30" s="2">
-        <f t="shared" si="126"/>
+        <f t="shared" si="121"/>
         <v>13137</v>
       </c>
       <c r="N30" s="2">
-        <f t="shared" si="126"/>
+        <f t="shared" si="121"/>
         <v>14901</v>
       </c>
       <c r="O30" s="2">
@@ -6385,11 +6427,11 @@
         <v>24369</v>
       </c>
       <c r="R30" s="2">
-        <f t="shared" ref="R30" si="127">+R28+R29</f>
+        <f t="shared" ref="R30" si="122">+R28+R29</f>
         <v>23248</v>
       </c>
       <c r="S30" s="2">
-        <f t="shared" ref="S30" si="128">+S28+S29</f>
+        <f t="shared" ref="S30" si="123">+S28+S29</f>
         <v>41241</v>
       </c>
       <c r="T30" s="2">
@@ -6397,155 +6439,155 @@
         <v>30139</v>
       </c>
       <c r="U30" s="2">
-        <f t="shared" ref="U30:Z30" si="129">+U28+U29</f>
+        <f t="shared" ref="U30:Z30" si="124">+U28+U29</f>
         <v>23066</v>
       </c>
       <c r="V30" s="2">
+        <f t="shared" si="124"/>
+        <v>24657</v>
+      </c>
+      <c r="W30" s="2">
+        <f t="shared" si="124"/>
+        <v>35623</v>
+      </c>
+      <c r="X30" s="2">
+        <f t="shared" si="124"/>
+        <v>28382</v>
+      </c>
+      <c r="Y30" s="2">
+        <f t="shared" si="124"/>
+        <v>22733</v>
+      </c>
+      <c r="Z30" s="2">
+        <f t="shared" si="124"/>
+        <v>26998</v>
+      </c>
+      <c r="AA30" s="2">
+        <f t="shared" ref="AA30:AB30" si="125">+AA28+AA29</f>
+        <v>40323</v>
+      </c>
+      <c r="AB30" s="2">
+        <f t="shared" si="125"/>
+        <v>28058</v>
+      </c>
+      <c r="AC30" s="2">
+        <f t="shared" ref="AC30:AD30" si="126">+AC28+AC29</f>
+        <v>25494</v>
+      </c>
+      <c r="AD30" s="2">
+        <f t="shared" si="126"/>
+        <v>29610</v>
+      </c>
+      <c r="AE30" s="2">
+        <f t="shared" ref="AE30:AH30" si="127">+AE28+AE29</f>
+        <v>42584</v>
+      </c>
+      <c r="AF30" s="2">
+        <f t="shared" si="127"/>
+        <v>29310</v>
+      </c>
+      <c r="AG30" s="2">
+        <f t="shared" si="127"/>
+        <v>28031</v>
+      </c>
+      <c r="AH30" s="2">
+        <f t="shared" si="127"/>
+        <v>32804</v>
+      </c>
+      <c r="AI30" s="2">
+        <f t="shared" ref="AI30:AL30" si="128">+AI28+AI29</f>
+        <v>51659.029999999992</v>
+      </c>
+      <c r="AJ30" s="2">
+        <f t="shared" si="128"/>
+        <v>36520.14</v>
+      </c>
+      <c r="AK30" s="2">
+        <f t="shared" si="128"/>
+        <v>35444.509999999995</v>
+      </c>
+      <c r="AL30" s="2">
+        <f t="shared" si="128"/>
+        <v>32789.690199999997</v>
+      </c>
+      <c r="AQ30" s="2">
+        <f t="shared" ref="AQ30:AR30" si="129">+AQ28+AQ29</f>
+        <v>823</v>
+      </c>
+      <c r="AR30" s="2">
         <f t="shared" si="129"/>
-        <v>24657</v>
-      </c>
-      <c r="W30" s="2">
-        <f t="shared" si="129"/>
-        <v>35623</v>
-      </c>
-      <c r="X30" s="2">
-        <f t="shared" si="129"/>
-        <v>28382</v>
-      </c>
-      <c r="Y30" s="2">
-        <f t="shared" si="129"/>
-        <v>22733</v>
-      </c>
-      <c r="Z30" s="2">
-        <f t="shared" si="129"/>
-        <v>26998</v>
-      </c>
-      <c r="AA30" s="2">
-        <f t="shared" ref="AA30:AB30" si="130">+AA28+AA29</f>
-        <v>40323</v>
-      </c>
-      <c r="AB30" s="2">
+        <v>-116</v>
+      </c>
+      <c r="AS30" s="2">
+        <f t="shared" ref="AS30:AU30" si="130">+AS28+AS29</f>
+        <v>118</v>
+      </c>
+      <c r="AT30" s="2">
         <f t="shared" si="130"/>
-        <v>28058</v>
-      </c>
-      <c r="AC30" s="2">
-        <f t="shared" ref="AC30:AD30" si="131">+AC28+AC29</f>
-        <v>25494</v>
-      </c>
-      <c r="AD30" s="2">
+        <v>118</v>
+      </c>
+      <c r="AU30" s="2">
+        <f t="shared" si="130"/>
+        <v>406</v>
+      </c>
+      <c r="AV30" s="2">
+        <f t="shared" ref="AV30:AW30" si="131">+AV28+AV29</f>
+        <v>1815</v>
+      </c>
+      <c r="AW30" s="2">
         <f t="shared" si="131"/>
-        <v>29610</v>
-      </c>
-      <c r="AE30" s="2">
-        <f t="shared" ref="AE30:AH30" si="132">+AE28+AE29</f>
-        <v>42584</v>
-      </c>
-      <c r="AF30" s="2">
+        <v>2818</v>
+      </c>
+      <c r="AX30" s="2">
+        <f t="shared" ref="AX30:AY30" si="132">+AX28+AX29</f>
+        <v>5008</v>
+      </c>
+      <c r="AY30" s="2">
         <f t="shared" si="132"/>
-        <v>29310</v>
-      </c>
-      <c r="AG30" s="2">
-        <f t="shared" si="132"/>
-        <v>28031</v>
-      </c>
-      <c r="AH30" s="2">
-        <f t="shared" si="132"/>
-        <v>32804</v>
-      </c>
-      <c r="AI30" s="2">
-        <f t="shared" ref="AI30:AL30" si="133">+AI28+AI29</f>
-        <v>43594.112000000001</v>
-      </c>
-      <c r="AJ30" s="2">
+        <v>8947</v>
+      </c>
+      <c r="AZ30" s="2">
+        <f t="shared" ref="AZ30:BB30" si="133">+AZ28+AZ29</f>
+        <v>12066</v>
+      </c>
+      <c r="BA30" s="2">
         <f t="shared" si="133"/>
-        <v>30031.5033</v>
-      </c>
-      <c r="AK30" s="2">
+        <v>18540</v>
+      </c>
+      <c r="BB30" s="2">
         <f t="shared" si="133"/>
-        <v>29172.961599999999</v>
-      </c>
-      <c r="AL30" s="2">
-        <f t="shared" si="133"/>
-        <v>32789.690199999997</v>
-      </c>
-      <c r="AQ30" s="2">
-        <f t="shared" ref="AQ30:AR30" si="134">+AQ28+AQ29</f>
-        <v>823</v>
-      </c>
-      <c r="AR30" s="2">
+        <v>34205</v>
+      </c>
+      <c r="BC30" s="2">
+        <f t="shared" ref="BC30:BH30" si="134">+BC28+BC29</f>
+        <v>55763</v>
+      </c>
+      <c r="BD30" s="2">
         <f t="shared" si="134"/>
-        <v>-116</v>
-      </c>
-      <c r="AS30" s="2">
-        <f t="shared" ref="AS30:AU30" si="135">+AS28+AS29</f>
-        <v>118</v>
-      </c>
-      <c r="AT30" s="2">
+        <v>50155</v>
+      </c>
+      <c r="BE30" s="2">
+        <f t="shared" si="134"/>
+        <v>53483</v>
+      </c>
+      <c r="BF30" s="2">
+        <f t="shared" si="134"/>
+        <v>72515</v>
+      </c>
+      <c r="BG30" s="2">
+        <f t="shared" si="134"/>
+        <v>61372</v>
+      </c>
+      <c r="BH30" s="2">
+        <f t="shared" si="134"/>
+        <v>64089</v>
+      </c>
+      <c r="BI30" s="2">
+        <f t="shared" ref="BI30:BJ30" si="135">+BI28+BI29</f>
+        <v>72903</v>
+      </c>
+      <c r="BJ30" s="2">
         <f t="shared" si="135"/>
-        <v>118</v>
-      </c>
-      <c r="AU30" s="2">
-        <f t="shared" si="135"/>
-        <v>406</v>
-      </c>
-      <c r="AV30" s="2">
-        <f t="shared" ref="AV30:AW30" si="136">+AV28+AV29</f>
-        <v>1815</v>
-      </c>
-      <c r="AW30" s="2">
-        <f t="shared" si="136"/>
-        <v>2818</v>
-      </c>
-      <c r="AX30" s="2">
-        <f t="shared" ref="AX30:AY30" si="137">+AX28+AX29</f>
-        <v>5008</v>
-      </c>
-      <c r="AY30" s="2">
-        <f t="shared" si="137"/>
-        <v>8947</v>
-      </c>
-      <c r="AZ30" s="2">
-        <f t="shared" ref="AZ30:BB30" si="138">+AZ28+AZ29</f>
-        <v>12066</v>
-      </c>
-      <c r="BA30" s="2">
-        <f t="shared" si="138"/>
-        <v>18540</v>
-      </c>
-      <c r="BB30" s="2">
-        <f t="shared" si="138"/>
-        <v>34205</v>
-      </c>
-      <c r="BC30" s="2">
-        <f t="shared" ref="BC30:BH30" si="139">+BC28+BC29</f>
-        <v>55763</v>
-      </c>
-      <c r="BD30" s="2">
-        <f t="shared" si="139"/>
-        <v>50155</v>
-      </c>
-      <c r="BE30" s="2">
-        <f t="shared" si="139"/>
-        <v>53483</v>
-      </c>
-      <c r="BF30" s="2">
-        <f t="shared" si="139"/>
-        <v>72515</v>
-      </c>
-      <c r="BG30" s="2">
-        <f t="shared" si="139"/>
-        <v>61372</v>
-      </c>
-      <c r="BH30" s="2">
-        <f t="shared" si="139"/>
-        <v>64089</v>
-      </c>
-      <c r="BI30" s="2">
-        <f t="shared" ref="BI30:BJ30" si="140">+BI28+BI29</f>
-        <v>72903</v>
-      </c>
-      <c r="BJ30" s="2">
-        <f t="shared" si="140"/>
         <v>65737</v>
       </c>
       <c r="BK30" s="2">
@@ -6561,75 +6603,75 @@
         <v>119103</v>
       </c>
       <c r="BN30" s="2">
-        <f t="shared" ref="BN30:CE30" si="141">+BN28+BN29</f>
+        <f t="shared" ref="BN30:CE30" si="136">+BN28+BN29</f>
         <v>113736</v>
       </c>
       <c r="BO30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>123485</v>
       </c>
       <c r="BP30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>139063.61999429748</v>
       </c>
       <c r="BQ30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>151775.11280931855</v>
       </c>
       <c r="BR30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>165598.87969255034</v>
       </c>
       <c r="BS30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>180634.46636454249</v>
       </c>
       <c r="BT30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>191617.78812544863</v>
       </c>
       <c r="BU30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>202043.13562531775</v>
       </c>
       <c r="BV30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>213010.89772704628</v>
       </c>
       <c r="BW30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>224548.71447310344</v>
       </c>
       <c r="BX30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>236685.62254490727</v>
       </c>
       <c r="BY30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>248204.78470747796</v>
       </c>
       <c r="BZ30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>260079.70672053329</v>
       </c>
       <c r="CA30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>272517.92097923666</v>
       </c>
       <c r="CB30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>285546.14318630204</v>
       </c>
       <c r="CC30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>299192.36142075481</v>
       </c>
       <c r="CD30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>313485.89711021993</v>
       </c>
       <c r="CE30" s="2">
-        <f t="shared" si="141"/>
+        <f t="shared" si="136"/>
         <v>328457.46894459665</v>
       </c>
     </row>
@@ -6724,15 +6766,15 @@
       </c>
       <c r="AI31" s="2">
         <f>+AI30*0.15</f>
-        <v>6539.1167999999998</v>
+        <v>7748.8544999999986</v>
       </c>
       <c r="AJ31" s="2">
         <f>+AJ30*0.15</f>
-        <v>4504.7254949999997</v>
+        <v>5478.0209999999997</v>
       </c>
       <c r="AK31" s="2">
         <f>+AK30*0.15</f>
-        <v>4375.9442399999998</v>
+        <v>5316.6764999999987</v>
       </c>
       <c r="AL31" s="2">
         <f>+AL30*0.15</f>
@@ -6803,11 +6845,11 @@
         <v>9680</v>
       </c>
       <c r="BL31" s="7">
-        <f t="shared" ref="BL31" si="142">SUM(O31:R31)</f>
+        <f t="shared" ref="BL31" si="137">SUM(O31:R31)</f>
         <v>14527</v>
       </c>
       <c r="BM31" s="7">
-        <f t="shared" ref="BM31" si="143">SUM(S31:V31)</f>
+        <f t="shared" ref="BM31" si="138">SUM(S31:V31)</f>
         <v>19300</v>
       </c>
       <c r="BN31" s="2">
@@ -6815,71 +6857,71 @@
         <v>16741</v>
       </c>
       <c r="BO31" s="2">
-        <f t="shared" si="123"/>
+        <f t="shared" si="118"/>
         <v>29749</v>
       </c>
       <c r="BP31" s="2">
-        <f t="shared" ref="BP31:CE31" si="144">+BP30*0.2</f>
+        <f t="shared" ref="BP31:CE31" si="139">+BP30*0.2</f>
         <v>27812.723998859496</v>
       </c>
       <c r="BQ31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>30355.022561863712</v>
       </c>
       <c r="BR31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>33119.775938510073</v>
       </c>
       <c r="BS31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>36126.893272908499</v>
       </c>
       <c r="BT31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>38323.557625089728</v>
       </c>
       <c r="BU31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>40408.627125063555</v>
       </c>
       <c r="BV31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>42602.179545409257</v>
       </c>
       <c r="BW31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>44909.742894620693</v>
       </c>
       <c r="BX31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>47337.124508981455</v>
       </c>
       <c r="BY31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>49640.956941495591</v>
       </c>
       <c r="BZ31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>52015.941344106657</v>
       </c>
       <c r="CA31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>54503.584195847332</v>
       </c>
       <c r="CB31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>57109.228637260414</v>
       </c>
       <c r="CC31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>59838.472284150965</v>
       </c>
       <c r="CD31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>62697.179422043992</v>
       </c>
       <c r="CE31" s="2">
-        <f t="shared" si="144"/>
+        <f t="shared" si="139"/>
         <v>65691.493788919339</v>
       </c>
     </row>
@@ -6888,35 +6930,35 @@
         <v>32</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" ref="C32" si="145">+C30-C31</f>
+        <f t="shared" ref="C32" si="140">+C30-C31</f>
         <v>20065</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" ref="D32:F32" si="146">+D30-D31</f>
+        <f t="shared" ref="D32:F32" si="141">+D30-D31</f>
         <v>13822</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="141"/>
         <v>11519</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="141"/>
         <v>14125</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" ref="K32:N32" si="147">+K30-K31</f>
+        <f t="shared" ref="K32:N32" si="142">+K30-K31</f>
         <v>22236</v>
       </c>
       <c r="L32" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="142"/>
         <v>11249</v>
       </c>
       <c r="M32" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="142"/>
         <v>11253</v>
       </c>
       <c r="N32" s="2">
-        <f t="shared" si="147"/>
+        <f t="shared" si="142"/>
         <v>12673</v>
       </c>
       <c r="O32" s="2">
@@ -6932,11 +6974,11 @@
         <v>21744</v>
       </c>
       <c r="R32" s="2">
-        <f t="shared" ref="R32" si="148">+R30-R31</f>
+        <f t="shared" ref="R32" si="143">+R30-R31</f>
         <v>20551</v>
       </c>
       <c r="S32" s="2">
-        <f t="shared" ref="S32" si="149">+S30-S31</f>
+        <f t="shared" ref="S32" si="144">+S30-S31</f>
         <v>34630</v>
       </c>
       <c r="T32" s="2">
@@ -6944,155 +6986,155 @@
         <v>25010</v>
       </c>
       <c r="U32" s="2">
-        <f t="shared" ref="U32:AA32" si="150">+U30-U31</f>
+        <f t="shared" ref="U32:AA32" si="145">+U30-U31</f>
         <v>19442</v>
       </c>
       <c r="V32" s="2">
+        <f t="shared" si="145"/>
+        <v>20721</v>
+      </c>
+      <c r="W32" s="2">
+        <f t="shared" si="145"/>
+        <v>29998</v>
+      </c>
+      <c r="X32" s="2">
+        <f t="shared" si="145"/>
+        <v>24160</v>
+      </c>
+      <c r="Y32" s="2">
+        <f t="shared" si="145"/>
+        <v>19881</v>
+      </c>
+      <c r="Z32" s="2">
+        <f t="shared" si="145"/>
+        <v>22956</v>
+      </c>
+      <c r="AA32" s="2">
+        <f t="shared" si="145"/>
+        <v>33916</v>
+      </c>
+      <c r="AB32" s="2">
+        <f t="shared" ref="AB32:AC32" si="146">+AB30-AB31</f>
+        <v>23636</v>
+      </c>
+      <c r="AC32" s="2">
+        <f t="shared" si="146"/>
+        <v>21448</v>
+      </c>
+      <c r="AD32" s="2">
+        <f t="shared" ref="AD32:AH32" si="147">+AD30-AD31</f>
+        <v>14736</v>
+      </c>
+      <c r="AE32" s="2">
+        <f t="shared" si="147"/>
+        <v>36330</v>
+      </c>
+      <c r="AF32" s="2">
+        <f t="shared" si="147"/>
+        <v>24780</v>
+      </c>
+      <c r="AG32" s="2">
+        <f t="shared" si="147"/>
+        <v>23434</v>
+      </c>
+      <c r="AH32" s="2">
+        <f t="shared" si="147"/>
+        <v>27466</v>
+      </c>
+      <c r="AI32" s="2">
+        <f t="shared" ref="AI32:AL32" si="148">+AI30-AI31</f>
+        <v>43910.17549999999</v>
+      </c>
+      <c r="AJ32" s="2">
+        <f t="shared" si="148"/>
+        <v>31042.118999999999</v>
+      </c>
+      <c r="AK32" s="2">
+        <f t="shared" si="148"/>
+        <v>30127.833499999997</v>
+      </c>
+      <c r="AL32" s="2">
+        <f t="shared" si="148"/>
+        <v>27871.236669999998</v>
+      </c>
+      <c r="AQ32" s="2">
+        <f t="shared" ref="AQ32:AR32" si="149">+AQ30-AQ31</f>
+        <v>517</v>
+      </c>
+      <c r="AR32" s="2">
+        <f t="shared" si="149"/>
+        <v>-116</v>
+      </c>
+      <c r="AS32" s="2">
+        <f t="shared" ref="AS32:AU32" si="150">+AS30-AS31</f>
+        <v>96</v>
+      </c>
+      <c r="AT32" s="2">
         <f t="shared" si="150"/>
-        <v>20721</v>
-      </c>
-      <c r="W32" s="2">
+        <v>94</v>
+      </c>
+      <c r="AU32" s="2">
         <f t="shared" si="150"/>
-        <v>29998</v>
-      </c>
-      <c r="X32" s="2">
-        <f t="shared" si="150"/>
-        <v>24160</v>
-      </c>
-      <c r="Y32" s="2">
-        <f t="shared" si="150"/>
-        <v>19881</v>
-      </c>
-      <c r="Z32" s="2">
-        <f t="shared" si="150"/>
-        <v>22956</v>
-      </c>
-      <c r="AA32" s="2">
-        <f t="shared" si="150"/>
-        <v>33916</v>
-      </c>
-      <c r="AB32" s="2">
-        <f t="shared" ref="AB32:AC32" si="151">+AB30-AB31</f>
-        <v>23636</v>
-      </c>
-      <c r="AC32" s="2">
+        <v>299</v>
+      </c>
+      <c r="AV32" s="2">
+        <f t="shared" ref="AV32:AW32" si="151">+AV30-AV31</f>
+        <v>1335</v>
+      </c>
+      <c r="AW32" s="2">
         <f t="shared" si="151"/>
-        <v>21448</v>
-      </c>
-      <c r="AD32" s="2">
-        <f t="shared" ref="AD32:AH32" si="152">+AD30-AD31</f>
-        <v>14736</v>
-      </c>
-      <c r="AE32" s="2">
+        <v>1989</v>
+      </c>
+      <c r="AX32" s="2">
+        <f t="shared" ref="AX32:AY32" si="152">+AX30-AX31</f>
+        <v>3496</v>
+      </c>
+      <c r="AY32" s="2">
         <f t="shared" si="152"/>
-        <v>36330</v>
-      </c>
-      <c r="AF32" s="2">
-        <f t="shared" si="152"/>
-        <v>24780</v>
-      </c>
-      <c r="AG32" s="2">
-        <f t="shared" si="152"/>
-        <v>23434</v>
-      </c>
-      <c r="AH32" s="2">
-        <f t="shared" si="152"/>
-        <v>27466</v>
-      </c>
-      <c r="AI32" s="2">
-        <f t="shared" ref="AI32:AL32" si="153">+AI30-AI31</f>
-        <v>37054.995200000005</v>
-      </c>
-      <c r="AJ32" s="2">
+        <v>6119</v>
+      </c>
+      <c r="AZ32" s="2">
+        <f t="shared" ref="AZ32:BB32" si="153">+AZ30-AZ31</f>
+        <v>8235</v>
+      </c>
+      <c r="BA32" s="2">
         <f t="shared" si="153"/>
-        <v>25526.777805000002</v>
-      </c>
-      <c r="AK32" s="2">
+        <v>14013</v>
+      </c>
+      <c r="BB32" s="2">
         <f t="shared" si="153"/>
-        <v>24797.017359999998</v>
-      </c>
-      <c r="AL32" s="2">
-        <f t="shared" si="153"/>
-        <v>27871.236669999998</v>
-      </c>
-      <c r="AQ32" s="2">
-        <f t="shared" ref="AQ32:AR32" si="154">+AQ30-AQ31</f>
-        <v>517</v>
-      </c>
-      <c r="AR32" s="2">
+        <v>25922</v>
+      </c>
+      <c r="BC32" s="2">
+        <f t="shared" ref="BC32:BH32" si="154">+BC30-BC31</f>
+        <v>41733</v>
+      </c>
+      <c r="BD32" s="2">
         <f t="shared" si="154"/>
-        <v>-116</v>
-      </c>
-      <c r="AS32" s="2">
-        <f t="shared" ref="AS32:AU32" si="155">+AS30-AS31</f>
-        <v>96</v>
-      </c>
-      <c r="AT32" s="2">
+        <v>37037</v>
+      </c>
+      <c r="BE32" s="2">
+        <f t="shared" si="154"/>
+        <v>39510</v>
+      </c>
+      <c r="BF32" s="2">
+        <f t="shared" si="154"/>
+        <v>53394</v>
+      </c>
+      <c r="BG32" s="2">
+        <f t="shared" si="154"/>
+        <v>45687</v>
+      </c>
+      <c r="BH32" s="2">
+        <f t="shared" si="154"/>
+        <v>48351</v>
+      </c>
+      <c r="BI32" s="2">
+        <f t="shared" ref="BI32:BJ32" si="155">+BI30-BI31</f>
+        <v>59531</v>
+      </c>
+      <c r="BJ32" s="2">
         <f t="shared" si="155"/>
-        <v>94</v>
-      </c>
-      <c r="AU32" s="2">
-        <f t="shared" si="155"/>
-        <v>299</v>
-      </c>
-      <c r="AV32" s="2">
-        <f t="shared" ref="AV32:AW32" si="156">+AV30-AV31</f>
-        <v>1335</v>
-      </c>
-      <c r="AW32" s="2">
-        <f t="shared" si="156"/>
-        <v>1989</v>
-      </c>
-      <c r="AX32" s="2">
-        <f t="shared" ref="AX32:AY32" si="157">+AX30-AX31</f>
-        <v>3496</v>
-      </c>
-      <c r="AY32" s="2">
-        <f t="shared" si="157"/>
-        <v>6119</v>
-      </c>
-      <c r="AZ32" s="2">
-        <f t="shared" ref="AZ32:BB32" si="158">+AZ30-AZ31</f>
-        <v>8235</v>
-      </c>
-      <c r="BA32" s="2">
-        <f t="shared" si="158"/>
-        <v>14013</v>
-      </c>
-      <c r="BB32" s="2">
-        <f t="shared" si="158"/>
-        <v>25922</v>
-      </c>
-      <c r="BC32" s="2">
-        <f t="shared" ref="BC32:BH32" si="159">+BC30-BC31</f>
-        <v>41733</v>
-      </c>
-      <c r="BD32" s="2">
-        <f t="shared" si="159"/>
-        <v>37037</v>
-      </c>
-      <c r="BE32" s="2">
-        <f t="shared" si="159"/>
-        <v>39510</v>
-      </c>
-      <c r="BF32" s="2">
-        <f t="shared" si="159"/>
-        <v>53394</v>
-      </c>
-      <c r="BG32" s="2">
-        <f t="shared" si="159"/>
-        <v>45687</v>
-      </c>
-      <c r="BH32" s="2">
-        <f t="shared" si="159"/>
-        <v>48351</v>
-      </c>
-      <c r="BI32" s="2">
-        <f t="shared" ref="BI32:BJ32" si="160">+BI30-BI31</f>
-        <v>59531</v>
-      </c>
-      <c r="BJ32" s="2">
-        <f t="shared" si="160"/>
         <v>55256</v>
       </c>
       <c r="BK32" s="2">
@@ -7112,71 +7154,71 @@
         <v>96995</v>
       </c>
       <c r="BO32" s="2">
-        <f t="shared" ref="BO32:CE32" si="161">+BO30-BO31</f>
+        <f t="shared" ref="BO32:CE32" si="156">+BO30-BO31</f>
         <v>93736</v>
       </c>
       <c r="BP32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>111250.89599543798</v>
       </c>
       <c r="BQ32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>121420.09024745485</v>
       </c>
       <c r="BR32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>132479.10375404026</v>
       </c>
       <c r="BS32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>144507.573091634</v>
       </c>
       <c r="BT32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>153294.23050035891</v>
       </c>
       <c r="BU32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>161634.50850025419</v>
       </c>
       <c r="BV32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>170408.71818163703</v>
       </c>
       <c r="BW32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>179638.97157848274</v>
       </c>
       <c r="BX32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>189348.49803592582</v>
       </c>
       <c r="BY32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>198563.82776598237</v>
       </c>
       <c r="BZ32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>208063.76537642663</v>
       </c>
       <c r="CA32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>218014.33678338933</v>
       </c>
       <c r="CB32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>228436.91454904163</v>
       </c>
       <c r="CC32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>239353.88913660386</v>
       </c>
       <c r="CD32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>250788.71768817594</v>
       </c>
       <c r="CE32" s="2">
-        <f t="shared" si="161"/>
+        <f t="shared" si="156"/>
         <v>262765.9751556773</v>
       </c>
       <c r="CF32" s="2">
@@ -7184,447 +7226,447 @@
         <v>260138.31540412051</v>
       </c>
       <c r="CG32" s="2">
-        <f t="shared" ref="CG32:ER32" si="162">+CF32*(1+$CH$37)</f>
+        <f t="shared" ref="CG32:ER32" si="157">+CF32*(1+$CH$37)</f>
         <v>257536.93225007929</v>
       </c>
       <c r="CH32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>254961.56292757849</v>
       </c>
       <c r="CI32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>252411.94729830269</v>
       </c>
       <c r="CJ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>249887.82782531966</v>
       </c>
       <c r="CK32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>247388.94954706647</v>
       </c>
       <c r="CL32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>244915.06005159579</v>
       </c>
       <c r="CM32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>242465.90945107985</v>
       </c>
       <c r="CN32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>240041.25035656904</v>
       </c>
       <c r="CO32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>237640.83785300335</v>
       </c>
       <c r="CP32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>235264.42947447332</v>
       </c>
       <c r="CQ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>232911.78517972858</v>
       </c>
       <c r="CR32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>230582.6673279313</v>
       </c>
       <c r="CS32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>228276.84065465198</v>
       </c>
       <c r="CT32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>225994.07224810545</v>
       </c>
       <c r="CU32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>223734.1315256244</v>
       </c>
       <c r="CV32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>221496.79021036814</v>
       </c>
       <c r="CW32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>219281.82230826447</v>
       </c>
       <c r="CX32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>217089.00408518183</v>
       </c>
       <c r="CY32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>214918.11404433002</v>
       </c>
       <c r="CZ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>212768.93290388671</v>
       </c>
       <c r="DA32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>210641.24357484785</v>
       </c>
       <c r="DB32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>208534.83113909938</v>
       </c>
       <c r="DC32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>206449.48282770839</v>
       </c>
       <c r="DD32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>204384.98799943129</v>
       </c>
       <c r="DE32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>202341.13811943698</v>
       </c>
       <c r="DF32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>200317.72673824261</v>
       </c>
       <c r="DG32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>198314.54947086019</v>
       </c>
       <c r="DH32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>196331.40397615157</v>
       </c>
       <c r="DI32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>194368.08993639005</v>
       </c>
       <c r="DJ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>192424.40903702614</v>
       </c>
       <c r="DK32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>190500.16494665589</v>
       </c>
       <c r="DL32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>188595.16329718934</v>
       </c>
       <c r="DM32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>186709.21166421744</v>
       </c>
       <c r="DN32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>184842.11954757525</v>
       </c>
       <c r="DO32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>182993.69835209948</v>
       </c>
       <c r="DP32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>181163.76136857847</v>
       </c>
       <c r="DQ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>179352.1237548927</v>
       </c>
       <c r="DR32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>177558.60251734377</v>
       </c>
       <c r="DS32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>175783.01649217034</v>
       </c>
       <c r="DT32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>174025.18632724864</v>
       </c>
       <c r="DU32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>172284.93446397615</v>
       </c>
       <c r="DV32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>170562.08511933638</v>
       </c>
       <c r="DW32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>168856.46426814303</v>
       </c>
       <c r="DX32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>167167.89962546161</v>
       </c>
       <c r="DY32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>165496.22062920697</v>
       </c>
       <c r="DZ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>163841.25842291489</v>
       </c>
       <c r="EA32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>162202.84583868575</v>
       </c>
       <c r="EB32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>160580.81738029889</v>
       </c>
       <c r="EC32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>158975.00920649589</v>
       </c>
       <c r="ED32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>157385.25911443093</v>
       </c>
       <c r="EE32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>155811.40652328663</v>
       </c>
       <c r="EF32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>154253.29245805377</v>
       </c>
       <c r="EG32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>152710.75953347323</v>
       </c>
       <c r="EH32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>151183.6519381385</v>
       </c>
       <c r="EI32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>149671.81541875712</v>
       </c>
       <c r="EJ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>148175.09726456954</v>
       </c>
       <c r="EK32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>146693.34629192384</v>
       </c>
       <c r="EL32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>145226.41282900461</v>
       </c>
       <c r="EM32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>143774.14870071455</v>
       </c>
       <c r="EN32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>142336.4072137074</v>
       </c>
       <c r="EO32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>140913.04314157032</v>
       </c>
       <c r="EP32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>139503.9127101546</v>
       </c>
       <c r="EQ32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>138108.87358305306</v>
       </c>
       <c r="ER32" s="2">
-        <f t="shared" si="162"/>
+        <f t="shared" si="157"/>
         <v>136727.78484722253</v>
       </c>
       <c r="ES32" s="2">
-        <f t="shared" ref="ES32:GM32" si="163">+ER32*(1+$CH$37)</f>
+        <f t="shared" ref="ES32:GM32" si="158">+ER32*(1+$CH$37)</f>
         <v>135360.50699875029</v>
       </c>
       <c r="ET32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>134006.90192876279</v>
       </c>
       <c r="EU32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>132666.83290947517</v>
       </c>
       <c r="EV32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>131340.16458038043</v>
       </c>
       <c r="EW32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>130026.76293457662</v>
       </c>
       <c r="EX32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>128726.49530523086</v>
       </c>
       <c r="EY32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>127439.23035217855</v>
       </c>
       <c r="EZ32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>126164.83804865676</v>
       </c>
       <c r="FA32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>124903.18966817019</v>
       </c>
       <c r="FB32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>123654.15777148849</v>
       </c>
       <c r="FC32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>122417.6161937736</v>
       </c>
       <c r="FD32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>121193.44003183587</v>
       </c>
       <c r="FE32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>119981.5056315175</v>
       </c>
       <c r="FF32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>118781.69057520233</v>
       </c>
       <c r="FG32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>117593.8736694503</v>
       </c>
       <c r="FH32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>116417.9349327558</v>
       </c>
       <c r="FI32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>115253.75558342824</v>
       </c>
       <c r="FJ32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>114101.21802759396</v>
       </c>
       <c r="FK32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>112960.20584731802</v>
       </c>
       <c r="FL32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>111830.60378884485</v>
       </c>
       <c r="FM32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>110712.29775095639</v>
       </c>
       <c r="FN32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>109605.17477344682</v>
       </c>
       <c r="FO32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>108509.12302571235</v>
       </c>
       <c r="FP32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>107424.03179545523</v>
       </c>
       <c r="FQ32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>106349.79147750068</v>
       </c>
       <c r="FR32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>105286.29356272567</v>
       </c>
       <c r="FS32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>104233.43062709841</v>
       </c>
       <c r="FT32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>103191.09632082742</v>
       </c>
       <c r="FU32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>102159.18535761915</v>
       </c>
       <c r="FV32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>101137.59350404296</v>
       </c>
       <c r="FW32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>100126.21756900253</v>
       </c>
       <c r="FX32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>99124.955393312499</v>
       </c>
       <c r="FY32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>98133.70583937937</v>
       </c>
       <c r="FZ32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>97152.368780985576</v>
       </c>
       <c r="GA32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>96180.845093175725</v>
       </c>
       <c r="GB32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>95219.036642243969</v>
       </c>
       <c r="GC32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>94266.846275821532</v>
       </c>
       <c r="GD32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>93324.177813063317</v>
       </c>
       <c r="GE32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>92390.936034932689</v>
       </c>
       <c r="GF32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>91467.026674583365</v>
       </c>
       <c r="GG32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>90552.356407837535</v>
       </c>
       <c r="GH32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>89646.832843759155</v>
       </c>
       <c r="GI32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>88750.364515321562</v>
       </c>
       <c r="GJ32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>87862.860870168341</v>
       </c>
       <c r="GK32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>86984.232261466663</v>
       </c>
       <c r="GL32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>86114.389938851993</v>
       </c>
       <c r="GM32" s="2">
-        <f t="shared" si="163"/>
+        <f t="shared" si="158"/>
         <v>85253.246039463469</v>
       </c>
     </row>
@@ -7633,19 +7675,19 @@
         <v>36</v>
       </c>
       <c r="C33" s="12">
-        <f t="shared" ref="C33" si="164">+C32/C34</f>
+        <f t="shared" ref="C33" si="159">+C32/C34</f>
         <v>0.97255857987156114</v>
       </c>
       <c r="D33" s="12">
-        <f t="shared" ref="D33:F33" si="165">+D32/D34</f>
+        <f t="shared" ref="D33:F33" si="160">+D32/D34</f>
         <v>0.68176083107937602</v>
       </c>
       <c r="E33" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="160"/>
         <v>0.58452984598534197</v>
       </c>
       <c r="F33" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="160"/>
         <v>0.70623460408563088</v>
       </c>
       <c r="G33" s="12"/>
@@ -7653,19 +7695,19 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
       <c r="K33" s="12">
-        <f t="shared" ref="K33:N33" si="166">+K32/K34</f>
+        <f t="shared" ref="K33:N33" si="161">+K32/K34</f>
         <v>1.2479223042091785</v>
       </c>
       <c r="L33" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="161"/>
         <v>0.63846699811252383</v>
       </c>
       <c r="M33" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="161"/>
         <v>0.64601300384622584</v>
       </c>
       <c r="N33" s="12">
-        <f t="shared" si="166"/>
+        <f t="shared" si="161"/>
         <v>0.73438904632051849</v>
       </c>
       <c r="O33" s="12">
@@ -7681,11 +7723,11 @@
         <v>1.2956943963183782</v>
       </c>
       <c r="R33" s="12">
-        <f t="shared" ref="R33" si="167">+R32/R34</f>
+        <f t="shared" ref="R33" si="162">+R32/R34</f>
         <v>1.2354000701047909</v>
       </c>
       <c r="S33" s="12">
-        <f t="shared" ref="S33" si="168">+S32/S34</f>
+        <f t="shared" ref="S33" si="163">+S32/S34</f>
         <v>2.0963369432743812</v>
       </c>
       <c r="T33" s="12">
@@ -7693,156 +7735,156 @@
         <v>1.5246917147727936</v>
       </c>
       <c r="U33" s="12">
-        <f t="shared" ref="U33:Z33" si="169">+U32/U34</f>
+        <f t="shared" ref="U33:Z33" si="164">+U32/U34</f>
         <v>1.1955329791418789</v>
       </c>
       <c r="V33" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="164"/>
         <v>1.2855442500262897</v>
       </c>
       <c r="W33" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="164"/>
         <v>1.8800783518485347</v>
       </c>
       <c r="X33" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="164"/>
         <v>1.5245739743359175</v>
       </c>
       <c r="Y33" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="164"/>
         <v>1.2602852614896989</v>
       </c>
       <c r="Z33" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="164"/>
         <v>1.4647405630279984</v>
       </c>
       <c r="AA33" s="12">
-        <f t="shared" ref="AA33:AB33" si="170">+AA32/AA34</f>
+        <f t="shared" ref="AA33:AB33" si="165">+AA32/AA34</f>
         <v>2.1773628858750742</v>
       </c>
       <c r="AB33" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="165"/>
         <v>1.5283831076291186</v>
       </c>
       <c r="AC33" s="12">
-        <f t="shared" ref="AC33:AD33" si="171">+AC32/AC34</f>
+        <f t="shared" ref="AC33:AD33" si="166">+AC32/AC34</f>
         <v>1.3974299876043894</v>
       </c>
       <c r="AD33" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="166"/>
         <v>0.96674815403651804</v>
       </c>
       <c r="AE33" s="12">
-        <f t="shared" ref="AE33:AH33" si="172">+AE32/AE34</f>
+        <f t="shared" ref="AE33:AH33" si="167">+AE32/AE34</f>
         <v>2.3978828931549452</v>
       </c>
       <c r="AF33" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="167"/>
         <v>1.6458409340565736</v>
       </c>
       <c r="AG33" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="167"/>
         <v>1.5676825919732431</v>
       </c>
       <c r="AH33" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="167"/>
         <v>1.8478688453120637</v>
       </c>
       <c r="AI33" s="12">
-        <f t="shared" ref="AI33:AL33" si="173">+AI32/AI34</f>
-        <v>2.4930012085221027</v>
+        <f t="shared" ref="AI33:AL33" si="168">+AI32/AI34</f>
+        <v>2.9542068484174999</v>
       </c>
       <c r="AJ33" s="12">
-        <f t="shared" si="173"/>
-        <v>1.7174010568361964</v>
+        <f t="shared" si="168"/>
+        <v>2.0884644503229328</v>
       </c>
       <c r="AK33" s="12">
-        <f t="shared" si="173"/>
-        <v>1.6683039334525012</v>
+        <f t="shared" si="168"/>
+        <v>2.0269527743901228</v>
       </c>
       <c r="AL33" s="12">
-        <f t="shared" si="173"/>
+        <f t="shared" si="168"/>
         <v>1.8751325246782258</v>
       </c>
       <c r="AM33" s="12"/>
       <c r="AQ33" s="12">
-        <f t="shared" ref="AQ33:AR33" si="174">+AQ32/AQ34</f>
+        <f t="shared" ref="AQ33:AR33" si="169">+AQ32/AQ34</f>
         <v>1.4348197733151276</v>
       </c>
       <c r="AR33" s="12">
+        <f t="shared" si="169"/>
+        <v>-0.33563552296933274</v>
+      </c>
+      <c r="AS33" s="12">
+        <f t="shared" ref="AS33:AU33" si="170">+AS32/AS34</f>
+        <v>0.26535096811642273</v>
+      </c>
+      <c r="AT33" s="12">
+        <f t="shared" si="170"/>
+        <v>0.12931058200767059</v>
+      </c>
+      <c r="AU33" s="12">
+        <f t="shared" si="170"/>
+        <v>0.38599471742346592</v>
+      </c>
+      <c r="AV33" s="12">
+        <f t="shared" ref="AV33:AW33" si="171">+AV32/AV34</f>
+        <v>1.5581596209061837</v>
+      </c>
+      <c r="AW33" s="12">
+        <f t="shared" si="171"/>
+        <v>2.266599508162721</v>
+      </c>
+      <c r="AX33" s="12">
+        <f t="shared" ref="AX33:AY33" si="172">+AX32/AX34</f>
+        <v>3.9312171930029729</v>
+      </c>
+      <c r="AY33" s="12">
+        <f t="shared" si="172"/>
+        <v>6.7827685090656757</v>
+      </c>
+      <c r="AZ33" s="12">
+        <f t="shared" ref="AZ33:BB33" si="173">+AZ32/AZ34</f>
+        <v>9.0793325284866118</v>
+      </c>
+      <c r="BA33" s="12">
+        <f t="shared" si="173"/>
+        <v>15.15390737872981</v>
+      </c>
+      <c r="BB33" s="12">
+        <f t="shared" si="173"/>
+        <v>27.675373273759003</v>
+      </c>
+      <c r="BC33" s="12">
+        <f t="shared" ref="BC33:BH33" si="174">+BC32/BC34</f>
+        <v>6.3064763445557777</v>
+      </c>
+      <c r="BD33" s="12">
         <f t="shared" si="174"/>
-        <v>-0.33563552296933274</v>
-      </c>
-      <c r="AS33" s="12">
-        <f t="shared" ref="AS33:AU33" si="175">+AS32/AS34</f>
-        <v>0.26535096811642273</v>
-      </c>
-      <c r="AT33" s="12">
+        <v>5.6790982137298718</v>
+      </c>
+      <c r="BE33" s="12">
+        <f t="shared" si="174"/>
+        <v>6.4530744220284548</v>
+      </c>
+      <c r="BF33" s="12">
+        <f t="shared" si="174"/>
+        <v>9.216876236067618</v>
+      </c>
+      <c r="BG33" s="12">
+        <f t="shared" si="174"/>
+        <v>8.3063028961611227</v>
+      </c>
+      <c r="BH33" s="12">
+        <f t="shared" si="174"/>
+        <v>9.2067470826545037</v>
+      </c>
+      <c r="BI33" s="12">
+        <f t="shared" ref="BI33:BJ33" si="175">+BI32/BI34</f>
+        <v>2.9764851126245446</v>
+      </c>
+      <c r="BJ33" s="12">
         <f t="shared" si="175"/>
-        <v>0.12931058200767059</v>
-      </c>
-      <c r="AU33" s="12">
-        <f t="shared" si="175"/>
-        <v>0.38599471742346592</v>
-      </c>
-      <c r="AV33" s="12">
-        <f t="shared" ref="AV33:AW33" si="176">+AV32/AV34</f>
-        <v>1.5581596209061837</v>
-      </c>
-      <c r="AW33" s="12">
-        <f t="shared" si="176"/>
-        <v>2.266599508162721</v>
-      </c>
-      <c r="AX33" s="12">
-        <f t="shared" ref="AX33:AY33" si="177">+AX32/AX34</f>
-        <v>3.9312171930029729</v>
-      </c>
-      <c r="AY33" s="12">
-        <f t="shared" si="177"/>
-        <v>6.7827685090656757</v>
-      </c>
-      <c r="AZ33" s="12">
-        <f t="shared" ref="AZ33:BB33" si="178">+AZ32/AZ34</f>
-        <v>9.0793325284866118</v>
-      </c>
-      <c r="BA33" s="12">
-        <f t="shared" si="178"/>
-        <v>15.15390737872981</v>
-      </c>
-      <c r="BB33" s="12">
-        <f t="shared" si="178"/>
-        <v>27.675373273759003</v>
-      </c>
-      <c r="BC33" s="12">
-        <f t="shared" ref="BC33:BH33" si="179">+BC32/BC34</f>
-        <v>6.3064763445557777</v>
-      </c>
-      <c r="BD33" s="12">
-        <f t="shared" si="179"/>
-        <v>5.6790982137298718</v>
-      </c>
-      <c r="BE33" s="12">
-        <f t="shared" si="179"/>
-        <v>6.4530744220284548</v>
-      </c>
-      <c r="BF33" s="12">
-        <f t="shared" si="179"/>
-        <v>9.216876236067618</v>
-      </c>
-      <c r="BG33" s="12">
-        <f t="shared" si="179"/>
-        <v>8.3063028961611227</v>
-      </c>
-      <c r="BH33" s="12">
-        <f t="shared" si="179"/>
-        <v>9.2067470826545037</v>
-      </c>
-      <c r="BI33" s="12">
-        <f t="shared" ref="BI33:BJ33" si="180">+BI32/BI34</f>
-        <v>2.9764851126245446</v>
-      </c>
-      <c r="BJ33" s="12">
-        <f t="shared" si="180"/>
         <v>2.9714474637107351</v>
       </c>
       <c r="BK33" s="12">
@@ -7862,71 +7904,71 @@
         <v>6.1340548534195198</v>
       </c>
       <c r="BO33" s="12">
-        <f t="shared" ref="BO33:CE33" si="181">+BO32/BO34</f>
+        <f t="shared" ref="BO33:CE33" si="176">+BO32/BO34</f>
         <v>6.0835556272062066</v>
       </c>
       <c r="BP33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>7.4144049495061761</v>
       </c>
       <c r="BQ33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>8.0921390344319768</v>
       </c>
       <c r="BR33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>8.8291758353153149</v>
       </c>
       <c r="BS33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>9.6308227954916656</v>
       </c>
       <c r="BT33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>10.216416606651054</v>
       </c>
       <c r="BU33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>10.772261105064951</v>
       </c>
       <c r="BV33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>11.357025327479104</v>
       </c>
       <c r="BW33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>11.972182948084471</v>
       </c>
       <c r="BX33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>12.619282105167928</v>
       </c>
       <c r="BY33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>13.233445126063188</v>
       </c>
       <c r="BZ33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>13.866576066795263</v>
       </c>
       <c r="CA33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>14.529739857343289</v>
       </c>
       <c r="CB33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>15.224360889208366</v>
       </c>
       <c r="CC33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>15.951931392721198</v>
       </c>
       <c r="CD33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>16.714014687879622</v>
       </c>
       <c r="CE33" s="12">
-        <f t="shared" si="181"/>
+        <f t="shared" si="176"/>
         <v>17.512248592010998</v>
       </c>
     </row>
@@ -8023,19 +8065,19 @@
         <v>14863.609</v>
       </c>
       <c r="AI34" s="2">
-        <f t="shared" ref="AI34:AL34" si="182">+AH34</f>
+        <f t="shared" ref="AI34:AL34" si="177">+AH34</f>
         <v>14863.609</v>
       </c>
       <c r="AJ34" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="177"/>
         <v>14863.609</v>
       </c>
       <c r="AK34" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="177"/>
         <v>14863.609</v>
       </c>
       <c r="AL34" s="2">
-        <f t="shared" si="182"/>
+        <f t="shared" si="177"/>
         <v>14863.609</v>
       </c>
       <c r="AQ34" s="2">
@@ -8124,63 +8166,63 @@
         <v>15004.696499999998</v>
       </c>
       <c r="BQ34" s="2">
-        <f t="shared" ref="BQ34:CE34" si="183">+BP34</f>
+        <f t="shared" ref="BQ34:CE34" si="178">+BP34</f>
         <v>15004.696499999998</v>
       </c>
       <c r="BR34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BS34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BT34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BU34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BV34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BW34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BX34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BY34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="BZ34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="CA34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="CB34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="CC34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="CD34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
       <c r="CE34" s="2">
-        <f t="shared" si="183"/>
+        <f t="shared" si="178"/>
         <v>15004.696499999998</v>
       </c>
     </row>
@@ -8196,15 +8238,15 @@
         <v>0.21368126422635836</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" ref="P36" si="184">P20/L20-1</f>
+        <f t="shared" ref="P36" si="179">P20/L20-1</f>
         <v>0.53626121105070901</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" ref="Q36" si="185">Q20/M20-1</f>
+        <f t="shared" ref="Q36" si="180">Q20/M20-1</f>
         <v>0.36439641450950822</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" ref="R36" si="186">R20/N20-1</f>
+        <f t="shared" ref="R36" si="181">R20/N20-1</f>
         <v>0.28844786546724777</v>
       </c>
       <c r="S36" s="9">
@@ -8224,144 +8266,144 @@
         <v>8.1405950095969182E-2</v>
       </c>
       <c r="W36" s="9">
-        <f t="shared" ref="W36:Z36" si="187">W20/S20-1</f>
+        <f t="shared" ref="W36:Z36" si="182">W20/S20-1</f>
         <v>-5.4790431239662762E-2</v>
       </c>
       <c r="X36" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="182"/>
         <v>-2.5103312156911084E-2</v>
       </c>
       <c r="Y36" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="182"/>
         <v>-1.4006919080509661E-2</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="182"/>
         <v>-7.1883389168682088E-3</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" ref="AA36" si="188">AA20/W20-1</f>
+        <f t="shared" ref="AA36" si="183">AA20/W20-1</f>
         <v>2.0665107465387411E-2</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" ref="AB36" si="189">AB20/X20-1</f>
+        <f t="shared" ref="AB36" si="184">AB20/X20-1</f>
         <v>-4.3053270909781061E-2</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" ref="AC36" si="190">AC20/Y20-1</f>
+        <f t="shared" ref="AC36" si="185">AC20/Y20-1</f>
         <v>4.8657041211780383E-2</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" ref="AD36:AH36" si="191">AD20/Z20-1</f>
+        <f t="shared" ref="AD36:AH36" si="186">AD20/Z20-1</f>
         <v>6.0694093722764686E-2</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="186"/>
         <v>3.9514948776918191E-2</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="186"/>
         <v>5.075314314678292E-2</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="186"/>
         <v>9.628455180293094E-2</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="191"/>
+        <f t="shared" si="186"/>
         <v>7.9384809859896821E-2</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" ref="AI36" si="192">AI20/AE20-1</f>
-        <v>1.8476267095736132E-2</v>
+        <f t="shared" ref="AI36" si="187">AI20/AE20-1</f>
+        <v>0.15652453740949324</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" ref="AJ36" si="193">AJ20/AF20-1</f>
-        <v>2.1176711165175721E-2</v>
+        <f t="shared" ref="AJ36" si="188">AJ20/AF20-1</f>
+        <v>0.16595182415922993</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" ref="AK36" si="194">AK20/AG20-1</f>
-        <v>2.166489429580154E-2</v>
+        <f t="shared" ref="AK36" si="189">AK20/AG20-1</f>
+        <v>0.16356501765281384</v>
       </c>
       <c r="AL36" s="9">
-        <f t="shared" ref="AL36" si="195">AL20/AH20-1</f>
+        <f t="shared" ref="AL36" si="190">AL20/AH20-1</f>
         <v>2.122323502430068E-2</v>
       </c>
       <c r="AM36" s="9"/>
       <c r="AQ36" s="9">
-        <f t="shared" ref="AQ36:AW36" si="196">+AQ20/AP20-1</f>
+        <f t="shared" ref="AQ36:AW36" si="191">+AQ20/AP20-1</f>
         <v>0.30143462667101395</v>
       </c>
       <c r="AR36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>-0.32819741951647252</v>
       </c>
       <c r="AS36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>7.0669401454409808E-2</v>
       </c>
       <c r="AT36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>8.0982236154649945E-2</v>
       </c>
       <c r="AU36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>0.33381665861124543</v>
       </c>
       <c r="AV36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>0.68269114627370464</v>
       </c>
       <c r="AW36" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="191"/>
         <v>0.38647620414902017</v>
       </c>
       <c r="AX36" s="9">
-        <f t="shared" ref="AX36:AY36" si="197">+AX20/AW20-1</f>
+        <f t="shared" ref="AX36:AY36" si="192">+AX20/AW20-1</f>
         <v>0.24286823712140815</v>
       </c>
       <c r="AY36" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="192"/>
         <v>0.56173456635841035</v>
       </c>
       <c r="AZ36" s="9">
-        <f t="shared" ref="AZ36:BE36" si="198">+AZ20/AY20-1</f>
+        <f t="shared" ref="AZ36:BE36" si="193">+AZ20/AY20-1</f>
         <v>0.14440799125123371</v>
       </c>
       <c r="BA36" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="193"/>
         <v>0.52021908868430256</v>
       </c>
       <c r="BB36" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="193"/>
         <v>0.65962437715599842</v>
       </c>
       <c r="BC36" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="193"/>
         <v>0.44581474193756976</v>
       </c>
       <c r="BD36" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="193"/>
         <v>9.2020855163953197E-2</v>
       </c>
       <c r="BE36" s="9">
-        <f t="shared" si="198"/>
+        <f t="shared" si="193"/>
         <v>6.9539523725937524E-2</v>
       </c>
       <c r="BF36" s="9">
-        <f t="shared" ref="BF36:BI36" si="199">+BF20/BE20-1</f>
+        <f t="shared" ref="BF36:BI36" si="194">+BF20/BE20-1</f>
         <v>0.27856341803659834</v>
       </c>
       <c r="BG36" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="194"/>
         <v>-7.7342061913013738E-2</v>
       </c>
       <c r="BH36" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="194"/>
         <v>6.304518199398057E-2</v>
       </c>
       <c r="BI36" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="194"/>
         <v>0.15861957650261305</v>
       </c>
       <c r="BJ36" s="9">
@@ -8373,83 +8415,83 @@
         <v>5.5120803769784787E-2</v>
       </c>
       <c r="BL36" s="9">
-        <f t="shared" ref="BL36:CE36" si="200">+BL20/BK20-1</f>
+        <f t="shared" ref="BL36:CE36" si="195">+BL20/BK20-1</f>
         <v>0.33259384733074704</v>
       </c>
       <c r="BM36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>7.7937876041846099E-2</v>
       </c>
       <c r="BN36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>-2.800460530319937E-2</v>
       </c>
       <c r="BO36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>2.021994077514111E-2</v>
       </c>
       <c r="BP36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>0.11765159195963926</v>
       </c>
       <c r="BQ36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>6.6070808352805876E-2</v>
       </c>
       <c r="BR36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>6.6485316846670361E-2</v>
       </c>
       <c r="BS36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>6.6905452919508779E-2</v>
       </c>
       <c r="BT36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>5.3447771782809683E-2</v>
       </c>
       <c r="BU36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.7573033802885023E-2</v>
       </c>
       <c r="BV36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.7593868549967722E-2</v>
       </c>
       <c r="BW36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.7614782229041364E-2</v>
       </c>
       <c r="BX36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.7635775550880277E-2</v>
       </c>
       <c r="BY36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.2505849062257406E-2</v>
       </c>
       <c r="BZ36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.1760944585279347E-2</v>
       </c>
       <c r="CA36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.1799225996251632E-2</v>
       </c>
       <c r="CB36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.183761544036968E-2</v>
       </c>
       <c r="CC36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.1876110527089283E-2</v>
       </c>
       <c r="CD36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.1914708836016112E-2</v>
       </c>
       <c r="CE36" s="9">
-        <f t="shared" si="200"/>
+        <f t="shared" si="195"/>
         <v>4.1953407917453944E-2</v>
       </c>
       <c r="CG36" s="4" t="s">
@@ -8467,88 +8509,88 @@
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
       <c r="O37" s="9">
-        <f t="shared" ref="O37:X37" si="201">+O10/K10-1</f>
+        <f t="shared" ref="O37:X37" si="196">+O10/K10-1</f>
         <v>0.1722751398395197</v>
       </c>
       <c r="P37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>0.65520336993301576</v>
       </c>
       <c r="Q37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>0.49784238019532134</v>
       </c>
       <c r="R37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>0.46982302223566785</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>9.1940180191167231E-2</v>
       </c>
       <c r="T37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>5.4904251324627618E-2</v>
       </c>
       <c r="U37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>2.7672479150871787E-2</v>
       </c>
       <c r="V37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>9.6686220026757308E-2</v>
       </c>
       <c r="W37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>-8.1713854917071505E-2</v>
       </c>
       <c r="X37" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="196"/>
         <v>1.510777140597197E-2</v>
       </c>
       <c r="AX37" s="9"/>
       <c r="AY37" s="9">
-        <f t="shared" ref="AY37" si="202">+AY10/AX10-1</f>
+        <f t="shared" ref="AY37" si="197">+AY10/AX10-1</f>
         <v>53.8130081300813</v>
       </c>
       <c r="AZ37" s="9">
-        <f t="shared" ref="AZ37:BG37" si="203">+AZ10/AY10-1</f>
+        <f t="shared" ref="AZ37:BG37" si="198">+AZ10/AY10-1</f>
         <v>0.93310590329279153</v>
       </c>
       <c r="BA37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.93194199340136574</v>
       </c>
       <c r="BB37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.82683982683982693</v>
       </c>
       <c r="BC37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.71077003347971646</v>
       </c>
       <c r="BD37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.15995272708788688</v>
       </c>
       <c r="BE37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.11735448460215392</v>
       </c>
       <c r="BF37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>0.52014393426870997</v>
       </c>
       <c r="BG37" s="9">
-        <f t="shared" si="203"/>
+        <f t="shared" si="198"/>
         <v>-0.11829774059764842</v>
       </c>
       <c r="BH37" s="9">
-        <f t="shared" ref="BH37:BL37" si="204">+BH10/BG10-1</f>
+        <f t="shared" ref="BH37:BL37" si="199">+BH10/BG10-1</f>
         <v>3.3789319678127372E-2</v>
       </c>
       <c r="BI37" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="199"/>
         <v>0.16677870633106662</v>
       </c>
       <c r="BJ37" s="9">
@@ -8560,7 +8602,7 @@
         <v>-3.2307681502447672E-2</v>
       </c>
       <c r="BL37" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="199"/>
         <v>0.39331983364905176</v>
       </c>
       <c r="BM37" s="9">
@@ -8572,71 +8614,71 @@
         <v>-2.3874757286278081E-2</v>
       </c>
       <c r="BO37" s="9">
-        <f t="shared" ref="BO37:CE37" si="205">+BO10/BN10-1</f>
+        <f t="shared" ref="BO37:CE37" si="200">+BO10/BN10-1</f>
         <v>2.9912804175826757E-3</v>
       </c>
       <c r="BP37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>0.13387662109590526</v>
       </c>
       <c r="BQ37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>5.6640000000000024E-2</v>
       </c>
       <c r="BR37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>5.6640000000000024E-2</v>
       </c>
       <c r="BS37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>5.6640000000000246E-2</v>
       </c>
       <c r="BT37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>5.6639999999999802E-2</v>
       </c>
       <c r="BU37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>4.6479999999999855E-2</v>
       </c>
       <c r="BV37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>4.6480000000000299E-2</v>
       </c>
       <c r="BW37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>4.6479999999999855E-2</v>
       </c>
       <c r="BX37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>4.6480000000000077E-2</v>
       </c>
       <c r="BY37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.6320000000000352E-2</v>
       </c>
       <c r="BZ37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.6319999999999908E-2</v>
       </c>
       <c r="CA37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="CB37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.6319999999999908E-2</v>
       </c>
       <c r="CC37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="CD37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.6319999999999908E-2</v>
       </c>
       <c r="CE37" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="200"/>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="CG37" s="4" t="s">
@@ -8658,35 +8700,35 @@
         <v>0.23955957530475813</v>
       </c>
       <c r="P38" s="9">
-        <f t="shared" ref="P38:W38" si="206">+P19/L19-1</f>
+        <f t="shared" ref="P38:W38" si="201">+P19/L19-1</f>
         <v>0.26618219958046141</v>
       </c>
       <c r="Q38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>0.32912739434478566</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>0.25623754209911342</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>0.23824630416851722</v>
       </c>
       <c r="T38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>0.17277084196201398</v>
       </c>
       <c r="U38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>0.12112547180601618</v>
       </c>
       <c r="V38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>4.984406631285232E-2</v>
       </c>
       <c r="W38" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="201"/>
         <v>6.4050010248001721E-2</v>
       </c>
       <c r="X38" s="9">
@@ -8694,59 +8736,59 @@
         <v>5.4790373845921003E-2</v>
       </c>
       <c r="Y38" s="9">
-        <f t="shared" ref="Y38:Z38" si="207">+Y19/U19-1</f>
+        <f t="shared" ref="Y38:Z38" si="202">+Y19/U19-1</f>
         <v>8.2075086716996593E-2</v>
       </c>
       <c r="Z38" s="9">
-        <f t="shared" si="207"/>
+        <f t="shared" si="202"/>
         <v>0.16291432145090678</v>
       </c>
       <c r="AA38" s="9">
-        <f t="shared" ref="AA38" si="208">+AA19/W19-1</f>
+        <f t="shared" ref="AA38" si="203">+AA19/W19-1</f>
         <v>0.11321390734855052</v>
       </c>
       <c r="AB38" s="9">
-        <f t="shared" ref="AB38" si="209">+AB19/X19-1</f>
+        <f t="shared" ref="AB38" si="204">+AB19/X19-1</f>
         <v>0.14157937532883724</v>
       </c>
       <c r="AC38" s="9">
-        <f t="shared" ref="AC38" si="210">+AC19/Y19-1</f>
+        <f t="shared" ref="AC38" si="205">+AC19/Y19-1</f>
         <v>0.1414227124876255</v>
       </c>
       <c r="AD38" s="9">
-        <f t="shared" ref="AD38:AE38" si="211">+AD19/Z19-1</f>
+        <f t="shared" ref="AD38:AE38" si="206">+AD19/Z19-1</f>
         <v>0.11911804248453883</v>
       </c>
       <c r="AE38" s="9">
-        <f t="shared" si="211"/>
+        <f t="shared" si="206"/>
         <v>0.13942120517368162</v>
       </c>
       <c r="AF38" s="9">
-        <f t="shared" ref="AF38" si="212">+AF19/AB19-1</f>
+        <f t="shared" ref="AF38" si="207">+AF19/AB19-1</f>
         <v>0.11639502241588806</v>
       </c>
       <c r="AG38" s="9">
-        <f t="shared" ref="AG38" si="213">+AG19/AC19-1</f>
+        <f t="shared" ref="AG38" si="208">+AG19/AC19-1</f>
         <v>0.13257341097757402</v>
       </c>
       <c r="AH38" s="9">
-        <f t="shared" ref="AH38" si="214">+AH19/AD19-1</f>
+        <f t="shared" ref="AH38" si="209">+AH19/AD19-1</f>
         <v>0.1512894441774788</v>
       </c>
       <c r="AI38" s="9">
-        <f t="shared" ref="AI38" si="215">+AI19/AE19-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AI38" si="210">+AI19/AE19-1</f>
+        <v>0.13944570994684891</v>
       </c>
       <c r="AJ38" s="9">
-        <f t="shared" ref="AJ38" si="216">+AJ19/AF19-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AJ38" si="211">+AJ19/AF19-1</f>
+        <v>0.16254456746106216</v>
       </c>
       <c r="AK38" s="9">
-        <f t="shared" ref="AK38" si="217">+AK19/AG19-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AK38" si="212">+AK19/AG19-1</f>
+        <v>0.12092039528862641</v>
       </c>
       <c r="AL38" s="9">
-        <f t="shared" ref="AL38" si="218">+AL19/AH19-1</f>
+        <f t="shared" ref="AL38" si="213">+AL19/AH19-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM38" s="9"/>
@@ -8755,15 +8797,15 @@
         <v>0.16461205595250084</v>
       </c>
       <c r="BK38" s="9">
-        <f t="shared" ref="BK38:BM38" si="219">+BK19/BJ19-1</f>
+        <f t="shared" ref="BK38:BM38" si="214">+BK19/BJ19-1</f>
         <v>0.16152167807997242</v>
       </c>
       <c r="BL38" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="214"/>
         <v>0.27259708376729663</v>
       </c>
       <c r="BM38" s="9">
-        <f t="shared" si="219"/>
+        <f t="shared" si="214"/>
         <v>0.14181951041286078</v>
       </c>
       <c r="BN38" s="9">
@@ -8771,71 +8813,71 @@
         <v>9.0504166186691215E-2</v>
       </c>
       <c r="BO38" s="9">
-        <f t="shared" ref="BO38:CE38" si="220">+BO19/BN19-1</f>
+        <f t="shared" ref="BO38:CE38" si="215">+BO19/BN19-1</f>
         <v>0.12874413145539898</v>
       </c>
       <c r="BP38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="BQ38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BR38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BS38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="BT38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BU38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BV38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BW38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BX38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BY38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BZ38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CA38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CB38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CC38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CD38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CE38" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="215"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="CG38" s="4" t="s">
@@ -8853,39 +8895,39 @@
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5">
-        <f t="shared" ref="E39" si="221">+E24/E20</f>
+        <f t="shared" ref="E39" si="216">+E24/E20</f>
         <v>0.38338496198254013</v>
       </c>
       <c r="K39" s="5">
-        <f t="shared" ref="K39" si="222">+K24/K20</f>
+        <f t="shared" ref="K39" si="217">+K24/K20</f>
         <v>0.38354806739345887</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" ref="L39:N39" si="223">+L24/L20</f>
+        <f t="shared" ref="L39:N39" si="218">+L24/L20</f>
         <v>0.38361943305952362</v>
       </c>
       <c r="M39" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="218"/>
         <v>0.37999497361146017</v>
       </c>
       <c r="N39" s="5">
-        <f t="shared" si="223"/>
+        <f t="shared" si="218"/>
         <v>0.38160375900336951</v>
       </c>
       <c r="O39" s="5">
-        <f t="shared" ref="O39:Q39" si="224">+O24/O20</f>
+        <f t="shared" ref="O39:Q39" si="219">+O24/O20</f>
         <v>0.39777815665969724</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="219"/>
         <v>0.42506474370423292</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" si="224"/>
+        <f t="shared" si="219"/>
         <v>0.43292727853230839</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" ref="R39" si="225">+R24/R20</f>
+        <f t="shared" ref="R39" si="220">+R24/R20</f>
         <v>0.42195297504798462</v>
       </c>
       <c r="S39" s="5">
@@ -8901,132 +8943,132 @@
         <v>0.43256307332537758</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" ref="V39:X39" si="226">+V24/V20</f>
+        <f t="shared" ref="V39:X39" si="221">+V24/V20</f>
         <v>0.4225922392563175</v>
       </c>
       <c r="W39" s="5">
+        <f t="shared" si="221"/>
+        <v>0.42962254809908323</v>
+      </c>
+      <c r="X39" s="5">
+        <f t="shared" si="221"/>
+        <v>0.44261672782487665</v>
+      </c>
+      <c r="Y39" s="5">
+        <f t="shared" ref="Y39:Z39" si="222">+Y24/Y20</f>
+        <v>0.44516302553883397</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="222"/>
+        <v>0.45170841806520817</v>
+      </c>
+      <c r="AA39" s="5">
+        <f t="shared" ref="AA39:AD39" si="223">+AA24/AA20</f>
+        <v>0.45874973865774621</v>
+      </c>
+      <c r="AB39" s="5">
+        <f t="shared" si="223"/>
+        <v>0.46578074554009236</v>
+      </c>
+      <c r="AC39" s="5">
+        <f t="shared" si="223"/>
+        <v>0.46257155181458898</v>
+      </c>
+      <c r="AD39" s="5">
+        <f t="shared" si="223"/>
+        <v>0.4622247972190035</v>
+      </c>
+      <c r="AE39" s="5">
+        <f t="shared" ref="AE39" si="224">+AE24/AE20</f>
+        <v>0.46882542236524538</v>
+      </c>
+      <c r="AF39" s="5">
+        <f t="shared" ref="AF39:AH39" si="225">+AF24/AF20</f>
+        <v>0.47050619238876246</v>
+      </c>
+      <c r="AG39" s="5">
+        <f t="shared" si="225"/>
+        <v>0.46490705687183631</v>
+      </c>
+      <c r="AH39" s="5">
+        <f t="shared" si="225"/>
+        <v>0.47177600374758455</v>
+      </c>
+      <c r="AI39" s="5">
+        <f t="shared" ref="AI39:AL39" si="226">+AI24/AI20</f>
+        <v>0.47</v>
+      </c>
+      <c r="AJ39" s="5">
         <f t="shared" si="226"/>
-        <v>0.42962254809908323</v>
-      </c>
-      <c r="X39" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="AK39" s="5">
         <f t="shared" si="226"/>
-        <v>0.44261672782487665</v>
-      </c>
-      <c r="Y39" s="5">
-        <f t="shared" ref="Y39:Z39" si="227">+Y24/Y20</f>
-        <v>0.44516302553883397</v>
-      </c>
-      <c r="Z39" s="5">
-        <f t="shared" si="227"/>
-        <v>0.45170841806520817</v>
-      </c>
-      <c r="AA39" s="5">
-        <f t="shared" ref="AA39:AD39" si="228">+AA24/AA20</f>
-        <v>0.45874973865774621</v>
-      </c>
-      <c r="AB39" s="5">
-        <f t="shared" si="228"/>
-        <v>0.46578074554009236</v>
-      </c>
-      <c r="AC39" s="5">
-        <f t="shared" si="228"/>
-        <v>0.46257155181458898</v>
-      </c>
-      <c r="AD39" s="5">
-        <f t="shared" si="228"/>
-        <v>0.4622247972190035</v>
-      </c>
-      <c r="AE39" s="5">
-        <f t="shared" ref="AE39" si="229">+AE24/AE20</f>
-        <v>0.46882542236524538</v>
-      </c>
-      <c r="AF39" s="5">
-        <f t="shared" ref="AF39:AH39" si="230">+AF24/AF20</f>
-        <v>0.47050619238876246</v>
-      </c>
-      <c r="AG39" s="5">
-        <f t="shared" si="230"/>
-        <v>0.46490705687183631</v>
-      </c>
-      <c r="AH39" s="5">
-        <f t="shared" si="230"/>
-        <v>0.47177600374758455</v>
-      </c>
-      <c r="AI39" s="5">
-        <f t="shared" ref="AI39:AL39" si="231">+AI24/AI20</f>
         <v>0.47</v>
       </c>
-      <c r="AJ39" s="5">
-        <f t="shared" si="231"/>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="AK39" s="5">
-        <f t="shared" si="231"/>
-        <v>0.47</v>
-      </c>
       <c r="AL39" s="5">
-        <f t="shared" si="231"/>
+        <f t="shared" si="226"/>
         <v>0.46999999999999992</v>
       </c>
       <c r="AM39" s="5"/>
       <c r="AQ39" s="5">
-        <f t="shared" ref="AQ39:AR39" si="232">+AQ24/AQ20</f>
+        <f t="shared" ref="AQ39:AR39" si="227">+AQ24/AQ20</f>
         <v>0.27132656895903795</v>
       </c>
       <c r="AR39" s="5">
-        <f t="shared" si="232"/>
+        <f t="shared" si="227"/>
         <v>0.23028155882901361</v>
       </c>
       <c r="AS39" s="5">
-        <f t="shared" ref="AS39:AV39" si="233">+AS24/AS20</f>
+        <f t="shared" ref="AS39:AV39" si="228">+AS24/AS20</f>
         <v>0.27917102055033088</v>
       </c>
       <c r="AT39" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="228"/>
         <v>0.27517319155791847</v>
       </c>
       <c r="AU39" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="228"/>
         <v>0.27285904094697427</v>
       </c>
       <c r="AV39" s="5">
-        <f t="shared" si="233"/>
+        <f t="shared" si="228"/>
         <v>0.29021606489124974</v>
       </c>
       <c r="AW39" s="5">
-        <f t="shared" ref="AW39:AY39" si="234">+AW24/AW20</f>
+        <f t="shared" ref="AW39:AY39" si="229">+AW24/AW20</f>
         <v>0.28982655966865128</v>
       </c>
       <c r="AX39" s="5">
-        <f t="shared" si="234"/>
+        <f t="shared" si="229"/>
         <v>0.33966508372906773</v>
       </c>
       <c r="AY39" s="5">
-        <f t="shared" si="234"/>
+        <f t="shared" si="229"/>
         <v>0.35200448107545812</v>
       </c>
       <c r="AZ39" s="5">
-        <f t="shared" ref="AZ39:BA39" si="235">+AZ24/AZ20</f>
+        <f t="shared" ref="AZ39:BA39" si="230">+AZ24/AZ20</f>
         <v>0.40139843841044165</v>
       </c>
       <c r="BA39" s="5">
-        <f t="shared" si="235"/>
+        <f t="shared" si="230"/>
         <v>0.39377539287083174</v>
       </c>
       <c r="BB39" s="5">
-        <f t="shared" ref="BB39:BE39" si="236">+BB24/BB20</f>
+        <f t="shared" ref="BB39:BE39" si="231">+BB24/BB20</f>
         <v>0.40478895878945764</v>
       </c>
       <c r="BC39" s="5">
-        <f t="shared" si="236"/>
+        <f t="shared" si="231"/>
         <v>0.43871239808827661</v>
       </c>
       <c r="BD39" s="5">
-        <f t="shared" si="236"/>
+        <f t="shared" si="231"/>
         <v>0.37624480720847231</v>
       </c>
       <c r="BE39" s="5">
-        <f t="shared" si="236"/>
+        <f t="shared" si="231"/>
         <v>0.38588035777783858</v>
       </c>
       <c r="BF39" s="5">
@@ -9042,23 +9084,23 @@
         <v>0.38469860491899105</v>
       </c>
       <c r="BI39" s="5">
-        <f t="shared" ref="BI39:BM39" si="237">+BI24/BI20</f>
+        <f t="shared" ref="BI39:BM39" si="232">+BI24/BI20</f>
         <v>0.38343718820007905</v>
       </c>
       <c r="BJ39" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="232"/>
         <v>0.37817768109034722</v>
       </c>
       <c r="BK39" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="232"/>
         <v>0.38233247727810865</v>
       </c>
       <c r="BL39" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="232"/>
         <v>0.41779359625167778</v>
       </c>
       <c r="BM39" s="5">
-        <f t="shared" si="237"/>
+        <f t="shared" si="232"/>
         <v>0.43309630561360085</v>
       </c>
       <c r="BN39" s="5">
@@ -9066,71 +9108,71 @@
         <v>0.44131129577207562</v>
       </c>
       <c r="BO39" s="5">
-        <f t="shared" ref="BO39:BX39" si="238">+BO24/BO20</f>
+        <f t="shared" ref="BO39:BX39" si="233">+BO24/BO20</f>
         <v>0.46206349815233932</v>
       </c>
       <c r="BP39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.45362947589520725</v>
       </c>
       <c r="BQ39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.45660936466674518</v>
       </c>
       <c r="BR39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.45964534856197958</v>
       </c>
       <c r="BS39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46273626694683956</v>
       </c>
       <c r="BT39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46240002701949035</v>
       </c>
       <c r="BU39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46263726241610775</v>
       </c>
       <c r="BV39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46287300142953525</v>
       </c>
       <c r="BW39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46310722350746308</v>
       </c>
       <c r="BX39" s="5">
-        <f t="shared" si="238"/>
+        <f t="shared" si="233"/>
         <v>0.46333990801899477</v>
       </c>
       <c r="BY39" s="5">
-        <f t="shared" ref="BY39:CE39" si="239">+BY24/BY20</f>
+        <f t="shared" ref="BY39:CE39" si="234">+BY24/BY20</f>
         <v>0.46408277662667069</v>
       </c>
       <c r="BZ39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.46490594413818304</v>
       </c>
       <c r="CA39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.46573173659229478</v>
       </c>
       <c r="CB39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.46656010281888677</v>
       </c>
       <c r="CC39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.4673909909530668</v>
       </c>
       <c r="CD39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.46822434844661281</v>
       </c>
       <c r="CE39" s="5">
-        <f t="shared" si="239"/>
+        <f t="shared" si="234"/>
         <v>0.46906012207980208</v>
       </c>
       <c r="CG39" s="4" t="s">
@@ -9155,172 +9197,172 @@
         <v>0.64396382225717652</v>
       </c>
       <c r="L40" s="5">
-        <f t="shared" ref="L40:U40" si="240">(L19-L22)/L19</f>
+        <f t="shared" ref="L40:U40" si="235">(L19-L22)/L19</f>
         <v>0.65373089601438417</v>
       </c>
       <c r="M40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.67224080267558528</v>
+      </c>
+      <c r="N40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.66925561894288266</v>
+      </c>
+      <c r="O40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.6839667533785927</v>
+      </c>
+      <c r="P40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.70072776758771671</v>
+      </c>
+      <c r="Q40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.69804414960539862</v>
+      </c>
+      <c r="R40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.704765552333534</v>
+      </c>
+      <c r="S40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.72366263578602175</v>
+      </c>
+      <c r="T40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.72609858231168967</v>
+      </c>
+      <c r="U40" s="5">
+        <f t="shared" si="235"/>
+        <v>0.71490512140379514</v>
+      </c>
+      <c r="V40" s="5">
+        <f t="shared" ref="V40:X40" si="236">(V19-V22)/V19</f>
+        <v>0.70481550969355844</v>
+      </c>
+      <c r="W40" s="5">
+        <f t="shared" si="236"/>
+        <v>0.70832129442357705</v>
+      </c>
+      <c r="X40" s="5">
+        <f t="shared" si="236"/>
+        <v>0.70990577318601422</v>
+      </c>
+      <c r="Y40" s="5">
+        <f t="shared" ref="Y40:Z40" si="237">(Y19-Y22)/Y19</f>
+        <v>0.70546363079243857</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="237"/>
+        <v>0.70937528009321504</v>
+      </c>
+      <c r="AA40" s="5">
+        <f t="shared" ref="AA40:AD40" si="238">(AA19-AA22)/AA19</f>
+        <v>0.728338452221309</v>
+      </c>
+      <c r="AB40" s="5">
+        <f t="shared" si="238"/>
+        <v>0.74617672937528801</v>
+      </c>
+      <c r="AC40" s="5">
+        <f t="shared" si="238"/>
+        <v>0.73997439392062114</v>
+      </c>
+      <c r="AD40" s="5">
+        <f t="shared" si="238"/>
+        <v>0.74030914624379307</v>
+      </c>
+      <c r="AE40" s="5">
+        <f t="shared" ref="AE40" si="239">(AE19-AE22)/AE19</f>
+        <v>0.75026575550493546</v>
+      </c>
+      <c r="AF40" s="5">
+        <f t="shared" ref="AF40:AH40" si="240">(AF19-AF22)/AF19</f>
+        <v>0.75747795083505343</v>
+      </c>
+      <c r="AG40" s="5">
         <f t="shared" si="240"/>
-        <v>0.67224080267558528</v>
-      </c>
-      <c r="N40" s="5">
+        <v>0.75575247055391459</v>
+      </c>
+      <c r="AH40" s="5">
         <f t="shared" si="240"/>
-        <v>0.66925561894288266</v>
-      </c>
-      <c r="O40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.6839667533785927</v>
-      </c>
-      <c r="P40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.70072776758771671</v>
-      </c>
-      <c r="Q40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.69804414960539862</v>
-      </c>
-      <c r="R40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.704765552333534</v>
-      </c>
-      <c r="S40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.72366263578602175</v>
-      </c>
-      <c r="T40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.72609858231168967</v>
-      </c>
-      <c r="U40" s="5">
-        <f t="shared" si="240"/>
-        <v>0.71490512140379514</v>
-      </c>
-      <c r="V40" s="5">
-        <f t="shared" ref="V40:X40" si="241">(V19-V22)/V19</f>
-        <v>0.70481550969355844</v>
-      </c>
-      <c r="W40" s="5">
+        <v>0.75283478260869563</v>
+      </c>
+      <c r="AI40" s="5">
+        <f t="shared" ref="AI40:AL40" si="241">(AI19-AI22)/AI19</f>
+        <v>1</v>
+      </c>
+      <c r="AJ40" s="5">
         <f t="shared" si="241"/>
-        <v>0.70832129442357705</v>
-      </c>
-      <c r="X40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="5">
         <f t="shared" si="241"/>
-        <v>0.70990577318601422</v>
-      </c>
-      <c r="Y40" s="5">
-        <f t="shared" ref="Y40:Z40" si="242">(Y19-Y22)/Y19</f>
-        <v>0.70546363079243857</v>
-      </c>
-      <c r="Z40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="5">
+        <f t="shared" si="241"/>
+        <v>1</v>
+      </c>
+      <c r="AM40" s="5"/>
+      <c r="AQ40" s="5">
+        <f t="shared" ref="AQ40:AR40" si="242">(AQ19-AQ22)/AQ19</f>
+        <v>1</v>
+      </c>
+      <c r="AR40" s="5">
         <f t="shared" si="242"/>
-        <v>0.70937528009321504</v>
-      </c>
-      <c r="AA40" s="5">
-        <f t="shared" ref="AA40:AD40" si="243">(AA19-AA22)/AA19</f>
-        <v>0.728338452221309</v>
-      </c>
-      <c r="AB40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS40" s="5">
+        <f t="shared" ref="AS40:AV40" si="243">(AS19-AS22)/AS19</f>
+        <v>1</v>
+      </c>
+      <c r="AT40" s="5">
         <f t="shared" si="243"/>
-        <v>0.74617672937528801</v>
-      </c>
-      <c r="AC40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AU40" s="5">
         <f t="shared" si="243"/>
-        <v>0.73997439392062114</v>
-      </c>
-      <c r="AD40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV40" s="5">
         <f t="shared" si="243"/>
-        <v>0.74030914624379307</v>
-      </c>
-      <c r="AE40" s="5">
-        <f t="shared" ref="AE40" si="244">(AE19-AE22)/AE19</f>
-        <v>0.75026575550493546</v>
-      </c>
-      <c r="AF40" s="5">
-        <f t="shared" ref="AF40:AH40" si="245">(AF19-AF22)/AF19</f>
-        <v>0.75747795083505343</v>
-      </c>
-      <c r="AG40" s="5">
+        <v>1</v>
+      </c>
+      <c r="AW40" s="5">
+        <f t="shared" ref="AW40:AY40" si="244">(AW19-AW22)/AW19</f>
+        <v>1</v>
+      </c>
+      <c r="AX40" s="5">
+        <f t="shared" si="244"/>
+        <v>1</v>
+      </c>
+      <c r="AY40" s="5">
+        <f t="shared" si="244"/>
+        <v>1</v>
+      </c>
+      <c r="AZ40" s="5">
+        <f t="shared" ref="AZ40:BA40" si="245">(AZ19-AZ22)/AZ19</f>
+        <v>1</v>
+      </c>
+      <c r="BA40" s="5">
         <f t="shared" si="245"/>
-        <v>0.75575247055391459</v>
-      </c>
-      <c r="AH40" s="5">
-        <f t="shared" si="245"/>
-        <v>0.75283478260869563</v>
-      </c>
-      <c r="AI40" s="5">
-        <f t="shared" ref="AI40:AL40" si="246">(AI19-AI22)/AI19</f>
         <v>1</v>
       </c>
-      <c r="AJ40" s="5">
+      <c r="BB40" s="5">
+        <f t="shared" ref="BB40:BE40" si="246">(BB19-BB22)/BB19</f>
+        <v>1</v>
+      </c>
+      <c r="BC40" s="5">
         <f t="shared" si="246"/>
         <v>1</v>
       </c>
-      <c r="AK40" s="5">
+      <c r="BD40" s="5">
         <f t="shared" si="246"/>
         <v>1</v>
       </c>
-      <c r="AL40" s="5">
+      <c r="BE40" s="5">
         <f t="shared" si="246"/>
-        <v>1</v>
-      </c>
-      <c r="AM40" s="5"/>
-      <c r="AQ40" s="5">
-        <f t="shared" ref="AQ40:AR40" si="247">(AQ19-AQ22)/AQ19</f>
-        <v>1</v>
-      </c>
-      <c r="AR40" s="5">
-        <f t="shared" si="247"/>
-        <v>1</v>
-      </c>
-      <c r="AS40" s="5">
-        <f t="shared" ref="AS40:AV40" si="248">(AS19-AS22)/AS19</f>
-        <v>1</v>
-      </c>
-      <c r="AT40" s="5">
-        <f t="shared" si="248"/>
-        <v>1</v>
-      </c>
-      <c r="AU40" s="5">
-        <f t="shared" si="248"/>
-        <v>1</v>
-      </c>
-      <c r="AV40" s="5">
-        <f t="shared" si="248"/>
-        <v>1</v>
-      </c>
-      <c r="AW40" s="5">
-        <f t="shared" ref="AW40:AY40" si="249">(AW19-AW22)/AW19</f>
-        <v>1</v>
-      </c>
-      <c r="AX40" s="5">
-        <f t="shared" si="249"/>
-        <v>1</v>
-      </c>
-      <c r="AY40" s="5">
-        <f t="shared" si="249"/>
-        <v>1</v>
-      </c>
-      <c r="AZ40" s="5">
-        <f t="shared" ref="AZ40:BA40" si="250">(AZ19-AZ22)/AZ19</f>
-        <v>1</v>
-      </c>
-      <c r="BA40" s="5">
-        <f t="shared" si="250"/>
-        <v>1</v>
-      </c>
-      <c r="BB40" s="5">
-        <f t="shared" ref="BB40:BE40" si="251">(BB19-BB22)/BB19</f>
-        <v>1</v>
-      </c>
-      <c r="BC40" s="5">
-        <f t="shared" si="251"/>
-        <v>1</v>
-      </c>
-      <c r="BD40" s="5">
-        <f t="shared" si="251"/>
-        <v>1</v>
-      </c>
-      <c r="BE40" s="5">
-        <f t="shared" si="251"/>
         <v>1</v>
       </c>
       <c r="BF40" s="5">
@@ -9336,23 +9378,23 @@
         <v>1</v>
       </c>
       <c r="BI40" s="5">
-        <f t="shared" ref="BI40:BM40" si="252">(BI19-BI22)/BI19</f>
+        <f t="shared" ref="BI40:BM40" si="247">(BI19-BI22)/BI19</f>
         <v>0.60772869075173597</v>
       </c>
       <c r="BJ40" s="5">
-        <f t="shared" si="252"/>
+        <f t="shared" si="247"/>
         <v>0.63738091637683347</v>
       </c>
       <c r="BK40" s="5">
-        <f t="shared" si="252"/>
+        <f t="shared" si="247"/>
         <v>0.66015101919357233</v>
       </c>
       <c r="BL40" s="5">
-        <f t="shared" si="252"/>
+        <f t="shared" si="247"/>
         <v>0.69725977347460721</v>
       </c>
       <c r="BM40" s="5">
-        <f t="shared" si="252"/>
+        <f t="shared" si="247"/>
         <v>0.71745446633132381</v>
       </c>
       <c r="BN40" s="5">
@@ -9360,71 +9402,71 @@
         <v>0.70827464788732397</v>
       </c>
       <c r="BO40" s="5">
-        <f t="shared" ref="BO40:BX40" si="253">(BO19-BO22)/BO19</f>
+        <f t="shared" ref="BO40:BX40" si="248">(BO19-BO22)/BO19</f>
         <v>0.7388035645582256</v>
       </c>
       <c r="BP40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BQ40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73000000000000009</v>
       </c>
       <c r="BR40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BS40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BT40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BU40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BV40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BW40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BX40" s="5">
-        <f t="shared" si="253"/>
+        <f t="shared" si="248"/>
         <v>0.73</v>
       </c>
       <c r="BY40" s="5">
-        <f t="shared" ref="BY40:CE40" si="254">(BY19-BY22)/BY19</f>
+        <f t="shared" ref="BY40:CE40" si="249">(BY19-BY22)/BY19</f>
         <v>0.73</v>
       </c>
       <c r="BZ40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73000000000000009</v>
       </c>
       <c r="CA40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73</v>
       </c>
       <c r="CB40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73</v>
       </c>
       <c r="CC40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73</v>
       </c>
       <c r="CD40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73</v>
       </c>
       <c r="CE40" s="5">
-        <f t="shared" si="254"/>
+        <f t="shared" si="249"/>
         <v>0.73</v>
       </c>
       <c r="CG40" s="4" t="s">
@@ -9432,7 +9474,7 @@
       </c>
       <c r="CH40" s="5">
         <f>CH39/Main!O2-1</f>
-        <v>-0.40632405297096819</v>
+        <v>-0.52185979116524084</v>
       </c>
     </row>
     <row r="41" spans="2:86" x14ac:dyDescent="0.25">
@@ -9449,172 +9491,172 @@
         <v>0.3416894215210356</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" ref="L41:V41" si="255">(L18-L21)/L18</f>
+        <f t="shared" ref="L41:V41" si="250">(L18-L21)/L18</f>
         <v>0.30343600578227509</v>
       </c>
       <c r="M41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.29736293494379851</v>
+      </c>
+      <c r="N41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.2981515085046561</v>
+      </c>
+      <c r="O41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.35063441961579467</v>
+      </c>
+      <c r="P41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.3609647372838215</v>
+      </c>
+      <c r="Q41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.36043347720022517</v>
+      </c>
+      <c r="R41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.34253184395310604</v>
+      </c>
+      <c r="S41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.38418446983117716</v>
+      </c>
+      <c r="T41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.36364692668190091</v>
+      </c>
+      <c r="U41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.34519769552521506</v>
+      </c>
+      <c r="V41" s="5">
+        <f t="shared" si="250"/>
+        <v>0.34627526142224979</v>
+      </c>
+      <c r="W41" s="5">
+        <f t="shared" ref="W41:X41" si="251">(W18-W21)/W18</f>
+        <v>0.36957920073038136</v>
+      </c>
+      <c r="X41" s="5">
+        <f t="shared" si="251"/>
+        <v>0.36702782399329087</v>
+      </c>
+      <c r="Y41" s="5">
+        <f t="shared" ref="Y41:Z41" si="252">(Y18-Y21)/Y18</f>
+        <v>0.35402086359434837</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="252"/>
+        <v>0.36612884020004766</v>
+      </c>
+      <c r="AA41" s="5">
+        <f t="shared" ref="AA41:AD41" si="253">(AA18-AA21)/AA18</f>
+        <v>0.39414045491301913</v>
+      </c>
+      <c r="AB41" s="5">
+        <f t="shared" si="253"/>
+        <v>0.36572675896301171</v>
+      </c>
+      <c r="AC41" s="5">
+        <f t="shared" si="253"/>
+        <v>0.35346956013254499</v>
+      </c>
+      <c r="AD41" s="5">
+        <f t="shared" si="253"/>
+        <v>0.36296063352297092</v>
+      </c>
+      <c r="AE41" s="5">
+        <f t="shared" ref="AE41" si="254">(AE18-AE21)/AE18</f>
+        <v>0.39315026541445486</v>
+      </c>
+      <c r="AF41" s="5">
+        <f t="shared" ref="AF41:AH41" si="255">(AF18-AF21)/AF18</f>
+        <v>0.35922810489856505</v>
+      </c>
+      <c r="AG41" s="5">
         <f t="shared" si="255"/>
-        <v>0.29736293494379851</v>
-      </c>
-      <c r="N41" s="5">
+        <v>0.3451728641556453</v>
+      </c>
+      <c r="AH41" s="5">
         <f t="shared" si="255"/>
-        <v>0.2981515085046561</v>
-      </c>
-      <c r="O41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.35063441961579467</v>
-      </c>
-      <c r="P41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.3609647372838215</v>
-      </c>
-      <c r="Q41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.36043347720022517</v>
-      </c>
-      <c r="R41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.34253184395310604</v>
-      </c>
-      <c r="S41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.38418446983117716</v>
-      </c>
-      <c r="T41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.36364692668190091</v>
-      </c>
-      <c r="U41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.34519769552521506</v>
-      </c>
-      <c r="V41" s="5">
-        <f t="shared" si="255"/>
-        <v>0.34627526142224979</v>
-      </c>
-      <c r="W41" s="5">
-        <f t="shared" ref="W41:X41" si="256">(W18-W21)/W18</f>
-        <v>0.36957920073038136</v>
-      </c>
-      <c r="X41" s="5">
+        <v>0.36216018232134134</v>
+      </c>
+      <c r="AI41" s="5">
+        <f t="shared" ref="AI41:AL41" si="256">(AI18-AI21)/AI18</f>
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="5">
         <f t="shared" si="256"/>
-        <v>0.36702782399329087</v>
-      </c>
-      <c r="Y41" s="5">
-        <f t="shared" ref="Y41:Z41" si="257">(Y18-Y21)/Y18</f>
-        <v>0.35402086359434837</v>
-      </c>
-      <c r="Z41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="5">
+        <f t="shared" si="256"/>
+        <v>1</v>
+      </c>
+      <c r="AL41" s="5">
+        <f t="shared" si="256"/>
+        <v>1</v>
+      </c>
+      <c r="AM41" s="5"/>
+      <c r="AQ41" s="5">
+        <f t="shared" ref="AQ41:AR41" si="257">(AQ18-AQ21)/AQ18</f>
+        <v>1</v>
+      </c>
+      <c r="AR41" s="5">
         <f t="shared" si="257"/>
-        <v>0.36612884020004766</v>
-      </c>
-      <c r="AA41" s="5">
-        <f t="shared" ref="AA41:AD41" si="258">(AA18-AA21)/AA18</f>
-        <v>0.39414045491301913</v>
-      </c>
-      <c r="AB41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="5">
+        <f t="shared" ref="AS41:AV41" si="258">(AS18-AS21)/AS18</f>
+        <v>1</v>
+      </c>
+      <c r="AT41" s="5">
         <f t="shared" si="258"/>
-        <v>0.36572675896301171</v>
-      </c>
-      <c r="AC41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AU41" s="5">
         <f t="shared" si="258"/>
-        <v>0.35346956013254499</v>
-      </c>
-      <c r="AD41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV41" s="5">
         <f t="shared" si="258"/>
-        <v>0.36296063352297092</v>
-      </c>
-      <c r="AE41" s="5">
-        <f t="shared" ref="AE41" si="259">(AE18-AE21)/AE18</f>
-        <v>0.39315026541445486</v>
-      </c>
-      <c r="AF41" s="5">
-        <f t="shared" ref="AF41:AH41" si="260">(AF18-AF21)/AF18</f>
-        <v>0.35922810489856505</v>
-      </c>
-      <c r="AG41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AW41" s="5">
+        <f t="shared" ref="AW41:AY41" si="259">(AW18-AW21)/AW18</f>
+        <v>1</v>
+      </c>
+      <c r="AX41" s="5">
+        <f t="shared" si="259"/>
+        <v>1</v>
+      </c>
+      <c r="AY41" s="5">
+        <f t="shared" si="259"/>
+        <v>1</v>
+      </c>
+      <c r="AZ41" s="5">
+        <f t="shared" ref="AZ41:BA41" si="260">(AZ18-AZ21)/AZ18</f>
+        <v>1</v>
+      </c>
+      <c r="BA41" s="5">
         <f t="shared" si="260"/>
-        <v>0.3451728641556453</v>
-      </c>
-      <c r="AH41" s="5">
-        <f t="shared" si="260"/>
-        <v>0.36216018232134134</v>
-      </c>
-      <c r="AI41" s="5">
-        <f t="shared" ref="AI41:AL41" si="261">(AI18-AI21)/AI18</f>
         <v>1</v>
       </c>
-      <c r="AJ41" s="5">
+      <c r="BB41" s="5">
+        <f t="shared" ref="BB41:BE41" si="261">(BB18-BB21)/BB18</f>
+        <v>1</v>
+      </c>
+      <c r="BC41" s="5">
         <f t="shared" si="261"/>
         <v>1</v>
       </c>
-      <c r="AK41" s="5">
+      <c r="BD41" s="5">
         <f t="shared" si="261"/>
         <v>1</v>
       </c>
-      <c r="AL41" s="5">
+      <c r="BE41" s="5">
         <f t="shared" si="261"/>
-        <v>1</v>
-      </c>
-      <c r="AM41" s="5"/>
-      <c r="AQ41" s="5">
-        <f t="shared" ref="AQ41:AR41" si="262">(AQ18-AQ21)/AQ18</f>
-        <v>1</v>
-      </c>
-      <c r="AR41" s="5">
-        <f t="shared" si="262"/>
-        <v>1</v>
-      </c>
-      <c r="AS41" s="5">
-        <f t="shared" ref="AS41:AV41" si="263">(AS18-AS21)/AS18</f>
-        <v>1</v>
-      </c>
-      <c r="AT41" s="5">
-        <f t="shared" si="263"/>
-        <v>1</v>
-      </c>
-      <c r="AU41" s="5">
-        <f t="shared" si="263"/>
-        <v>1</v>
-      </c>
-      <c r="AV41" s="5">
-        <f t="shared" si="263"/>
-        <v>1</v>
-      </c>
-      <c r="AW41" s="5">
-        <f t="shared" ref="AW41:AY41" si="264">(AW18-AW21)/AW18</f>
-        <v>1</v>
-      </c>
-      <c r="AX41" s="5">
-        <f t="shared" si="264"/>
-        <v>1</v>
-      </c>
-      <c r="AY41" s="5">
-        <f t="shared" si="264"/>
-        <v>1</v>
-      </c>
-      <c r="AZ41" s="5">
-        <f t="shared" ref="AZ41:BA41" si="265">(AZ18-AZ21)/AZ18</f>
-        <v>1</v>
-      </c>
-      <c r="BA41" s="5">
-        <f t="shared" si="265"/>
-        <v>1</v>
-      </c>
-      <c r="BB41" s="5">
-        <f t="shared" ref="BB41:BE41" si="266">(BB18-BB21)/BB18</f>
-        <v>1</v>
-      </c>
-      <c r="BC41" s="5">
-        <f t="shared" si="266"/>
-        <v>1</v>
-      </c>
-      <c r="BD41" s="5">
-        <f t="shared" si="266"/>
-        <v>1</v>
-      </c>
-      <c r="BE41" s="5">
-        <f t="shared" si="266"/>
         <v>1</v>
       </c>
       <c r="BF41" s="5">
@@ -9630,23 +9672,23 @@
         <v>1</v>
       </c>
       <c r="BI41" s="5">
-        <f t="shared" ref="BI41:BM41" si="267">(BI18-BI21)/BI18</f>
+        <f t="shared" ref="BI41:BM41" si="262">(BI18-BI21)/BI18</f>
         <v>0.34396294836770025</v>
       </c>
       <c r="BJ41" s="5">
-        <f t="shared" si="267"/>
+        <f t="shared" si="262"/>
         <v>0.32207795851002652</v>
       </c>
       <c r="BK41" s="5">
-        <f t="shared" si="267"/>
+        <f t="shared" si="262"/>
         <v>0.31466339293399231</v>
       </c>
       <c r="BL41" s="5">
-        <f t="shared" si="267"/>
+        <f t="shared" si="262"/>
         <v>0.35349303276483562</v>
       </c>
       <c r="BM41" s="5">
-        <f t="shared" si="267"/>
+        <f t="shared" si="262"/>
         <v>0.36283479707399452</v>
       </c>
       <c r="BN41" s="5">
@@ -9654,71 +9696,71 @@
         <v>0.36500662562691849</v>
       </c>
       <c r="BO41" s="5">
-        <f t="shared" ref="BO41:BX41" si="268">(BO18-BO21)/BO18</f>
+        <f t="shared" ref="BO41:BX41" si="263">(BO18-BO21)/BO18</f>
         <v>0.37180617636485724</v>
       </c>
       <c r="BP41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="BQ41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36</v>
       </c>
       <c r="BR41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36</v>
       </c>
       <c r="BS41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.35999999999999993</v>
       </c>
       <c r="BT41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36</v>
       </c>
       <c r="BU41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.35999999999999993</v>
       </c>
       <c r="BV41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.35999999999999993</v>
       </c>
       <c r="BW41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36</v>
       </c>
       <c r="BX41" s="5">
-        <f t="shared" si="268"/>
+        <f t="shared" si="263"/>
         <v>0.36000000000000004</v>
       </c>
       <c r="BY41" s="5">
-        <f t="shared" ref="BY41:CE41" si="269">(BY18-BY21)/BY18</f>
+        <f t="shared" ref="BY41:CE41" si="264">(BY18-BY21)/BY18</f>
         <v>0.36</v>
       </c>
       <c r="BZ41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.35999999999999993</v>
       </c>
       <c r="CA41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.36</v>
       </c>
       <c r="CB41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.36</v>
       </c>
       <c r="CC41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.36</v>
       </c>
       <c r="CD41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.36</v>
       </c>
       <c r="CE41" s="5">
-        <f t="shared" si="269"/>
+        <f t="shared" si="264"/>
         <v>0.36</v>
       </c>
     </row>
@@ -9729,39 +9771,39 @@
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5">
-        <f t="shared" ref="E42" si="270">+E28/E20</f>
+        <f t="shared" ref="E42" si="265">+E28/E20</f>
         <v>0.23677837228949591</v>
       </c>
       <c r="K42" s="5">
-        <f t="shared" ref="K42" si="271">+K28/K20</f>
+        <f t="shared" ref="K42" si="266">+K28/K20</f>
         <v>0.2784717759940753</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" ref="L42:N42" si="272">+L28/L20</f>
+        <f t="shared" ref="L42:N42" si="267">+L28/L20</f>
         <v>0.22041397287054346</v>
       </c>
       <c r="M42" s="5">
-        <f t="shared" si="272"/>
+        <f t="shared" si="267"/>
         <v>0.21933484124989527</v>
       </c>
       <c r="N42" s="5">
-        <f t="shared" si="272"/>
+        <f t="shared" si="267"/>
         <v>0.2283687285542057</v>
       </c>
       <c r="O42" s="5">
-        <f t="shared" ref="O42:Q42" si="273">+O28/O20</f>
+        <f t="shared" ref="O42:Q42" si="268">+O28/O20</f>
         <v>0.30091799100853384</v>
       </c>
       <c r="P42" s="5">
-        <f t="shared" si="273"/>
+        <f t="shared" si="268"/>
         <v>0.30700794784782998</v>
       </c>
       <c r="Q42" s="5">
-        <f t="shared" si="273"/>
+        <f t="shared" si="268"/>
         <v>0.29626445956234498</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" ref="R42" si="274">+R28/R20</f>
+        <f t="shared" ref="R42" si="269">+R28/R20</f>
         <v>0.28534069097888676</v>
       </c>
       <c r="S42" s="5">
@@ -9777,132 +9819,132 @@
         <v>0.27816150146457891</v>
       </c>
       <c r="V42" s="5">
-        <f t="shared" ref="V42:X42" si="275">+V28/V20</f>
+        <f t="shared" ref="V42:X42" si="270">+V28/V20</f>
         <v>0.27615202005635303</v>
       </c>
       <c r="W42" s="5">
+        <f t="shared" si="270"/>
+        <v>0.30742441572630896</v>
+      </c>
+      <c r="X42" s="5">
+        <f t="shared" si="270"/>
+        <v>0.29859968788223878</v>
+      </c>
+      <c r="Y42" s="5">
+        <f t="shared" ref="Y42:Z42" si="271">+Y28/Y20</f>
+        <v>0.28115945572576012</v>
+      </c>
+      <c r="Z42" s="5">
+        <f t="shared" si="271"/>
+        <v>0.30133634271156895</v>
+      </c>
+      <c r="AA42" s="5">
+        <f t="shared" ref="AA42:AD42" si="272">+AA28/AA20</f>
+        <v>0.33763746602550698</v>
+      </c>
+      <c r="AB42" s="5">
+        <f t="shared" si="272"/>
+        <v>0.30742785362467356</v>
+      </c>
+      <c r="AC42" s="5">
+        <f t="shared" si="272"/>
+        <v>0.29555708406682446</v>
+      </c>
+      <c r="AD42" s="5">
+        <f t="shared" si="272"/>
+        <v>0.31171389444854103</v>
+      </c>
+      <c r="AE42" s="5">
+        <f t="shared" ref="AE42" si="273">+AE28/AE20</f>
+        <v>0.34458567980691873</v>
+      </c>
+      <c r="AF42" s="5">
+        <f t="shared" ref="AF42:AH42" si="274">+AF28/AF20</f>
+        <v>0.31029058610094484</v>
+      </c>
+      <c r="AG42" s="5">
+        <f t="shared" si="274"/>
+        <v>0.29990641881832492</v>
+      </c>
+      <c r="AH42" s="5">
+        <f t="shared" si="274"/>
+        <v>0.31646594968086977</v>
+      </c>
+      <c r="AI42" s="5">
+        <f t="shared" ref="AI42:AL42" si="275">+AI28/AI20</f>
+        <v>0.35935216617045546</v>
+      </c>
+      <c r="AJ42" s="5">
         <f t="shared" si="275"/>
-        <v>0.30742441572630896</v>
-      </c>
-      <c r="X42" s="5">
+        <v>0.32846578644409269</v>
+      </c>
+      <c r="AK42" s="5">
         <f t="shared" si="275"/>
-        <v>0.29859968788223878</v>
-      </c>
-      <c r="Y42" s="5">
-        <f t="shared" ref="Y42:Z42" si="276">+Y28/Y20</f>
-        <v>0.28115945572576012</v>
-      </c>
-      <c r="Z42" s="5">
-        <f t="shared" si="276"/>
-        <v>0.30133634271156895</v>
-      </c>
-      <c r="AA42" s="5">
-        <f t="shared" ref="AA42:AD42" si="277">+AA28/AA20</f>
-        <v>0.33763746602550698</v>
-      </c>
-      <c r="AB42" s="5">
-        <f t="shared" si="277"/>
-        <v>0.30742785362467356</v>
-      </c>
-      <c r="AC42" s="5">
-        <f t="shared" si="277"/>
-        <v>0.29555708406682446</v>
-      </c>
-      <c r="AD42" s="5">
-        <f t="shared" si="277"/>
-        <v>0.31171389444854103</v>
-      </c>
-      <c r="AE42" s="5">
-        <f t="shared" ref="AE42" si="278">+AE28/AE20</f>
-        <v>0.34458567980691873</v>
-      </c>
-      <c r="AF42" s="5">
-        <f t="shared" ref="AF42:AH42" si="279">+AF28/AF20</f>
-        <v>0.31029058610094484</v>
-      </c>
-      <c r="AG42" s="5">
-        <f t="shared" si="279"/>
-        <v>0.29990641881832492</v>
-      </c>
-      <c r="AH42" s="5">
-        <f t="shared" si="279"/>
-        <v>0.31646594968086977</v>
-      </c>
-      <c r="AI42" s="5">
-        <f t="shared" ref="AI42:AL42" si="280">+AI28/AI20</f>
-        <v>0.34435452452909476</v>
-      </c>
-      <c r="AJ42" s="5">
-        <f t="shared" si="280"/>
-        <v>0.30840008034636845</v>
-      </c>
-      <c r="AK42" s="5">
-        <f t="shared" si="280"/>
-        <v>0.30365322803593259</v>
+        <v>0.32393969858431498</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="280"/>
+        <f t="shared" si="275"/>
         <v>0.31335515467887909</v>
       </c>
       <c r="AM42" s="5"/>
       <c r="AQ42" s="5">
-        <f t="shared" ref="AQ42:AR42" si="281">+AQ28/AQ20</f>
+        <f t="shared" ref="AQ42:AR42" si="276">+AQ28/AQ20</f>
         <v>7.7665038206188156E-2</v>
       </c>
       <c r="AR42" s="5">
-        <f t="shared" si="281"/>
+        <f t="shared" si="276"/>
         <v>-6.2092112623531606E-2</v>
       </c>
       <c r="AS42" s="5">
-        <f t="shared" ref="AS42:AV42" si="282">+AS28/AS20</f>
+        <f t="shared" ref="AS42:AV42" si="277">+AS28/AS20</f>
         <v>8.3594566353187051E-3</v>
       </c>
       <c r="AT42" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="277"/>
         <v>4.0277106492669565E-3</v>
       </c>
       <c r="AU42" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="277"/>
         <v>4.2154849619519263E-2</v>
       </c>
       <c r="AV42" s="5">
-        <f t="shared" si="282"/>
+        <f t="shared" si="277"/>
         <v>0.11844088722991888</v>
       </c>
       <c r="AW42" s="5">
-        <f t="shared" ref="AW42:AY42" si="283">+AW28/AW20</f>
+        <f t="shared" ref="AW42:AY42" si="278">+AW28/AW20</f>
         <v>0.1269997411338338</v>
       </c>
       <c r="AX42" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="278"/>
         <v>0.1836624177289011</v>
       </c>
       <c r="AY42" s="5">
-        <f t="shared" si="283"/>
+        <f t="shared" si="278"/>
         <v>0.22210663892667573</v>
       </c>
       <c r="AZ42" s="5">
-        <f t="shared" ref="AZ42:BA42" si="284">+AZ28/AZ20</f>
+        <f t="shared" ref="AZ42:BA42" si="279">+AZ28/AZ20</f>
         <v>0.2736277823097541</v>
       </c>
       <c r="BA42" s="5">
-        <f t="shared" si="284"/>
+        <f t="shared" si="279"/>
         <v>0.28187044844768111</v>
       </c>
       <c r="BB42" s="5">
-        <f t="shared" ref="BB42:BE42" si="285">+BB28/BB20</f>
+        <f t="shared" ref="BB42:BE42" si="280">+BB28/BB20</f>
         <v>0.31215068961376086</v>
       </c>
       <c r="BC42" s="5">
-        <f t="shared" si="285"/>
+        <f t="shared" si="280"/>
         <v>0.35295959311984054</v>
       </c>
       <c r="BD42" s="5">
-        <f t="shared" si="285"/>
+        <f t="shared" si="280"/>
         <v>0.28669475162366159</v>
       </c>
       <c r="BE42" s="5">
-        <f t="shared" si="285"/>
+        <f t="shared" si="280"/>
         <v>0.28722339232473537</v>
       </c>
       <c r="BF42" s="5">
@@ -9918,23 +9960,23 @@
         <v>0.26760428208729942</v>
       </c>
       <c r="BI42" s="5">
-        <f t="shared" ref="BI42:BM42" si="286">+BI28/BI20</f>
+        <f t="shared" ref="BI42:BM42" si="281">+BI28/BI20</f>
         <v>0.26694026619477024</v>
       </c>
       <c r="BJ42" s="5">
-        <f t="shared" si="286"/>
+        <f t="shared" si="281"/>
         <v>0.24572017188496928</v>
       </c>
       <c r="BK42" s="5">
-        <f t="shared" si="286"/>
+        <f t="shared" si="281"/>
         <v>0.24147314354406862</v>
       </c>
       <c r="BL42" s="5">
-        <f t="shared" si="286"/>
+        <f t="shared" si="281"/>
         <v>0.29782377527561593</v>
       </c>
       <c r="BM42" s="5">
-        <f t="shared" si="286"/>
+        <f t="shared" si="281"/>
         <v>0.30288744395528594</v>
       </c>
       <c r="BN42" s="5">
@@ -9942,71 +9984,71 @@
         <v>0.29821412265024722</v>
       </c>
       <c r="BO42" s="5">
-        <f t="shared" ref="BO42:BX42" si="287">+BO28/BO20</f>
+        <f t="shared" ref="BO42:BX42" si="282">+BO28/BO20</f>
         <v>0.31510222870075566</v>
       </c>
       <c r="BP42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.318193613213058</v>
       </c>
       <c r="BQ42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.32575601283530864</v>
       </c>
       <c r="BR42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.33326859469828157</v>
       </c>
       <c r="BS42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.34073102634804647</v>
       </c>
       <c r="BT42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.3431103942699843</v>
       </c>
       <c r="BU42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.34534871281880053</v>
       </c>
       <c r="BV42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.34755426034865977</v>
       </c>
       <c r="BW42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.34972747235449292</v>
       </c>
       <c r="BX42" s="5">
-        <f t="shared" si="287"/>
+        <f t="shared" si="282"/>
         <v>0.35186877805863043</v>
       </c>
       <c r="BY42" s="5">
-        <f t="shared" ref="BY42:CE42" si="288">+BY28/BY20</f>
+        <f t="shared" ref="BY42:CE42" si="283">+BY28/BY20</f>
         <v>0.35394884887705413</v>
       </c>
       <c r="BZ42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.35601537171682562</v>
       </c>
       <c r="CA42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.35807443872211797</v>
       </c>
       <c r="CB42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.3601260336675135</v>
       </c>
       <c r="CC42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.36217013972301637</v>
       </c>
       <c r="CD42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.36420673947358395</v>
       </c>
       <c r="CE42" s="5">
-        <f t="shared" si="288"/>
+        <f t="shared" si="283"/>
         <v>0.3662358149388944</v>
       </c>
     </row>
@@ -10025,204 +10067,204 @@
         <v>0.14206343082027933</v>
       </c>
       <c r="L43" s="5">
-        <f t="shared" ref="L43:U43" si="289">L31/L30</f>
+        <f t="shared" ref="L43:U43" si="284">L31/L30</f>
         <v>0.14358583936048724</v>
       </c>
       <c r="M43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.14341173783968944</v>
+      </c>
+      <c r="N43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.14952016643178309</v>
+      </c>
+      <c r="O43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.14366121683194855</v>
+      </c>
+      <c r="P43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.1564028417407447</v>
+      </c>
+      <c r="Q43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.10771882309491568</v>
+      </c>
+      <c r="R43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.11600997935306263</v>
+      </c>
+      <c r="S43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.16030164157028201</v>
+      </c>
+      <c r="T43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.17017817445834302</v>
+      </c>
+      <c r="U43" s="5">
+        <f t="shared" si="284"/>
+        <v>0.15711436746726784</v>
+      </c>
+      <c r="V43" s="5">
+        <f t="shared" ref="V43:X43" si="285">V31/V30</f>
+        <v>0.15963012531938192</v>
+      </c>
+      <c r="W43" s="5">
+        <f t="shared" si="285"/>
+        <v>0.15790360160570419</v>
+      </c>
+      <c r="X43" s="5">
+        <f t="shared" si="285"/>
+        <v>0.14875625396377987</v>
+      </c>
+      <c r="Y43" s="5">
+        <f t="shared" ref="Y43:Z43" si="286">Y31/Y30</f>
+        <v>0.12545638499098227</v>
+      </c>
+      <c r="Z43" s="5">
+        <f t="shared" si="286"/>
+        <v>0.14971479368842136</v>
+      </c>
+      <c r="AA43" s="5">
+        <f t="shared" ref="AA43:AD43" si="287">AA31/AA30</f>
+        <v>0.15889194752374575</v>
+      </c>
+      <c r="AB43" s="5">
+        <f t="shared" si="287"/>
+        <v>0.1576021099151757</v>
+      </c>
+      <c r="AC43" s="5">
+        <f t="shared" si="287"/>
+        <v>0.15870400878638111</v>
+      </c>
+      <c r="AD43" s="5">
+        <f t="shared" si="287"/>
+        <v>0.50233029381965555</v>
+      </c>
+      <c r="AE43" s="5">
+        <f t="shared" ref="AE43" si="288">AE31/AE30</f>
+        <v>0.14686267142588766</v>
+      </c>
+      <c r="AF43" s="5">
+        <f t="shared" ref="AF43:AH43" si="289">AF31/AF30</f>
+        <v>0.15455475946775846</v>
+      </c>
+      <c r="AG43" s="5">
         <f t="shared" si="289"/>
-        <v>0.14341173783968944</v>
-      </c>
-      <c r="N43" s="5">
+        <v>0.16399700331775535</v>
+      </c>
+      <c r="AH43" s="5">
         <f t="shared" si="289"/>
-        <v>0.14952016643178309</v>
-      </c>
-      <c r="O43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.14366121683194855</v>
-      </c>
-      <c r="P43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.1564028417407447</v>
-      </c>
-      <c r="Q43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.10771882309491568</v>
-      </c>
-      <c r="R43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.11600997935306263</v>
-      </c>
-      <c r="S43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.16030164157028201</v>
-      </c>
-      <c r="T43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.17017817445834302</v>
-      </c>
-      <c r="U43" s="5">
-        <f t="shared" si="289"/>
-        <v>0.15711436746726784</v>
-      </c>
-      <c r="V43" s="5">
-        <f t="shared" ref="V43:X43" si="290">V31/V30</f>
-        <v>0.15963012531938192</v>
-      </c>
-      <c r="W43" s="5">
+        <v>0.16272405804170223</v>
+      </c>
+      <c r="AI43" s="5">
+        <f t="shared" ref="AI43:AL43" si="290">AI31/AI30</f>
+        <v>0.15</v>
+      </c>
+      <c r="AJ43" s="5">
         <f t="shared" si="290"/>
-        <v>0.15790360160570419</v>
-      </c>
-      <c r="X43" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="AK43" s="5">
         <f t="shared" si="290"/>
-        <v>0.14875625396377987</v>
-      </c>
-      <c r="Y43" s="5">
-        <f t="shared" ref="Y43:Z43" si="291">Y31/Y30</f>
-        <v>0.12545638499098227</v>
-      </c>
-      <c r="Z43" s="5">
-        <f t="shared" si="291"/>
-        <v>0.14971479368842136</v>
-      </c>
-      <c r="AA43" s="5">
-        <f t="shared" ref="AA43:AD43" si="292">AA31/AA30</f>
-        <v>0.15889194752374575</v>
-      </c>
-      <c r="AB43" s="5">
-        <f t="shared" si="292"/>
-        <v>0.1576021099151757</v>
-      </c>
-      <c r="AC43" s="5">
-        <f t="shared" si="292"/>
-        <v>0.15870400878638111</v>
-      </c>
-      <c r="AD43" s="5">
-        <f t="shared" si="292"/>
-        <v>0.50233029381965555</v>
-      </c>
-      <c r="AE43" s="5">
-        <f t="shared" ref="AE43" si="293">AE31/AE30</f>
-        <v>0.14686267142588766</v>
-      </c>
-      <c r="AF43" s="5">
-        <f t="shared" ref="AF43:AH43" si="294">AF31/AF30</f>
-        <v>0.15455475946775846</v>
-      </c>
-      <c r="AG43" s="5">
-        <f t="shared" si="294"/>
-        <v>0.16399700331775535</v>
-      </c>
-      <c r="AH43" s="5">
-        <f t="shared" si="294"/>
-        <v>0.16272405804170223</v>
-      </c>
-      <c r="AI43" s="5">
-        <f t="shared" ref="AI43:AL43" si="295">AI31/AI30</f>
         <v>0.15</v>
       </c>
-      <c r="AJ43" s="5">
-        <f t="shared" si="295"/>
-        <v>0.15</v>
-      </c>
-      <c r="AK43" s="5">
-        <f t="shared" si="295"/>
-        <v>0.15</v>
-      </c>
       <c r="AL43" s="5">
-        <f t="shared" si="295"/>
+        <f t="shared" si="290"/>
         <v>0.15</v>
       </c>
       <c r="AM43" s="5"/>
       <c r="AQ43" s="5">
-        <f t="shared" ref="AQ43:AR43" si="296">AQ31/AQ30</f>
+        <f t="shared" ref="AQ43:AR43" si="291">AQ31/AQ30</f>
         <v>0.37181044957472659</v>
       </c>
       <c r="AR43" s="5">
+        <f t="shared" si="291"/>
+        <v>0</v>
+      </c>
+      <c r="AS43" s="5">
+        <f t="shared" ref="AS43:AV43" si="292">AS31/AS30</f>
+        <v>0.1864406779661017</v>
+      </c>
+      <c r="AT43" s="5">
+        <f t="shared" si="292"/>
+        <v>0.20338983050847459</v>
+      </c>
+      <c r="AU43" s="5">
+        <f t="shared" si="292"/>
+        <v>0.26354679802955666</v>
+      </c>
+      <c r="AV43" s="5">
+        <f t="shared" si="292"/>
+        <v>0.26446280991735538</v>
+      </c>
+      <c r="AW43" s="5">
+        <f t="shared" ref="AW43:AY43" si="293">AW31/AW30</f>
+        <v>0.29418026969481903</v>
+      </c>
+      <c r="AX43" s="5">
+        <f t="shared" si="293"/>
+        <v>0.30191693290734822</v>
+      </c>
+      <c r="AY43" s="5">
+        <f t="shared" si="293"/>
+        <v>0.3160836034424947</v>
+      </c>
+      <c r="AZ43" s="5">
+        <f t="shared" ref="AZ43:BA43" si="294">AZ31/AZ30</f>
+        <v>0.31750372948781702</v>
+      </c>
+      <c r="BA43" s="5">
+        <f t="shared" si="294"/>
+        <v>0.24417475728155341</v>
+      </c>
+      <c r="BB43" s="5">
+        <f t="shared" ref="BB43:BE43" si="295">BB31/BB30</f>
+        <v>0.24215757930127174</v>
+      </c>
+      <c r="BC43" s="5">
+        <f t="shared" si="295"/>
+        <v>0.25160052364471064</v>
+      </c>
+      <c r="BD43" s="5">
+        <f t="shared" si="295"/>
+        <v>0.26154919748778788</v>
+      </c>
+      <c r="BE43" s="5">
+        <f t="shared" si="295"/>
+        <v>0.26126058747639436</v>
+      </c>
+      <c r="BF43" s="5">
+        <f t="shared" ref="BF43:BG43" si="296">BF31/BF30</f>
+        <v>0.26368337585327173</v>
+      </c>
+      <c r="BG43" s="5">
         <f t="shared" si="296"/>
-        <v>0</v>
-      </c>
-      <c r="AS43" s="5">
-        <f t="shared" ref="AS43:AV43" si="297">AS31/AS30</f>
-        <v>0.1864406779661017</v>
-      </c>
-      <c r="AT43" s="5">
-        <f t="shared" si="297"/>
-        <v>0.20338983050847459</v>
-      </c>
-      <c r="AU43" s="5">
-        <f t="shared" si="297"/>
-        <v>0.26354679802955666</v>
-      </c>
-      <c r="AV43" s="5">
-        <f t="shared" si="297"/>
-        <v>0.26446280991735538</v>
-      </c>
-      <c r="AW43" s="5">
-        <f t="shared" ref="AW43:AY43" si="298">AW31/AW30</f>
-        <v>0.29418026969481903</v>
-      </c>
-      <c r="AX43" s="5">
+        <v>0.25557257381216192</v>
+      </c>
+      <c r="BH43" s="5">
+        <f t="shared" ref="BH43" si="297">BH31/BH30</f>
+        <v>0.24556476150353415</v>
+      </c>
+      <c r="BI43" s="5">
+        <f t="shared" ref="BI43:BM43" si="298">BI31/BI30</f>
+        <v>0.18342180705869443</v>
+      </c>
+      <c r="BJ43" s="5">
         <f t="shared" si="298"/>
-        <v>0.30191693290734822</v>
-      </c>
-      <c r="AY43" s="5">
+        <v>0.15943836804235059</v>
+      </c>
+      <c r="BK43" s="5">
         <f t="shared" si="298"/>
-        <v>0.3160836034424947</v>
-      </c>
-      <c r="AZ43" s="5">
-        <f t="shared" ref="AZ43:BA43" si="299">AZ31/AZ30</f>
-        <v>0.31750372948781702</v>
-      </c>
-      <c r="BA43" s="5">
-        <f t="shared" si="299"/>
-        <v>0.24417475728155341</v>
-      </c>
-      <c r="BB43" s="5">
-        <f t="shared" ref="BB43:BE43" si="300">BB31/BB30</f>
-        <v>0.24215757930127174</v>
-      </c>
-      <c r="BC43" s="5">
-        <f t="shared" si="300"/>
-        <v>0.25160052364471064</v>
-      </c>
-      <c r="BD43" s="5">
-        <f t="shared" si="300"/>
-        <v>0.26154919748778788</v>
-      </c>
-      <c r="BE43" s="5">
-        <f t="shared" si="300"/>
-        <v>0.26126058747639436</v>
-      </c>
-      <c r="BF43" s="5">
-        <f t="shared" ref="BF43:BG43" si="301">BF31/BF30</f>
-        <v>0.26368337585327173</v>
-      </c>
-      <c r="BG43" s="5">
-        <f t="shared" si="301"/>
-        <v>0.25557257381216192</v>
-      </c>
-      <c r="BH43" s="5">
-        <f t="shared" ref="BH43" si="302">BH31/BH30</f>
-        <v>0.24556476150353415</v>
-      </c>
-      <c r="BI43" s="5">
-        <f t="shared" ref="BI43:BM43" si="303">BI31/BI30</f>
-        <v>0.18342180705869443</v>
-      </c>
-      <c r="BJ43" s="5">
-        <f t="shared" si="303"/>
-        <v>0.15943836804235059</v>
-      </c>
-      <c r="BK43" s="5">
-        <f t="shared" si="303"/>
         <v>0.14428164731484103</v>
       </c>
       <c r="BL43" s="5">
-        <f t="shared" si="303"/>
+        <f t="shared" si="298"/>
         <v>0.13302260844085087</v>
       </c>
       <c r="BM43" s="5">
-        <f t="shared" si="303"/>
+        <f t="shared" si="298"/>
         <v>0.16204461684424407</v>
       </c>
       <c r="BN43" s="5">
@@ -10230,71 +10272,71 @@
         <v>0.14719174228036858</v>
       </c>
       <c r="BO43" s="5">
-        <f t="shared" ref="BO43:BX43" si="304">BO31/BO30</f>
+        <f t="shared" ref="BO43:BX43" si="299">BO31/BO30</f>
         <v>0.24091185164189982</v>
       </c>
       <c r="BP43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BQ43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BR43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="BS43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BT43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BU43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BV43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BW43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="BX43" s="5">
-        <f t="shared" si="304"/>
+        <f t="shared" si="299"/>
         <v>0.2</v>
       </c>
       <c r="BY43" s="5">
-        <f t="shared" ref="BY43:CE43" si="305">BY31/BY30</f>
+        <f t="shared" ref="BY43:CE43" si="300">BY31/BY30</f>
         <v>0.2</v>
       </c>
       <c r="BZ43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.2</v>
       </c>
       <c r="CA43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.2</v>
       </c>
       <c r="CB43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.2</v>
       </c>
       <c r="CC43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.2</v>
       </c>
       <c r="CD43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.2</v>
       </c>
       <c r="CE43" s="5">
-        <f t="shared" si="305"/>
+        <f t="shared" si="300"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
@@ -10317,39 +10359,39 @@
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
       <c r="V44" s="5">
-        <f t="shared" ref="V44:AD44" si="306">+V33/R33-1</f>
+        <f t="shared" ref="V44:AD44" si="301">+V33/R33-1</f>
         <v>4.058942615831751E-2</v>
       </c>
       <c r="W44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>-0.10316022532525748</v>
       </c>
       <c r="X44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>-7.7222454700431875E-5</v>
       </c>
       <c r="Y44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>5.4161853731795384E-2</v>
       </c>
       <c r="Z44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>0.13939334487945021</v>
       </c>
       <c r="AA44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>0.15812348125504605</v>
       </c>
       <c r="AB44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>2.4984903043883122E-3</v>
       </c>
       <c r="AC44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>0.10882038400780858</v>
       </c>
       <c r="AD44" s="5">
-        <f t="shared" si="306"/>
+        <f t="shared" si="301"/>
         <v>-0.33998676732349176</v>
       </c>
       <c r="AE44" s="5">
@@ -10357,31 +10399,31 @@
         <v>0.10127848174065157</v>
       </c>
       <c r="AF44" s="5">
-        <f t="shared" ref="AF44:AH44" si="307">+AF33/AB33-1</f>
+        <f t="shared" ref="AF44:AH44" si="302">+AF33/AB33-1</f>
         <v>7.6851036785966498E-2</v>
       </c>
       <c r="AG44" s="5">
-        <f t="shared" si="307"/>
+        <f t="shared" si="302"/>
         <v>0.12183265414299371</v>
       </c>
       <c r="AH44" s="5">
-        <f t="shared" si="307"/>
+        <f t="shared" si="302"/>
         <v>0.91142733254421304</v>
       </c>
       <c r="AI44" s="5">
-        <f t="shared" ref="AI44" si="308">+AI33/AE33-1</f>
-        <v>3.9667623318338174E-2</v>
+        <f t="shared" ref="AI44" si="303">+AI33/AE33-1</f>
+        <v>0.23200630725155547</v>
       </c>
       <c r="AJ44" s="5">
-        <f t="shared" ref="AJ44" si="309">+AJ33/AF33-1</f>
-        <v>4.3479367476445985E-2</v>
+        <f t="shared" ref="AJ44" si="304">+AJ33/AF33-1</f>
+        <v>0.26893456536860239</v>
       </c>
       <c r="AK44" s="5">
-        <f t="shared" ref="AK44" si="310">+AK33/AG33-1</f>
-        <v>6.418476673432072E-2</v>
+        <f t="shared" ref="AK44" si="305">+AK33/AG33-1</f>
+        <v>0.29296120577494955</v>
       </c>
       <c r="AL44" s="5">
-        <f t="shared" ref="AL44" si="311">+AL33/AH33-1</f>
+        <f t="shared" ref="AL44" si="306">+AL33/AH33-1</f>
         <v>1.475412036699919E-2</v>
       </c>
       <c r="AM44" s="5"/>
@@ -10453,63 +10495,63 @@
         <v>128</v>
       </c>
       <c r="R48" s="2">
-        <f t="shared" ref="R48:V48" si="312">R49-R61</f>
+        <f t="shared" ref="R48:V48" si="307">R49-R61</f>
         <v>65797</v>
       </c>
       <c r="S48" s="2">
-        <f t="shared" si="312"/>
+        <f t="shared" si="307"/>
         <v>79798</v>
       </c>
       <c r="T48" s="2">
-        <f t="shared" si="312"/>
+        <f t="shared" si="307"/>
         <v>72749</v>
       </c>
       <c r="U48" s="2">
-        <f t="shared" si="312"/>
+        <f t="shared" si="307"/>
         <v>59617</v>
       </c>
       <c r="V48" s="2">
-        <f t="shared" si="312"/>
+        <f t="shared" si="307"/>
         <v>49040</v>
       </c>
       <c r="W48" s="2">
-        <f t="shared" ref="W48:AF48" si="313">W49-W61</f>
+        <f t="shared" ref="W48:AF48" si="308">W49-W61</f>
         <v>54340</v>
       </c>
       <c r="X48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>56718</v>
       </c>
       <c r="Y48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>57263</v>
       </c>
       <c r="Z48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>51011</v>
       </c>
       <c r="AA48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>64535</v>
       </c>
       <c r="AB48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>57747</v>
       </c>
       <c r="AC48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>51737</v>
       </c>
       <c r="AD48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>50021</v>
       </c>
       <c r="AE48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>44569</v>
       </c>
       <c r="AF48" s="2">
-        <f t="shared" si="313"/>
+        <f t="shared" si="308"/>
         <v>34736</v>
       </c>
       <c r="AG48" s="2">
@@ -10909,67 +10951,67 @@
         <v>121</v>
       </c>
       <c r="R56" s="2">
-        <f t="shared" ref="R56:U56" si="314">SUM(R49:R55)</f>
+        <f t="shared" ref="R56:U56" si="309">SUM(R49:R55)</f>
         <v>351002</v>
       </c>
       <c r="S56" s="2">
-        <f t="shared" si="314"/>
+        <f t="shared" si="309"/>
         <v>381191</v>
       </c>
       <c r="T56" s="2">
-        <f t="shared" si="314"/>
+        <f t="shared" si="309"/>
         <v>350662</v>
       </c>
       <c r="U56" s="2">
-        <f t="shared" si="314"/>
+        <f t="shared" si="309"/>
         <v>336309</v>
       </c>
       <c r="V56" s="2">
-        <f t="shared" ref="V56:AG56" si="315">SUM(V49:V55)</f>
+        <f t="shared" ref="V56:AG56" si="310">SUM(V49:V55)</f>
         <v>352755</v>
       </c>
       <c r="W56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>346747</v>
       </c>
       <c r="X56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>332160</v>
       </c>
       <c r="Y56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>335038</v>
       </c>
       <c r="Z56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>352583</v>
       </c>
       <c r="AA56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>353514</v>
       </c>
       <c r="AB56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>337411</v>
       </c>
       <c r="AC56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>331612</v>
       </c>
       <c r="AD56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>364980</v>
       </c>
       <c r="AE56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>344085</v>
       </c>
       <c r="AF56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>331233</v>
       </c>
       <c r="AG56" s="2">
-        <f t="shared" si="315"/>
+        <f t="shared" si="310"/>
         <v>331495</v>
       </c>
     </row>
@@ -11315,67 +11357,67 @@
         <v>125</v>
       </c>
       <c r="R64" s="2">
-        <f t="shared" ref="R64:U64" si="316">SUM(R58:R63)</f>
+        <f t="shared" ref="R64:U64" si="311">SUM(R58:R63)</f>
         <v>351002</v>
       </c>
       <c r="S64" s="2">
-        <f t="shared" si="316"/>
+        <f t="shared" si="311"/>
         <v>381191</v>
       </c>
       <c r="T64" s="2">
-        <f t="shared" si="316"/>
+        <f t="shared" si="311"/>
         <v>350662</v>
       </c>
       <c r="U64" s="2">
-        <f t="shared" si="316"/>
+        <f t="shared" si="311"/>
         <v>336309</v>
       </c>
       <c r="V64" s="2">
-        <f t="shared" ref="V64:AG64" si="317">SUM(V58:V63)</f>
+        <f t="shared" ref="V64:AG64" si="312">SUM(V58:V63)</f>
         <v>352755</v>
       </c>
       <c r="W64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>346747</v>
       </c>
       <c r="X64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>332160</v>
       </c>
       <c r="Y64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>335038</v>
       </c>
       <c r="Z64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>352583</v>
       </c>
       <c r="AA64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>353514</v>
       </c>
       <c r="AB64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>337411</v>
       </c>
       <c r="AC64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>331612</v>
       </c>
       <c r="AD64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>364980</v>
       </c>
       <c r="AE64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>344085</v>
       </c>
       <c r="AF64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>331233</v>
       </c>
       <c r="AG64" s="2">
-        <f t="shared" si="317"/>
+        <f t="shared" si="312"/>
         <v>331495</v>
       </c>
     </row>
@@ -11384,19 +11426,19 @@
         <v>129</v>
       </c>
       <c r="O66" s="2">
-        <f t="shared" ref="O66" si="318">O32</f>
+        <f t="shared" ref="O66" si="313">O32</f>
         <v>28755</v>
       </c>
       <c r="S66" s="2">
-        <f t="shared" ref="S66:U66" si="319">S32</f>
+        <f t="shared" ref="S66:U66" si="314">S32</f>
         <v>34630</v>
       </c>
       <c r="T66" s="2">
-        <f t="shared" si="319"/>
+        <f t="shared" si="314"/>
         <v>25010</v>
       </c>
       <c r="U66" s="2">
-        <f t="shared" si="319"/>
+        <f t="shared" si="314"/>
         <v>19442</v>
       </c>
       <c r="V66" s="2">
@@ -11404,83 +11446,83 @@
         <v>20721</v>
       </c>
       <c r="W66" s="2">
-        <f t="shared" ref="W66:AG66" si="320">W32</f>
+        <f t="shared" ref="W66:AG66" si="315">W32</f>
         <v>29998</v>
       </c>
       <c r="X66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>24160</v>
       </c>
       <c r="Y66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>19881</v>
       </c>
       <c r="Z66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>22956</v>
       </c>
       <c r="AA66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>33916</v>
       </c>
       <c r="AB66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>23636</v>
       </c>
       <c r="AC66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>21448</v>
       </c>
       <c r="AD66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>14736</v>
       </c>
       <c r="AE66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>36330</v>
       </c>
       <c r="AF66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>24780</v>
       </c>
       <c r="AG66" s="2">
-        <f t="shared" si="320"/>
+        <f t="shared" si="315"/>
         <v>23434</v>
       </c>
       <c r="BG66" s="2">
-        <f t="shared" ref="BG66:BO66" si="321">BG32</f>
+        <f t="shared" ref="BG66:BO66" si="316">BG32</f>
         <v>45687</v>
       </c>
       <c r="BH66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>48351</v>
       </c>
       <c r="BI66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>59531</v>
       </c>
       <c r="BJ66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>55256</v>
       </c>
       <c r="BK66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>57411</v>
       </c>
       <c r="BL66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>94680</v>
       </c>
       <c r="BM66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>99803</v>
       </c>
       <c r="BN66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>96995</v>
       </c>
       <c r="BO66" s="2">
-        <f t="shared" si="321"/>
+        <f t="shared" si="316"/>
         <v>93736</v>
       </c>
     </row>
@@ -11816,31 +11858,31 @@
         <v>131</v>
       </c>
       <c r="O72" s="2">
-        <f t="shared" ref="O72:R72" si="322">SUM(O67:O71)</f>
+        <f t="shared" ref="O72:R72" si="317">SUM(O67:O71)</f>
         <v>38763</v>
       </c>
       <c r="P72" s="2">
-        <f t="shared" si="322"/>
+        <f t="shared" si="317"/>
         <v>0</v>
       </c>
       <c r="Q72" s="2">
-        <f t="shared" si="322"/>
+        <f t="shared" si="317"/>
         <v>0</v>
       </c>
       <c r="R72" s="2">
-        <f t="shared" si="322"/>
+        <f t="shared" si="317"/>
         <v>0</v>
       </c>
       <c r="S72" s="2">
-        <f t="shared" ref="S72:U72" si="323">SUM(S67:S71)</f>
+        <f t="shared" ref="S72:U72" si="318">SUM(S67:S71)</f>
         <v>46966</v>
       </c>
       <c r="T72" s="2">
-        <f t="shared" si="323"/>
+        <f t="shared" si="318"/>
         <v>28166</v>
       </c>
       <c r="U72" s="2">
-        <f t="shared" si="323"/>
+        <f t="shared" si="318"/>
         <v>22892</v>
       </c>
       <c r="V72" s="2">
@@ -11848,47 +11890,47 @@
         <v>24127</v>
       </c>
       <c r="W72" s="2">
-        <f t="shared" ref="W72:AG72" si="324">SUM(W67:W71)</f>
+        <f t="shared" ref="W72:AG72" si="319">SUM(W67:W71)</f>
         <v>34005</v>
       </c>
       <c r="X72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>28560</v>
       </c>
       <c r="Y72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>26380</v>
       </c>
       <c r="Z72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>21598</v>
       </c>
       <c r="AA72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>39895</v>
       </c>
       <c r="AB72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>22690</v>
       </c>
       <c r="AC72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>28858</v>
       </c>
       <c r="AD72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>26811</v>
       </c>
       <c r="AE72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>29935</v>
       </c>
       <c r="AF72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>23952</v>
       </c>
       <c r="AG72" s="2">
-        <f t="shared" si="324"/>
+        <f t="shared" si="319"/>
         <v>27867</v>
       </c>
       <c r="BG72" s="2">
@@ -12157,79 +12199,79 @@
         <v>138</v>
       </c>
       <c r="O77" s="2">
-        <f t="shared" ref="O77:R77" si="325">SUM(O74:O76)</f>
+        <f t="shared" ref="O77:R77" si="320">SUM(O74:O76)</f>
         <v>-8584</v>
       </c>
       <c r="P77" s="2">
-        <f t="shared" si="325"/>
+        <f t="shared" si="320"/>
         <v>0</v>
       </c>
       <c r="Q77" s="2">
-        <f t="shared" si="325"/>
+        <f t="shared" si="320"/>
         <v>0</v>
       </c>
       <c r="R77" s="2">
-        <f t="shared" si="325"/>
+        <f t="shared" si="320"/>
         <v>0</v>
       </c>
       <c r="S77" s="2">
-        <f t="shared" ref="S77:V77" si="326">SUM(S74:S76)</f>
+        <f t="shared" ref="S77:V77" si="321">SUM(S74:S76)</f>
         <v>-16106</v>
       </c>
       <c r="T77" s="2">
-        <f t="shared" si="326"/>
+        <f t="shared" si="321"/>
         <v>-9265</v>
       </c>
       <c r="U77" s="2">
-        <f t="shared" si="326"/>
+        <f t="shared" si="321"/>
         <v>4234</v>
       </c>
       <c r="V77" s="2">
-        <f t="shared" si="326"/>
+        <f t="shared" si="321"/>
         <v>-1217</v>
       </c>
       <c r="W77" s="2">
-        <f t="shared" ref="W77:AG77" si="327">SUM(W74:W76)</f>
+        <f t="shared" ref="W77:AG77" si="322">SUM(W74:W76)</f>
         <v>-1445</v>
       </c>
       <c r="X77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>2319</v>
       </c>
       <c r="Y77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>437</v>
       </c>
       <c r="Z77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>2394</v>
       </c>
       <c r="AA77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>1927</v>
       </c>
       <c r="AB77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>-310</v>
       </c>
       <c r="AC77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>-127</v>
       </c>
       <c r="AD77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>1445</v>
       </c>
       <c r="AE77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>9792</v>
       </c>
       <c r="AF77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>2917</v>
       </c>
       <c r="AG77" s="2">
-        <f t="shared" si="327"/>
+        <f t="shared" si="322"/>
         <v>5073</v>
       </c>
     </row>
@@ -12575,79 +12617,79 @@
         <v>142</v>
       </c>
       <c r="O84" s="2">
-        <f t="shared" ref="O84:R84" si="328">SUM(O79:O83)</f>
+        <f t="shared" ref="O84:R84" si="323">SUM(O79:O83)</f>
         <v>-32249</v>
       </c>
       <c r="P84" s="2">
-        <f t="shared" si="328"/>
+        <f t="shared" si="323"/>
         <v>0</v>
       </c>
       <c r="Q84" s="2">
-        <f t="shared" si="328"/>
+        <f t="shared" si="323"/>
         <v>0</v>
       </c>
       <c r="R84" s="2">
-        <f t="shared" si="328"/>
+        <f t="shared" si="323"/>
         <v>0</v>
       </c>
       <c r="S84" s="2">
-        <f t="shared" ref="S84:V84" si="329">SUM(S79:S83)</f>
+        <f t="shared" ref="S84:V84" si="324">SUM(S79:S83)</f>
         <v>-28159</v>
       </c>
       <c r="T84" s="2">
-        <f t="shared" si="329"/>
+        <f t="shared" si="324"/>
         <v>-28351</v>
       </c>
       <c r="U84" s="2">
-        <f t="shared" si="329"/>
+        <f t="shared" si="324"/>
         <v>-27445</v>
       </c>
       <c r="V84" s="2">
-        <f t="shared" si="329"/>
+        <f t="shared" si="324"/>
         <v>-26794</v>
       </c>
       <c r="W84" s="2">
-        <f t="shared" ref="W84:AG84" si="330">SUM(W79:W83)</f>
+        <f t="shared" ref="W84:AG84" si="325">SUM(W79:W83)</f>
         <v>-35563</v>
       </c>
       <c r="X84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-25724</v>
       </c>
       <c r="Y84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-24048</v>
       </c>
       <c r="Z84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-23153</v>
       </c>
       <c r="AA84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-30585</v>
       </c>
       <c r="AB84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-30433</v>
       </c>
       <c r="AC84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-36017</v>
       </c>
       <c r="AD84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-24948</v>
       </c>
       <c r="AE84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-39371</v>
       </c>
       <c r="AF84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-29006</v>
       </c>
       <c r="AG84" s="2">
-        <f t="shared" si="330"/>
+        <f t="shared" si="325"/>
         <v>-24833</v>
       </c>
     </row>
@@ -12659,23 +12701,23 @@
         <v>143</v>
       </c>
       <c r="O86" s="2">
-        <f t="shared" ref="O86" si="331">O84+O77+O72</f>
+        <f t="shared" ref="O86" si="326">O84+O77+O72</f>
         <v>-2070</v>
       </c>
       <c r="S86" s="2">
-        <f t="shared" ref="S86:V86" si="332">S84+S77+S72</f>
+        <f t="shared" ref="S86:V86" si="327">S84+S77+S72</f>
         <v>2701</v>
       </c>
       <c r="T86" s="2">
-        <f t="shared" si="332"/>
+        <f t="shared" si="327"/>
         <v>-9450</v>
       </c>
       <c r="U86" s="2">
-        <f t="shared" si="332"/>
+        <f t="shared" si="327"/>
         <v>-319</v>
       </c>
       <c r="V86" s="2">
-        <f t="shared" si="332"/>
+        <f t="shared" si="327"/>
         <v>-3884</v>
       </c>
       <c r="W86" s="2">
@@ -12683,15 +12725,15 @@
         <v>-3003</v>
       </c>
       <c r="X86" s="2">
-        <f t="shared" ref="X86:Z86" si="333">X84+X77+X72</f>
+        <f t="shared" ref="X86:Z86" si="328">X84+X77+X72</f>
         <v>5155</v>
       </c>
       <c r="Y86" s="2">
-        <f t="shared" si="333"/>
+        <f t="shared" si="328"/>
         <v>2769</v>
       </c>
       <c r="Z86" s="2">
-        <f t="shared" si="333"/>
+        <f t="shared" si="328"/>
         <v>839</v>
       </c>
       <c r="AA86" s="2">
@@ -12728,103 +12770,103 @@
         <v>160</v>
       </c>
       <c r="O88" s="2">
-        <f t="shared" ref="O88" si="334">+O72+O75</f>
+        <f t="shared" ref="O88" si="329">+O72+O75</f>
         <v>35263</v>
       </c>
       <c r="S88" s="2">
-        <f t="shared" ref="S88:V88" si="335">+S72+S75</f>
+        <f t="shared" ref="S88:V88" si="330">+S72+S75</f>
         <v>44163</v>
       </c>
       <c r="T88" s="2">
-        <f t="shared" si="335"/>
+        <f t="shared" si="330"/>
         <v>25652</v>
       </c>
       <c r="U88" s="2">
-        <f t="shared" si="335"/>
+        <f t="shared" si="330"/>
         <v>20790</v>
       </c>
       <c r="V88" s="2">
-        <f t="shared" si="335"/>
+        <f t="shared" si="330"/>
         <v>20838</v>
       </c>
       <c r="W88" s="2">
-        <f t="shared" ref="W88:Z88" si="336">+W72+W75</f>
+        <f t="shared" ref="W88:Z88" si="331">+W72+W75</f>
         <v>30218</v>
       </c>
       <c r="X88" s="2">
-        <f t="shared" si="336"/>
+        <f t="shared" si="331"/>
         <v>25644</v>
       </c>
       <c r="Y88" s="2">
-        <f t="shared" si="336"/>
+        <f t="shared" si="331"/>
         <v>24287</v>
       </c>
       <c r="Z88" s="2">
-        <f t="shared" si="336"/>
+        <f t="shared" si="331"/>
         <v>19435</v>
       </c>
       <c r="AA88" s="2">
-        <f t="shared" ref="AA88:AG88" si="337">+AA72+AA75</f>
+        <f t="shared" ref="AA88:AG88" si="332">+AA72+AA75</f>
         <v>37503</v>
       </c>
       <c r="AB88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>20694</v>
       </c>
       <c r="AC88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>26707</v>
       </c>
       <c r="AD88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>23903</v>
       </c>
       <c r="AE88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>26995</v>
       </c>
       <c r="AF88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>20881</v>
       </c>
       <c r="AG88" s="2">
-        <f t="shared" si="337"/>
+        <f t="shared" si="332"/>
         <v>24405</v>
       </c>
       <c r="BG88" s="2">
-        <f t="shared" ref="BG88:BO88" si="338">+BG75+BG72</f>
+        <f t="shared" ref="BG88:BO88" si="333">+BG75+BG72</f>
         <v>53497</v>
       </c>
       <c r="BH88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>51774</v>
       </c>
       <c r="BI88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>64121</v>
       </c>
       <c r="BJ88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>58896</v>
       </c>
       <c r="BK88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>73365</v>
       </c>
       <c r="BL88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>92953</v>
       </c>
       <c r="BM88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>111443</v>
       </c>
       <c r="BN88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>99584</v>
       </c>
       <c r="BO88" s="2">
-        <f t="shared" si="338"/>
+        <f t="shared" si="333"/>
         <v>108807</v>
       </c>
     </row>
@@ -12833,35 +12875,35 @@
         <v>161</v>
       </c>
       <c r="V89" s="2">
-        <f t="shared" ref="V89" si="339">SUM(S88:V88)</f>
+        <f t="shared" ref="V89" si="334">SUM(S88:V88)</f>
         <v>111443</v>
       </c>
       <c r="W89" s="2">
-        <f t="shared" ref="W89" si="340">SUM(T88:W88)</f>
+        <f t="shared" ref="W89" si="335">SUM(T88:W88)</f>
         <v>97498</v>
       </c>
       <c r="X89" s="2">
-        <f t="shared" ref="X89" si="341">SUM(U88:X88)</f>
+        <f t="shared" ref="X89" si="336">SUM(U88:X88)</f>
         <v>97490</v>
       </c>
       <c r="Y89" s="2">
-        <f t="shared" ref="Y89" si="342">SUM(V88:Y88)</f>
+        <f t="shared" ref="Y89" si="337">SUM(V88:Y88)</f>
         <v>100987</v>
       </c>
       <c r="Z89" s="2">
-        <f t="shared" ref="Z89:AC89" si="343">SUM(W88:Z88)</f>
+        <f t="shared" ref="Z89:AC89" si="338">SUM(W88:Z88)</f>
         <v>99584</v>
       </c>
       <c r="AA89" s="2">
-        <f t="shared" si="343"/>
+        <f t="shared" si="338"/>
         <v>106869</v>
       </c>
       <c r="AB89" s="2">
-        <f t="shared" si="343"/>
+        <f t="shared" si="338"/>
         <v>101919</v>
       </c>
       <c r="AC89" s="2">
-        <f t="shared" si="343"/>
+        <f t="shared" si="338"/>
         <v>104339</v>
       </c>
       <c r="AD89" s="2">
@@ -12884,27 +12926,27 @@
     </row>
     <row r="90" spans="2:67" x14ac:dyDescent="0.25">
       <c r="Z90" s="5">
-        <f t="shared" ref="Z90" si="344">+Z89/V89-1</f>
+        <f t="shared" ref="Z90" si="339">+Z89/V89-1</f>
         <v>-0.1064131439390541</v>
       </c>
       <c r="AA90" s="5">
-        <f t="shared" ref="AA90" si="345">+AA89/W89-1</f>
+        <f t="shared" ref="AA90" si="340">+AA89/W89-1</f>
         <v>9.6114792098299429E-2</v>
       </c>
       <c r="AB90" s="5">
-        <f t="shared" ref="AB90" si="346">+AB89/X89-1</f>
+        <f t="shared" ref="AB90" si="341">+AB89/X89-1</f>
         <v>4.5430300543645608E-2</v>
       </c>
       <c r="AC90" s="5">
-        <f t="shared" ref="AC90" si="347">+AC89/Y89-1</f>
+        <f t="shared" ref="AC90" si="342">+AC89/Y89-1</f>
         <v>3.319239109984462E-2</v>
       </c>
       <c r="AD90" s="5">
-        <f t="shared" ref="AD90:AE90" si="348">+AD89/Z89-1</f>
+        <f t="shared" ref="AD90:AE90" si="343">+AD89/Z89-1</f>
         <v>9.2615279562981989E-2</v>
       </c>
       <c r="AE90" s="5">
-        <f t="shared" si="348"/>
+        <f t="shared" si="343"/>
         <v>-8.0191636489533868E-2</v>
       </c>
       <c r="AF90" s="5">
